--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STJ Paraná" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="STJ Paraná" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000177-47.2023.8.16.0030</t>
+          <t>0077248-55.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08/06/2026 13:33</t>
+          <t>26/05/2026 16:33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08/06/2026 13:33</t>
+          <t>26/05/2026 16:33</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>09/06/2026 10:04</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000431-64.2024.8.16.0101</t>
+          <t>0018234-64.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>01/06/2026 14:33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>01/06/2026 14:33</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>09/06/2026 12:15</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000457-14.2022.8.16.0075</t>
+          <t>0034028-70.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>09/06/2026 14:17</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000464-35.2022.8.16.0033</t>
+          <t>0001222-82.2021.8.16.0054</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Erro Médico | Erro Médico | COVID-19 | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08/06/2026 16:13</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08/06/2026 16:13</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>09/06/2026 09:09</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000518-25.2020.8.16.0177</t>
+          <t>0018379-70.2021.8.16.0021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>28/06/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01/06/2026 13:43</t>
+          <t>21/05/2026 15:53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/06/2026 13:43</t>
+          <t>21/05/2026 15:53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09/06/2026 12:50</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000551-37.2022.8.16.0147</t>
+          <t>0049261-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irregularidade no atendimento | Tratamento médico-hospitalar</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>05/09/2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01/06/2026 14:43</t>
+          <t>26/05/2026 14:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/06/2026 14:43</t>
+          <t>26/05/2026 14:33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09/06/2026 12:05</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000634-67.2016.8.16.0081</t>
+          <t>0001806-23.2018.8.16.0033</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>09/02/2023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02/06/2026 13:13</t>
+          <t>20/05/2026 15:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/06/2026 13:13</t>
+          <t>20/05/2026 15:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>09/06/2026 08:33</t>
+          <t>18/06/2026 08:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000921-05.2014.8.16.0112</t>
+          <t>0001444-16.2001.8.16.0001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Usucapião Ordinária</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>07/05/2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01/06/2026 15:43</t>
+          <t>21/05/2026 15:03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/06/2026 15:43</t>
+          <t>21/05/2026 15:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>09/06/2026 08:33</t>
+          <t>18/06/2026 08:11</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001248-44.2011.8.16.0050</t>
+          <t>0002350-52.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08/06/2026 15:13</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08/06/2026 15:13</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>09/06/2026 12:40</t>
+          <t>18/06/2026 08:21</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0002140-07.2015.8.16.0116</t>
+          <t>0001213-13.2021.8.16.0025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reintegração ou Readmissão</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>21/03/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>09/06/2026 19:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>09/06/2026 19:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>09/06/2026 09:00</t>
+          <t>18/06/2026 08:30</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,37 +959,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0003129-33.2024.8.16.0072</t>
+          <t>0000431-64.2024.8.16.0101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Perdas e Danos | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01/06/2026 15:33</t>
+          <t>03/06/2026 13:13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01/06/2026 15:33</t>
+          <t>03/06/2026 13:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>09/06/2026 10:02</t>
+          <t>18/06/2026 08:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0003981-72.2016.8.16.0190</t>
+          <t>0126817-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fornecimento de Água | Irregularidade no atendimento</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01/06/2026 15:33</t>
+          <t>19/05/2026 15:03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01/06/2026 15:33</t>
+          <t>19/05/2026 15:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>09/06/2026 12:50</t>
+          <t>18/06/2026 08:50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,12 +1053,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0004337-78.2024.8.16.0031</t>
+          <t>0003010-91.2018.8.16.0069</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>03/06/2026 13:03</t>
+          <t>25/05/2026 18:13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>03/06/2026 13:03</t>
+          <t>25/05/2026 18:13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>09/06/2026 08:37</t>
+          <t>18/06/2026 08:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0006042-46.2018.8.16.0056</t>
+          <t>0009888-66.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Indenização por Dano Moral</t>
+          <t>Aquisição</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>28/08/2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08/06/2026 15:23</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08/06/2026 15:23</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>09/06/2026 08:47</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0007962-53.2023.8.16.0194</t>
+          <t>0039237-70.2017.8.16.0019</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>21/05/2026 19:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>21/05/2026 19:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>09/06/2026 11:00</t>
+          <t>18/06/2026 07:30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0011570-88.2025.8.16.0000</t>
+          <t>0001689-46.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inadimplemento</t>
+          <t>Indenização por Dano Material | Pagamento com Sub-rogação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08/06/2026 13:43</t>
+          <t>02/06/2026 15:03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08/06/2026 13:43</t>
+          <t>02/06/2026 15:03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>09/06/2026 12:33</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0012005-59.2012.8.16.0019</t>
+          <t>0036615-36.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>13/05/2022</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08/06/2026 14:43</t>
+          <t>22/05/2026 10:58</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08/06/2026 14:43</t>
+          <t>22/05/2026 10:58</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09/06/2026 09:53</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0016897-43.2023.8.16.0013</t>
+          <t>0051298-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reintegração ou Readmissão</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>09/06/2026 08:58</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0017829-53.2022.8.16.0017</t>
+          <t>0131308-07.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08/06/2026 13:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08/06/2026 13:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>09/06/2026 12:18</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0018234-64.2023.8.16.0014</t>
+          <t>0009600-24.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>09/06/2026 13:26</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0022746-98.2024.8.16.0000</t>
+          <t>0043186-18.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Classificação de créditos</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>27/05/2026 16:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>27/05/2026 16:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>09/06/2026 08:35</t>
+          <t>18/06/2026 06:03</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0025526-62.2021.8.16.0017</t>
+          <t>0005159-54.2019.8.16.0189</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Preferências e Privilégios Creditórios</t>
+          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>02/06/2026 15:43</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>02/06/2026 15:43</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>09/06/2026 11:00</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0025916-47.2012.8.16.0017</t>
+          <t>0004060-93.2010.8.16.0050</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+          <t>Auxílio por Incapacidade Temporária</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>03/06/2026 16:13</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>03/06/2026 16:13</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>09/06/2026 09:53</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0035445-24.2024.8.16.0000</t>
+          <t>0007962-53.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Intimação | Intimação / Notificação | Indenização por Dano Moral</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>01/06/2026 13:53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>01/06/2026 13:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>09/06/2026 09:48</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0038304-13.2024.8.16.0000</t>
+          <t>0009244-75.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Perdas e Danos</t>
+          <t>Rescisão / Resolução | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>03/06/2026 16:23</t>
+          <t>22/05/2026 13:23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>03/06/2026 16:23</t>
+          <t>22/05/2026 13:23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>09/06/2026 12:25</t>
+          <t>18/06/2026 06:20</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0053017-95.2021.8.16.0000</t>
+          <t>0003261-17.2020.8.16.0174</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Honorários Advocatícios</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>07/11/2022</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>03/06/2026 14:23</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>03/06/2026 14:23</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>09/06/2026 11:49</t>
+          <t>17/06/2026 15:20</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0069567-89.2022.8.16.0014</t>
+          <t>0000772-34.2024.8.16.0055</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>20/05/2026 17:33</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>20/05/2026 17:33</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>09/06/2026 13:19</t>
+          <t>17/06/2026 15:20</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0084220-70.2024.8.16.0000</t>
+          <t>0003530-51.2014.8.16.0179</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito | Acidente de Trânsito</t>
+          <t>Promessa de Compra e Venda | Prescrição e Decadência | Corretagem | Atraso na Entrega do Imóvel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>17/01/2022</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>02/06/2026 14:53</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>02/06/2026 14:53</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>09/06/2026 09:03</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0098664-11.2024.8.16.0000</t>
+          <t>0002519-06.2019.8.16.0019</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>09/06/2026 08:36</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0099517-83.2025.8.16.0000</t>
+          <t>0022283-27.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02/06/2026 15:23</t>
+          <t>20/05/2026 14:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/06/2026 15:23</t>
+          <t>20/05/2026 14:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>09/06/2026 11:43</t>
+          <t>17/06/2026 15:50</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,45 +1899,7988 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0131494-93.2025.8.16.0000</t>
+          <t>0013333-39.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22/10/2024</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>17/06/2026 15:50</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0006907-35.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Previdência privada</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22/05/2024</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:00</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0002649-45.2014.8.16.0124</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>04/12/2024</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>26/05/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>26/05/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:10</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0003017-48.2024.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>03/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>03/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:20</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0041785-52.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>09/06/2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>28/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>28/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:20</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0071507-34.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0000243-05.2022.8.16.0081</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0026334-16.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>17/06/2026 16:50</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0002487-19.2023.8.16.0097</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>09/06/2026 11:07</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>09/06/2026 11:07</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0008525-89.2006.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Compromisso</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:55</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0003085-33.2024.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:10</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0006029-21.2023.8.16.0105</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Roubo Majorado</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>19/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:10</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0000311-95.1995.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Industrial</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>28/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>28/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:11</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0002487-35.2021.8.16.0179</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fornecimento de medicamentos | Fornecimento de medicamentos</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>18/07/2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:11</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0000863-07.2022.8.16.0052</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:12</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0113334-54.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21/05/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>21/05/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0015887-32.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:20</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0010170-10.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0020993-09.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>08/01/2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0012526-07.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:50</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0000869-34.2022.8.16.0110</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>26/05/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>26/05/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:50</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0000936-38.2011.8.16.0060</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:50</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0022746-98.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>03/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>03/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0005083-39.2016.8.16.0123</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22/04/2024</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>20/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0099021-88.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:10</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0004046-67.2021.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pagamento Indevido</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:10</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0000726-45.2023.8.16.0131</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Condomínio em Edifício</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>14/07/2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:21</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0036070-97.2020.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Desconsideração da Personalidade Jurídica</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>02/07/2021</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:40</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0009138-72.2012.8.16.0026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>31/08/2021</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:40</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0030231-62.2019.8.16.0021</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Roubo Majorado</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>12/03/2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>24/04/2025 08:54</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>02/06/2026 12:47</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0015088-72.2014.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>11/04/2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>25/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>25/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:02</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0016083-36.2023.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Limitação de Juros</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>06/05/2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>01/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>01/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:12</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0009827-23.2022.8.16.0170</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:12</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0123907-54.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:40</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0057283-15.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>29/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>29/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:50</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0000844-14.2020.8.16.0038</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Divisão e Demarcação</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>26/01/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>27/05/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>27/05/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:51</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0024646-82.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>10/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>17/06/2026 21:51</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0000679-63.2022.8.16.0048</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Promoção</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>21/09/2023</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:00</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0001182-69.2016.8.16.0024</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>19/05/2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>21/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>21/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:30</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0118728-42.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>25/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>25/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:30</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0004034-22.2024.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Furto Qualificado</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:30</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0000375-09.2022.8.16.0034</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>25/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>25/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:41</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0007390-80.2018.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Indenização Trabalhista</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>02/09/2020</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>09/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>09/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:50</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0075901-50.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Confissão/Composição de Dívida</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>13/08/2024</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>29/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>29/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>17/06/2026 22:50</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0112463-58.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0003565-73.2023.8.16.0024</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:14</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0040432-21.2016.8.16.0021</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:14</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0013575-85.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:14</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0089105-30.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Classificação e/ou Preterição | Anulação e Correção de Provas / Questões</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>28/05/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>28/05/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:32</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0005682-75.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>27/02/2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:40</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0000524-83.2023.8.16.0126</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>29/05/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>29/05/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0014750-24.2022.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ISS/ Imposto sobre Serviços</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0003496-27.2019.8.16.0074</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Espécies de Contratos | Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>17/03/2025</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>29/05/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>29/05/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0017293-88.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>12/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0025380-55.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0052023-33.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>11/08/2023</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:10</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0002140-07.2015.8.16.0116</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Reintegração ou Readmissão</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:30</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0015612-98.2016.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>15/06/2026 12:16</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>15/06/2026 12:16</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>18/06/2026 00:50</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0000192-37.2022.8.16.0099</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Anulação</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>25/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>25/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>18/06/2026 01:00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0003761-91.2024.8.16.0126</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>17/06/2026 08:43</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>17/06/2026 08:43</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>18/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0012927-54.2018.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Previdência privada</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>14/09/2023</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>20/05/2026 19:43</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>20/05/2026 19:43</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>18/06/2026 01:41</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0037437-46.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução | Despejo por Inadimplemento</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>02/06/2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>25/05/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>25/05/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>18/06/2026 01:41</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0003468-89.2019.8.16.0064</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Parceria Agrícola e/ou pecuária</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>10/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>10/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:01</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0000797-55.2023.8.16.0096</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:01</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0005963-31.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:11</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0004556-02.2002.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Depósito</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>29/11/2024</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>10/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:20</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0020425-61.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Antecipação de Tutela / Recebimento como Cautelar</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>29/01/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>26/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>26/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:20</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0003657-60.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>21/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>21/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:30</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0000108-47.2019.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>20/09/2023</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:00</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0046717-35.2012.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>09/04/2025</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:13</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0006192-28.2024.8.16.0117</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Vícios Formais da Sentença</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0082972-35.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0017760-67.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Vícios de Construção</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>18/06/2026 04:23</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0000105-96.2020.8.16.0052</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>14/01/2022</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>18/06/2026 04:30</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0007308-30.2022.8.16.0088</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Adjudicação Compulsória</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>22/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>22/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>18/06/2026 04:51</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0004710-71.2017.8.16.0123</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Violação dos Princípios Administrativos</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>25/01/2024</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>21/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>21/05/2026 18:03</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>18/06/2026 05:12</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0000625-95.2022.8.16.0081</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Transporte de Coisas</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>22/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>22/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>18/06/2026 05:30</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0010773-25.2019.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>28/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>28/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0001386-43.2022.8.16.0141</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Empreitada</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:12</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0000221-11.2021.8.16.0071</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:30</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0007495-27.2009.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>01/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>01/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:30</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0000199-63.2021.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Desacato | Ameaça</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>01/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>01/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:30</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0007959-52.2010.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Condomínio</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>17/02/2023</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>29/05/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>29/05/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:41</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0045337-54.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Anulação e Correção de Provas / Questões</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>24/06/2025</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>20/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>20/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:42</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0040189-91.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Crimes do Sistema Nacional de Armas | Prisão Preventiva</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>19/01/2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>01/06/2026 15:33</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>01/06/2026 15:33</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>09/06/2026 12:27</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Furto Qualificado</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>26/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>26/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:42</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0042451-40.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>11/12/2025</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:00</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0010088-08.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Seguro | Penhora / Depósito/ Avaliação</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>01/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>01/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:11</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>0010197-61.2021.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Protesto Indevido de Título | Contratos Bancários | Nulidade | Extinção do Processo Sem Resolução de Mérito | Litispendência</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:11</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>0003076-06.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:31</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>0028390-19.2024.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Dever de Informação | Direito de Imagem | Oferta e Publicidade | Interpretação / Revisão de Contrato | Irregularidade no atendimento | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:40</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>0009705-96.2023.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Franquia</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>28/05/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>28/05/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:51</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>0000150-04.2017.8.16.0118</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Poluição | Destruição ou Degradação</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:51</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>0011643-60.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:05</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0031752-95.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>03/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>03/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:05</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>0088297-25.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Indenização Trabalhista</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:30</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>0021675-22.2024.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>20/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>20/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:32</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>0041235-52.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cédula Hipotecária</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:41</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>0004254-22.2023.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:51</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>0036866-56.2024.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>13/02/2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:00</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>0029752-81.2015.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>28/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>28/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:00</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>0003717-27.2022.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Furto Qualificado</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>26/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>26/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:00</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>0115802-54.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>09/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>09/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:00</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>0095357-49.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Efeito Suspensivo a Recurso | Assistência Judiciária Gratuita | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>27/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>27/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>0001256-15.2022.8.16.0089</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>0012863-59.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Adulteração de Sinal Identificador de Veículo Automotor | Receptação</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:30</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>0008738-31.2014.8.16.0174</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Interpretação / Revisão de Contrato | Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>19/08/2024</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:13</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:13</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:42</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>0002905-49.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Excesso de prazo para instrução / julgamento</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>27/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>27/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:01</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>0018917-41.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Prisão Preventiva | Estelionato Majorado | Quadrilha ou Bando</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>0001930-24.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Furto Qualificado</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>0008738-15.2022.8.16.0024</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Água e/ou Esgoto | Indenização por Dano Ambiental | Indenização por Dano Moral | Ônus da Prova</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>30/12/1899</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>09/05/2024 21:01</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>25/05/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>4002935-85.2025.8.16.4321</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Pena Privativa de Liberdade | Prisão Domiciliar / Especial</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>28/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:30</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>0020024-69.2022.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:31</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>0128310-66.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:44</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>0001056-42.2015.8.16.0060</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Crime Tentado</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:44</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>0000422-89.2024.8.16.0170</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>19/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>19/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:44</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>0007581-42.2021.8.16.0056</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Vícios de Construção</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:51</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>0006055-31.2019.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Planos de Saúde</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>19/02/2021</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:51</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>0110583-94.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:11</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>0001206-21.2008.8.16.0043</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Fato Atípico</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:23</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>0004318-36.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Despejo por Inadimplemento</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:23</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>0000612-02.2023.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:23</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>0028245-63.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:30</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>0014115-97.2022.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:31</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>0051548-43.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>18/12/2024</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:31</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>0027393-27.2020.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>28/05/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>28/05/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:51</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>0018400-41.2023.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Esbulho / Turbação / Ameaça</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>15/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>15/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:53</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>0001389-27.2025.8.16.0162</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:53</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>0066442-45.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Bem de Família (Voluntário)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:54</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>0053341-80.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Despesas Condominiais</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>08/04/2025</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>27/05/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>16/06/2026 21:02</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>0026896-88.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Prova Oral</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>09/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>09/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>16/06/2026 21:30</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>0001075-40.2022.8.16.0145</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Desobediência</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>28/09/2023</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>03/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>03/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>16/06/2026 21:40</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>0085690-73.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>19/11/2024</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>16/06/2026 21:40</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>0061932-91.2021.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>27/03/2025</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>16/06/2026 21:41</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>0005931-60.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Decadência/Prescrição | Promoção / Ascensão</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>06/09/2024</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>22/05/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>22/05/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>16/06/2026 22:22</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>0054268-12.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>16/06/2026 22:40</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>5000051-75.2018.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias | Parcelamento | ICMS / Incidência Sobre o Ativo Fixo</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>04/07/2021</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>19/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>19/05/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>16/06/2026 22:42</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>0006515-35.2020.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>09/10/2023</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>20/05/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>20/05/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>16/06/2026 22:42</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>0108975-95.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural | Cessão de Crédito</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>16/06/2026 22:51</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>0001126-47.2014.8.16.0140</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>21/05/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>21/05/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>16/06/2026 23:14</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>0003259-74.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>16/06/2026 23:40</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>0055779-45.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>16/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>0045074-56.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>09/11/2023</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>0083330-68.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Imissão</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>04/09/2024</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>0010693-85.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Perdas e Danos</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>04/09/2024</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>20/05/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>20/05/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>0021100-55.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>0109367-35.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>27/11/2024</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:12</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>0001015-31.2023.8.16.0081</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>02/07/2024</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:12</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>0000841-39.2017.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Fato Gerador/Incidência | Honorários Advocatícios | IPTU/ Imposto Predial e Territorial Urbano</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>10/07/2024</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:12</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>0000478-26.2022.8.16.0160</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:21</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>0002958-19.2022.8.16.0049</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>26/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>26/05/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:30</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>0002424-23.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Servidão Administrativa | Efeito Suspensivo a Recurso</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:30</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>0007643-78.2006.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Despejo por Inadimplemento | Causas Supervenientes à Sentença</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>05/12/2023</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>29/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>29/05/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:42</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>0015514-75.2020.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>14/12/2023</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>29/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>29/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:42</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>0016824-42.2021.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>21/02/2025</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>17/06/2026 00:50</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>0003490-45.2019.8.16.0098</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Preconceituosa</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>08/06/2026 11:27</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>08/06/2026 11:27</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:02</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>0005542-20.2019.8.16.0193</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>20/11/2023</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>29/05/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>29/05/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:10</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>0001544-72.2020.8.16.0043</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Confissão/Composição de Dívida | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>07/12/2023</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>28/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>28/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:10</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>0006310-33.2022.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Propriedade Intelectual / Industrial</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>04/09/2024</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>21/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>21/05/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:10</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>0077125-23.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Bens Públicos | Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>19/06/2024</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>28/05/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>28/05/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:20</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>0129384-58.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Títulos de Crédito | Nulidade</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>0002938-90.2023.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>12/02/2026</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>19/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>0025126-26.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:40</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>0034729-86.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>27/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:41</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>0005666-18.2024.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Roubo Majorado</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:41</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>0016432-10.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Espécies de Contratos | Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>23/01/2024</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>29/05/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>29/05/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>17/06/2026 01:50</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>0006114-45.2017.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>21/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>21/05/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>17/06/2026 02:00</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>0009919-46.2022.8.16.0058</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>11/06/2025</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>17/06/2026 02:10</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>0002960-81.2022.8.16.0083</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>27/05/2026 14:25</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>27/05/2026 14:25</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>17/06/2026 02:10</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>0007014-41.2023.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>17/06/2026 02:20</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>0010929-71.2023.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Tratamento médico-hospitalar</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>17/06/2026 02:30</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000105-96.2020.8.16.0052</t>
+          <t>0077248-55.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14/01/2022</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>26/05/2026 16:33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>26/05/2026 16:33</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18/06/2026 04:30</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000199-63.2021.8.16.0196</t>
+          <t>0018234-64.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Desacato | Ameaça</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01/06/2026 16:03</t>
+          <t>01/06/2026 14:33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/06/2026 16:03</t>
+          <t>01/06/2026 14:33</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16/06/2026 15:30</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000221-11.2021.8.16.0071</t>
+          <t>0034028-70.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11/06/2026 14:03</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11/06/2026 14:03</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16/06/2026 15:30</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000293-21.2012.8.16.0133</t>
+          <t>0001222-82.2021.8.16.0054</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seguro | Compra e Venda</t>
+          <t>Erro Médico | Erro Médico | COVID-19 | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24/02/2023</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10/06/2026 16:53</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10/06/2026 16:53</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17/06/2026 08:23</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000317-11.2021.8.16.0173</t>
+          <t>0018379-70.2021.8.16.0021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça | Servidão</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22/09/2025</t>
+          <t>28/06/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>21/05/2026 15:53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>21/05/2026 15:53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>17/06/2026 10:30</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000431-64.2024.8.16.0101</t>
+          <t>0049261-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>05/09/2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>26/05/2026 14:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>26/05/2026 14:33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18/06/2026 08:50</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000556-60.2025.8.16.0145</t>
+          <t>0001806-23.2018.8.16.0033</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>09/02/2023</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01/06/2026 17:23</t>
+          <t>20/05/2026 15:53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/06/2026 17:23</t>
+          <t>20/05/2026 15:53</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15/06/2026 23:33</t>
+          <t>18/06/2026 08:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000615-20.2024.8.16.0004</t>
+          <t>0001444-16.2001.8.16.0001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Enquadramento | Reajustes de Remuneração, Proventos ou Pensão</t>
+          <t>Usucapião Ordinária</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>07/05/2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>21/05/2026 15:03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>21/05/2026 15:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17/06/2026 05:30</t>
+          <t>18/06/2026 08:11</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000679-63.2022.8.16.0048</t>
+          <t>0002350-52.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Promoção</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 08:21</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0001213-13.2021.8.16.0025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>21/03/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>09/06/2026 19:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>09/06/2026 19:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>18/06/2026 08:30</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0000431-64.2024.8.16.0101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>03/06/2026 13:13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>03/06/2026 13:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>18/06/2026 08:50</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001213-13.2021.8.16.0025</t>
+          <t>0003010-91.2018.8.16.0069</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21/03/2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>09/06/2026 19:53</t>
+          <t>25/05/2026 18:13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>09/06/2026 19:53</t>
+          <t>25/05/2026 18:13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18/06/2026 08:30</t>
+          <t>18/06/2026 08:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001444-85.2024.8.16.0170</t>
+          <t>0009888-66.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
+          <t>Aquisição</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/08/2024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16/06/2026 14:43</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16/06/2026 14:43</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17/06/2026 11:32</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001477-87.2017.8.16.0116</t>
+          <t>0039237-70.2017.8.16.0019</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>09/06/2026 17:43</t>
+          <t>21/05/2026 19:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>09/06/2026 17:43</t>
+          <t>21/05/2026 19:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17/06/2026 06:30</t>
+          <t>18/06/2026 07:30</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001783-48.2018.8.16.0172</t>
+          <t>0036615-36.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>13/05/2022</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10/06/2026 11:49</t>
+          <t>22/05/2026 10:58</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10/06/2026 11:49</t>
+          <t>22/05/2026 10:58</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17/06/2026 11:41</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001971-06.2018.8.16.0119</t>
+          <t>0051298-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08/06/2026 14:53</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>08/06/2026 14:53</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17/06/2026 11:41</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0002140-07.2015.8.16.0116</t>
+          <t>0131308-07.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reintegração ou Readmissão</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/06/2026 00:30</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002350-52.2009.8.16.0089</t>
+          <t>0009600-24.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/06/2026 08:21</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002487-19.2023.8.16.0097</t>
+          <t>0043186-18.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Classificação de créditos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>27/05/2026 16:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>27/05/2026 16:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17/06/2026 17:00</t>
+          <t>18/06/2026 06:03</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002549-70.2023.8.16.0061</t>
+          <t>0005159-54.2019.8.16.0189</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17/06/2026 09:30</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002680-95.2022.8.16.0185</t>
+          <t>0004060-93.2010.8.16.0050</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Auxílio por Incapacidade Temporária</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>09/06/2026 16:23</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>09/06/2026 16:23</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17/06/2026 09:30</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002816-47.2021.8.16.0179</t>
+          <t>0007962-53.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ICMS / Incidência Sobre o Ativo Fixo</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10/06/2026 16:53</t>
+          <t>01/06/2026 13:53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10/06/2026 16:53</t>
+          <t>01/06/2026 13:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17/06/2026 14:11</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0003017-48.2024.8.16.0045</t>
+          <t>0009244-75.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Rescisão / Resolução | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>22/05/2026 13:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>22/05/2026 13:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>18/06/2026 06:20</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0003085-33.2024.8.16.0001</t>
+          <t>0003261-17.2020.8.16.0174</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17/06/2026 18:10</t>
+          <t>17/06/2026 15:20</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003261-17.2020.8.16.0174</t>
+          <t>0000772-34.2024.8.16.0055</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>20/05/2026 17:33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>20/05/2026 17:33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003468-89.2019.8.16.0064</t>
+          <t>0003530-51.2014.8.16.0179</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Promessa de Compra e Venda | Prescrição e Decadência | Corretagem | Atraso na Entrega do Imóvel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>17/01/2022</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18/06/2026 02:01</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0002519-06.2019.8.16.0019</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004120-58.2024.8.16.0088</t>
+          <t>0022283-27.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Parcelamento do solo urbano</t>
+          <t>Espécies de Contratos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>20/05/2026 14:03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>20/05/2026 14:03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17/06/2026 05:51</t>
+          <t>17/06/2026 15:50</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0004156-44.2019.8.16.0034</t>
+          <t>0013333-39.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Enriquecimento sem Causa</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>22/10/2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16/06/2026 20:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>16/06/2026 20:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17/06/2026 14:11</t>
+          <t>17/06/2026 15:50</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004373-31.2009.8.16.0069</t>
+          <t>0006907-35.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>16/12/2014</t>
+          <t>22/05/2024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>20/05/2026 13:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>17/06/2026 06:50</t>
+          <t>17/06/2026 16:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004554-69.2014.8.16.0000</t>
+          <t>0002649-45.2014.8.16.0124</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Despesas Condominiais | Propriedade</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11/10/2015</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11/06/2026 13:33</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11/06/2026 13:33</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17/06/2026 08:23</t>
+          <t>17/06/2026 16:10</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004556-02.2002.8.16.0019</t>
+          <t>0003017-48.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depósito</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10/06/2026 13:33</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10/06/2026 13:33</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18/06/2026 02:20</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0004654-85.2017.8.16.0075</t>
+          <t>0041785-52.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17/06/2026 04:30</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0004723-72.2022.8.16.0001</t>
+          <t>0071507-34.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17/06/2026 09:10</t>
+          <t>17/06/2026 16:33</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0005682-75.2024.8.16.0000</t>
+          <t>0000243-05.2022.8.16.0081</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>17/06/2026 23:40</t>
+          <t>17/06/2026 16:40</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0006192-28.2024.8.16.0117</t>
+          <t>0026334-16.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vícios Formais da Sentença</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02/06/2026 14:33</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>02/06/2026 14:33</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/06/2026 03:30</t>
+          <t>17/06/2026 16:50</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0006558-86.2022.8.16.0004</t>
+          <t>0002487-19.2023.8.16.0097</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias | Alíquota</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02/06/2026 16:05</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>02/06/2026 16:05</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17/06/2026 09:30</t>
+          <t>17/06/2026 17:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0007014-41.2023.8.16.0185</t>
+          <t>0003085-33.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17/06/2026 02:20</t>
+          <t>17/06/2026 18:10</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0007390-80.2018.8.16.0030</t>
+          <t>0000311-95.1995.8.16.0017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indenização Trabalhista</t>
+          <t>Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02/09/2020</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>17/06/2026 22:50</t>
+          <t>17/06/2026 18:11</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0007495-27.2009.8.16.0045</t>
+          <t>0002487-35.2021.8.16.0179</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Fornecimento de medicamentos | Fornecimento de medicamentos</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01/06/2026 15:53</t>
+          <t>21/05/2026 16:13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01/06/2026 15:53</t>
+          <t>21/05/2026 16:13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>16/06/2026 15:30</t>
+          <t>17/06/2026 18:11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0007529-95.2013.8.16.0001</t>
+          <t>0000863-07.2022.8.16.0052</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>03/06/2026 15:13</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>03/06/2026 15:13</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17/06/2026 05:30</t>
+          <t>17/06/2026 18:12</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0007555-05.2023.8.16.0014</t>
+          <t>0113334-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>21/05/2026 17:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>21/05/2026 17:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>17/06/2026 09:30</t>
+          <t>17/06/2026 18:13</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0007831-95.2021.8.16.0017</t>
+          <t>0015887-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2525,22 +2525,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>17/06/2026 04:11</t>
+          <t>17/06/2026 18:20</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0007962-53.2023.8.16.0194</t>
+          <t>0010170-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>17/06/2026 19:11</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0008663-54.2015.8.16.0045</t>
+          <t>0020993-09.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10/06/2026 11:40</t>
+          <t>21/05/2026 15:23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10/06/2026 11:40</t>
+          <t>21/05/2026 15:23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17/06/2026 12:51</t>
+          <t>17/06/2026 19:11</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0009778-70.2023.8.16.0194</t>
+          <t>0012526-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>17/06/2026 07:33</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0009888-66.2023.8.16.0001</t>
+          <t>0000869-34.2022.8.16.0110</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Aquisição</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>28/08/2024</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18/06/2026 07:20</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0010088-08.2025.8.16.0000</t>
+          <t>0000936-38.2011.8.16.0060</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seguro | Penhora / Depósito/ Avaliação</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/06/2026 14:23</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01/06/2026 14:23</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>16/06/2026 16:11</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0010170-10.2023.8.16.0000</t>
+          <t>0022746-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>17/06/2026 20:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0010197-61.2021.8.16.0194</t>
+          <t>0005083-39.2016.8.16.0123</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Protesto Indevido de Título | Contratos Bancários | Nulidade | Extinção do Processo Sem Resolução de Mérito | Litispendência</t>
+          <t>Perdas e Danos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>22/04/2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>20/05/2026 18:23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>20/05/2026 18:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>16/06/2026 16:11</t>
+          <t>17/06/2026 20:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0010287-32.2022.8.16.0001</t>
+          <t>0099021-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pagamento em Consignação</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17/06/2026 06:00</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0004046-67.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Pagamento Indevido</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0012558-24.2016.8.16.0001</t>
+          <t>0000726-45.2023.8.16.0131</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Condomínio em Edifício</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/07/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02/06/2026 16:23</t>
+          <t>21/05/2026 16:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>02/06/2026 16:23</t>
+          <t>21/05/2026 16:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17/06/2026 02:50</t>
+          <t>17/06/2026 20:21</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0013226-22.2021.8.16.0000</t>
+          <t>0036070-97.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>07/10/2022</t>
+          <t>02/07/2021</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17/06/2026 05:40</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0013333-39.2016.8.16.0001</t>
+          <t>0009138-72.2012.8.16.0026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22/10/2024</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17/06/2026 15:50</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0013575-85.2022.8.16.0001</t>
+          <t>0030231-62.2019.8.16.0021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>24/04/2025 08:54</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>02/06/2026 12:47</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>17/06/2026 21:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0014353-53.2025.8.16.0000</t>
+          <t>0015088-72.2014.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08/06/2026 14:53</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>08/06/2026 14:53</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>17/06/2026 14:40</t>
+          <t>17/06/2026 21:02</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0015612-98.2016.8.16.0000</t>
+          <t>0016083-36.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/06/2026 00:50</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0015769-90.2020.8.16.0013</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17/06/2026 10:10</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0123907-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>17/06/2026 21:40</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0016083-36.2023.8.16.0173</t>
+          <t>0057283-15.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>17/06/2026 21:50</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0017293-88.2025.8.16.0000</t>
+          <t>0000844-14.2020.8.16.0038</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Divisão e Demarcação</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/06/2026 00:00</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0017760-67.2025.8.16.0000</t>
+          <t>0024646-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/06/2026 04:23</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0018234-64.2023.8.16.0014</t>
+          <t>0000679-63.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Promoção</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0022746-98.2024.8.16.0000</t>
+          <t>0001182-69.2016.8.16.0024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>19/05/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>21/05/2026 18:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>21/05/2026 18:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>17/06/2026 22:30</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0024646-82.2025.8.16.0000</t>
+          <t>0118728-42.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>25/05/2026 14:03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>25/05/2026 14:03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>17/06/2026 22:30</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0026334-16.2024.8.16.0000</t>
+          <t>0004034-22.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>27/05/2026 13:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>27/05/2026 13:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17/06/2026 16:50</t>
+          <t>17/06/2026 22:30</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0026871-77.2022.8.16.0001</t>
+          <t>0000375-09.2022.8.16.0034</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11/06/2026 13:23</t>
+          <t>25/05/2026 13:43</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11/06/2026 13:23</t>
+          <t>25/05/2026 13:43</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>15/06/2026 23:33</t>
+          <t>17/06/2026 22:41</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0026929-78.2025.8.16.0000</t>
+          <t>0007390-80.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Indenização Trabalhista</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>02/09/2020</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17/06/2026 11:32</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0028390-19.2024.8.16.0001</t>
+          <t>0075901-50.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dever de Informação | Direito de Imagem | Oferta e Publicidade | Interpretação / Revisão de Contrato | Irregularidade no atendimento | Indenização por Dano Material</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>13/08/2024</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>29/05/2026 16:13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>29/05/2026 16:13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>16/06/2026 16:40</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0030231-62.2019.8.16.0021</t>
+          <t>0112463-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>24/04/2025 08:54</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>02/06/2026 12:47</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17/06/2026 21:00</t>
+          <t>17/06/2026 23:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0031752-95.2025.8.16.0000</t>
+          <t>0003565-73.2023.8.16.0024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>03/06/2026 13:03</t>
+          <t>28/05/2026 17:23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>03/06/2026 13:03</t>
+          <t>28/05/2026 17:23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16/06/2026 17:05</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0034028-70.2023.8.16.0000</t>
+          <t>0040432-21.2016.8.16.0021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0036070-97.2020.8.16.0000</t>
+          <t>0013575-85.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>02/07/2021</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0039522-68.2023.8.16.0014</t>
+          <t>0089105-30.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cobrança | Honorários Advocatícios</t>
+          <t>Classificação e/ou Preterição | Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>28/05/2026 14:53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>28/05/2026 14:53</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/06/2026 06:00</t>
+          <t>17/06/2026 23:32</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0042491-30.2025.8.16.0000</t>
+          <t>0005682-75.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01/06/2026 13:33</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>01/06/2026 13:33</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/06/2026 05:30</t>
+          <t>17/06/2026 23:40</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0046717-35.2012.8.16.0000</t>
+          <t>0000524-83.2023.8.16.0126</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>29/05/2026 16:43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>29/05/2026 16:43</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/06/2026 03:13</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0052023-33.2022.8.16.0000</t>
+          <t>0014750-24.2022.8.16.0031</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11/08/2023</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>21/05/2026 15:43</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>21/05/2026 15:43</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/06/2026 00:10</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0052750-84.2025.8.16.0000</t>
+          <t>0003496-27.2019.8.16.0074</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Espécies de Contratos | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>17/03/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>11/06/2026 15:03</t>
+          <t>29/05/2026 13:23</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11/06/2026 15:03</t>
+          <t>29/05/2026 13:23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17/06/2026 13:20</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0056160-87.2024.8.16.0000</t>
+          <t>0017293-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>15/06/2026 15:43</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>15/06/2026 15:43</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17/06/2026 15:00</t>
+          <t>18/06/2026 00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0057438-89.2025.8.16.0000</t>
+          <t>0025380-55.2020.8.16.0017</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Divisão e Demarcação | Multa Cominatória / Astreintes | Indenização por Dano Moral</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16/06/2026 18:53</t>
+          <t>22/05/2026 13:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>16/06/2026 18:53</t>
+          <t>22/05/2026 13:33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>17/06/2026 02:50</t>
+          <t>18/06/2026 00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0059962-93.2024.8.16.0000</t>
+          <t>0052023-33.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Diligências</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>11/08/2023</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>17/06/2026 09:41</t>
+          <t>18/06/2026 00:10</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0060779-60.2024.8.16.0000</t>
+          <t>0002140-07.2015.8.16.0116</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Responsabilidade dos sócios e administradores | Antecipação de Tutela / Recebimento como Cautelar</t>
+          <t>Reintegração ou Readmissão</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>17/06/2026 05:18</t>
+          <t>18/06/2026 00:30</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,37 +4437,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0079213-63.2025.8.16.0000</t>
+          <t>0015612-98.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Perdimento de Bens</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12/06/2026 14:03</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>12/06/2026 14:03</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>17/06/2026 11:51</t>
+          <t>18/06/2026 00:50</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0088297-25.2024.8.16.0000</t>
+          <t>0000192-37.2022.8.16.0099</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indenização Trabalhista</t>
+          <t>Anulação</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>25/05/2026 13:13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>25/05/2026 13:13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>16/06/2026 17:30</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0090734-39.2024.8.16.0000</t>
+          <t>0003761-91.2024.8.16.0126</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Incorporação Imobiliária | Enriquecimento sem Causa | Confissão/Composição de Dívida</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>17/06/2026 05:22</t>
+          <t>18/06/2026 01:30</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0093845-31.2024.8.16.0000</t>
+          <t>0012927-54.2018.8.16.0031</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>14/09/2023</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>20/05/2026 19:43</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>20/05/2026 19:43</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>17/06/2026 12:30</t>
+          <t>18/06/2026 01:41</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0099021-88.2024.8.16.0000</t>
+          <t>0037437-46.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Rescisão / Resolução | Despejo por Inadimplemento</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>25/05/2026 15:13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>25/05/2026 15:13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>18/06/2026 01:41</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0112463-58.2023.8.16.0000</t>
+          <t>0003468-89.2019.8.16.0064</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0118099-68.2024.8.16.0000</t>
+          <t>0000797-55.2023.8.16.0096</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Cerceamento de Defesa | Aplicação da Pena</t>
+          <t>Promessa de Compra e Venda</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>09/06/2026 18:53</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>09/06/2026 18:53</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>17/06/2026 05:22</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0131308-07.2024.8.16.0000</t>
+          <t>0005963-31.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>20/05/2026 14:13</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>20/05/2026 14:13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>18/06/2026 02:11</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0133988-28.2025.8.16.0000</t>
+          <t>0004556-02.2002.8.16.0019</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prisão Preventiva</t>
+          <t>Depósito</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16/06/2026 15:13</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>16/06/2026 15:13</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>17/06/2026 02:50</t>
+          <t>18/06/2026 02:20</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4003768-06.2025.8.16.4321</t>
+          <t>0020425-61.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
+          <t>Promessa de Compra e Venda | Antecipação de Tutela / Recebimento como Cautelar</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>29/01/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>26/05/2026 14:03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>26/05/2026 14:03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>17/06/2026 03:40</t>
+          <t>18/06/2026 02:20</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4899,6 +4899,288 @@
         </is>
       </c>
       <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0003657-60.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>22/10/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>21/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>21/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:30</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0000108-47.2019.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>20/09/2023</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>28/05/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:00</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0046717-35.2012.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>09/04/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:13</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0006192-28.2024.8.16.0117</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Vícios Formais da Sentença</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0082972-35.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>18/06/2026 03:30</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0017760-67.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Vícios de Construção</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>18/06/2026 04:23</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0077248-55.2022.8.16.0000</t>
+          <t>0000243-05.2022.8.16.0081</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:33</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:33</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18/06/2026 09:00</t>
+          <t>17/06/2026 16:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0018234-64.2023.8.16.0014</t>
+          <t>0000311-95.1995.8.16.0017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>17/06/2026 18:11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0034028-70.2023.8.16.0000</t>
+          <t>0000431-64.2024.8.16.0101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>03/06/2026 13:13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>03/06/2026 13:13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>18/06/2026 08:50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0001222-82.2021.8.16.0054</t>
+          <t>0000478-26.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico | COVID-19 | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>17/06/2026 00:21</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0018379-70.2021.8.16.0021</t>
+          <t>0000841-39.2017.8.16.0014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Fato Gerador/Incidência | Honorários Advocatícios | IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28/06/2024</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21/05/2026 15:53</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21/05/2026 15:53</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18/06/2026 09:00</t>
+          <t>17/06/2026 00:12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0049261-10.2023.8.16.0000</t>
+          <t>0000844-14.2020.8.16.0038</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Divisão e Demarcação</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26/05/2026 14:33</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26/05/2026 14:33</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18/06/2026 09:00</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0001806-23.2018.8.16.0033</t>
+          <t>0000863-07.2022.8.16.0052</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>09/02/2023</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20/05/2026 15:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20/05/2026 15:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18/06/2026 08:00</t>
+          <t>17/06/2026 18:12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001444-16.2001.8.16.0001</t>
+          <t>0000869-34.2022.8.16.0110</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Usucapião Ordinária</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>07/05/2024</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21/05/2026 15:03</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21/05/2026 15:03</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18/06/2026 08:11</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,12 +865,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0002350-52.2009.8.16.0089</t>
+          <t>0000936-38.2011.8.16.0060</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18/06/2026 08:21</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -959,37 +959,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000431-64.2024.8.16.0101</t>
+          <t>0001222-82.2021.8.16.0054</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Erro Médico | Erro Médico | COVID-19 | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18/06/2026 08:50</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,37 +1006,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0003010-91.2018.8.16.0069</t>
+          <t>0001544-72.2020.8.16.0043</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Confissão/Composição de Dívida | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>07/12/2023</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25/05/2026 18:13</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25/05/2026 18:13</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18/06/2026 08:00</t>
+          <t>17/06/2026 01:10</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0009888-66.2023.8.16.0001</t>
+          <t>0001689-46.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aquisição</t>
+          <t>Indenização por Dano Material | Pagamento com Sub-rogação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28/08/2024</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>02/06/2026 15:03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>02/06/2026 15:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0039237-70.2017.8.16.0019</t>
+          <t>0002350-52.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21/05/2026 19:33</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21/05/2026 19:33</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18/06/2026 07:30</t>
+          <t>18/06/2026 08:21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001689-46.2023.8.16.0004</t>
+          <t>0002424-23.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Pagamento com Sub-rogação</t>
+          <t>Servidão Administrativa | Efeito Suspensivo a Recurso</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02/06/2026 15:03</t>
+          <t>12/06/2026 14:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02/06/2026 15:03</t>
+          <t>12/06/2026 14:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18/06/2026 07:20</t>
+          <t>17/06/2026 00:30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0036615-36.2021.8.16.0000</t>
+          <t>0002487-19.2023.8.16.0097</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13/05/2022</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22/05/2026 10:58</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22/05/2026 10:58</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18/06/2026 07:20</t>
+          <t>17/06/2026 17:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0051298-73.2024.8.16.0000</t>
+          <t>0002519-06.2019.8.16.0019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29/05/2026 18:13</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29/05/2026 18:13</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0131308-07.2024.8.16.0000</t>
+          <t>0002649-45.2014.8.16.0124</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>17/06/2026 16:10</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0009600-24.2023.8.16.0194</t>
+          <t>0002958-19.2022.8.16.0049</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20/05/2026 13:23</t>
+          <t>26/05/2026 15:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20/05/2026 13:23</t>
+          <t>26/05/2026 15:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>17/06/2026 00:30</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0043186-18.2024.8.16.0000</t>
+          <t>0002960-81.2022.8.16.0083</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Classificação de créditos</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27/05/2026 16:13</t>
+          <t>27/05/2026 14:25</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27/05/2026 16:13</t>
+          <t>27/05/2026 14:25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18/06/2026 06:03</t>
+          <t>17/06/2026 02:10</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0005159-54.2019.8.16.0189</t>
+          <t>0003010-91.2018.8.16.0069</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17/06/2026 14:53</t>
+          <t>25/05/2026 18:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17/06/2026 14:53</t>
+          <t>25/05/2026 18:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>18/06/2026 08:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0004060-93.2010.8.16.0050</t>
+          <t>0003017-48.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auxílio por Incapacidade Temporária</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20/05/2026 13:23</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20/05/2026 13:23</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0007962-53.2023.8.16.0194</t>
+          <t>0003085-33.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1538,22 +1538,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>17/06/2026 18:10</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0009244-75.2023.8.16.0017</t>
+          <t>0003259-74.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22/05/2026 13:23</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>22/05/2026 13:23</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18/06/2026 06:20</t>
+          <t>16/06/2026 23:40</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0000772-34.2024.8.16.0055</t>
+          <t>0003490-45.2019.8.16.0098</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20/05/2026 17:33</t>
+          <t>08/06/2026 11:27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20/05/2026 17:33</t>
+          <t>08/06/2026 11:27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17/06/2026 15:20</t>
+          <t>17/06/2026 01:02</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0002519-06.2019.8.16.0019</t>
+          <t>0004046-67.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Pagamento Indevido</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29/05/2026 13:53</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29/05/2026 13:53</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17/06/2026 15:30</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022283-27.2022.8.16.0001</t>
+          <t>0004654-85.2017.8.16.0075</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Espécies de Contratos</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20/05/2026 14:03</t>
+          <t>10/06/2026 15:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20/05/2026 14:03</t>
+          <t>10/06/2026 15:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17/06/2026 15:50</t>
+          <t>17/06/2026 04:30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0013333-39.2016.8.16.0001</t>
+          <t>0005159-54.2019.8.16.0189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22/10/2024</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17/06/2026 15:50</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0006907-35.2021.8.16.0001</t>
+          <t>0005542-20.2019.8.16.0193</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22/05/2024</t>
+          <t>20/11/2023</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20/05/2026 13:23</t>
+          <t>29/05/2026 14:33</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20/05/2026 13:23</t>
+          <t>29/05/2026 14:33</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>17/06/2026 16:00</t>
+          <t>17/06/2026 01:10</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0002649-45.2014.8.16.0124</t>
+          <t>0005666-18.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>15/06/2026 16:33</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>15/06/2026 16:33</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17/06/2026 16:10</t>
+          <t>17/06/2026 01:41</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0003017-48.2024.8.16.0045</t>
+          <t>0007014-41.2023.8.16.0185</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>17/06/2026 02:20</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0041785-52.2022.8.16.0000</t>
+          <t>0007643-78.2006.8.16.0001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Despejo por Inadimplemento | Causas Supervenientes à Sentença</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>05/12/2023</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>29/05/2026 18:23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>29/05/2026 18:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>17/06/2026 00:42</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0071507-34.2022.8.16.0000</t>
+          <t>0007831-95.2021.8.16.0017</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28/05/2026 17:43</t>
+          <t>12/06/2026 13:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>28/05/2026 17:43</t>
+          <t>12/06/2026 13:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17/06/2026 16:33</t>
+          <t>17/06/2026 04:11</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0000243-05.2022.8.16.0081</t>
+          <t>0007962-53.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>23/07/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>01/06/2026 13:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>01/06/2026 13:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>17/06/2026 16:40</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0026334-16.2024.8.16.0000</t>
+          <t>0008125-21.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Prova Subjetiva | Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>28/05/2026 17:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>28/05/2026 17:13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17/06/2026 16:50</t>
+          <t>17/06/2026 05:18</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0002487-19.2023.8.16.0097</t>
+          <t>0009138-72.2012.8.16.0026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17/06/2026 17:00</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0003085-33.2024.8.16.0001</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17/06/2026 18:10</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0000311-95.1995.8.16.0017</t>
+          <t>0009888-66.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Industrial</t>
+          <t>Aquisição</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>28/08/2024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>17/06/2026 18:11</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0002487-35.2021.8.16.0179</t>
+          <t>0010170-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fornecimento de medicamentos | Fornecimento de medicamentos</t>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21/05/2026 16:13</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>21/05/2026 16:13</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17/06/2026 18:11</t>
+          <t>17/06/2026 19:11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0011157-95.2012.8.16.0173</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Dissolução</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>25/05/2026 12:11</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>25/05/2026 12:11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>17/06/2026 04:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0113334-54.2024.8.16.0000</t>
+          <t>0012526-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21/05/2026 17:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21/05/2026 17:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>17/06/2026 18:13</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0012558-24.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>02/06/2026 16:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>02/06/2026 16:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>17/06/2026 02:50</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0010170-10.2023.8.16.0000</t>
+          <t>0013333-39.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>22/10/2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>17/06/2026 15:50</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0020993-09.2024.8.16.0000</t>
+          <t>0015088-72.2014.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21/05/2026 15:23</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21/05/2026 15:23</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>17/06/2026 21:02</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0015514-75.2020.8.16.0129</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Cédula de Crédito Bancário | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>14/12/2023</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>29/05/2026 13:43</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>29/05/2026 13:43</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>17/06/2026 00:42</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0000869-34.2022.8.16.0110</t>
+          <t>0015887-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26/05/2026 17:43</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26/05/2026 17:43</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>17/06/2026 18:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0016083-36.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0022746-98.2024.8.16.0000</t>
+          <t>0016432-10.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Espécies de Contratos | Contratos Bancários</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>23/01/2024</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>29/05/2026 15:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>29/05/2026 15:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>17/06/2026 01:50</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0005083-39.2016.8.16.0123</t>
+          <t>0016824-42.2021.8.16.0013</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Perdas e Danos</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22/04/2024</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20/05/2026 18:23</t>
+          <t>15/06/2026 16:13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>20/05/2026 18:23</t>
+          <t>15/06/2026 16:13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>17/06/2026 00:50</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0099021-88.2024.8.16.0000</t>
+          <t>0018234-64.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>01/06/2026 14:33</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>01/06/2026 14:33</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0021100-55.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>16/06/2026 13:53</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>16/06/2026 13:53</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>17/06/2026 00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0000726-45.2023.8.16.0131</t>
+          <t>0022746-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Condomínio em Edifício</t>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14/07/2025</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21/05/2026 16:53</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>21/05/2026 16:53</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17/06/2026 20:21</t>
+          <t>17/06/2026 20:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0036070-97.2020.8.16.0000</t>
+          <t>0023839-67.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Suspensão | Crimes contra o Meio Ambiente e o Patrimônio Genético</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02/07/2021</t>
+          <t>15/08/2022</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>28/05/2026 15:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>28/05/2026 15:43</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>17/06/2026 05:18</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0009138-72.2012.8.16.0026</t>
+          <t>0024646-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0030231-62.2019.8.16.0021</t>
+          <t>0026334-16.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>24/04/2025 08:54</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/06/2026 12:47</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17/06/2026 21:00</t>
+          <t>17/06/2026 16:50</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0015088-72.2014.8.16.0000</t>
+          <t>0030231-62.2019.8.16.0021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>24/04/2025 08:54</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>02/06/2026 12:47</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>17/06/2026 21:02</t>
+          <t>17/06/2026 21:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0016083-36.2023.8.16.0173</t>
+          <t>0034028-70.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0009827-23.2022.8.16.0170</t>
+          <t>0034729-86.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>17/06/2026 01:41</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0123907-54.2024.8.16.0000</t>
+          <t>0036070-97.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>02/07/2021</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27/05/2026 15:33</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>27/05/2026 15:33</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17/06/2026 21:40</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0057283-15.2023.8.16.0014</t>
+          <t>0041785-52.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29/05/2026 18:03</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>29/05/2026 18:03</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17/06/2026 21:50</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0000844-14.2020.8.16.0038</t>
+          <t>0043186-18.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Divisão e Demarcação</t>
+          <t>Classificação de créditos</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>27/05/2026 16:13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>27/05/2026 16:13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>18/06/2026 06:03</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0024646-82.2025.8.16.0000</t>
+          <t>0049261-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/09/2024</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>26/05/2026 14:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>26/05/2026 14:33</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0000679-63.2022.8.16.0048</t>
+          <t>0051298-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Promoção</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0001182-69.2016.8.16.0024</t>
+          <t>0054268-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21/05/2026 18:23</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>21/05/2026 18:23</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>17/06/2026 22:30</t>
+          <t>16/06/2026 22:40</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0118728-42.2024.8.16.0000</t>
+          <t>0055779-45.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>25/05/2026 14:03</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>25/05/2026 14:03</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17/06/2026 22:30</t>
+          <t>16/06/2026 23:50</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0004034-22.2024.8.16.0045</t>
+          <t>0056809-52.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>27/05/2026 13:03</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>27/05/2026 13:03</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17/06/2026 22:30</t>
+          <t>17/06/2026 03:01</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0000375-09.2022.8.16.0034</t>
+          <t>0057283-15.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>25/05/2026 13:43</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25/05/2026 13:43</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17/06/2026 22:41</t>
+          <t>17/06/2026 21:50</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0007390-80.2018.8.16.0030</t>
+          <t>0057438-89.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indenização Trabalhista</t>
+          <t>Divisão e Demarcação | Multa Cominatória / Astreintes | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>02/09/2020</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>16/06/2026 18:53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>16/06/2026 18:53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17/06/2026 22:50</t>
+          <t>17/06/2026 02:50</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0075901-50.2023.8.16.0000</t>
+          <t>0060779-60.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Desconsideração da Personalidade Jurídica | Responsabilidade dos sócios e administradores | Antecipação de Tutela / Recebimento como Cautelar</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>13/08/2024</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>29/05/2026 16:13</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>29/05/2026 16:13</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17/06/2026 22:50</t>
+          <t>17/06/2026 05:18</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0112463-58.2023.8.16.0000</t>
+          <t>0071507-34.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>17/06/2026 16:33</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0003565-73.2023.8.16.0024</t>
+          <t>0077125-23.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Bens Públicos | Inventário e Partilha</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>28/05/2026 17:23</t>
+          <t>28/05/2026 14:23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>28/05/2026 17:23</t>
+          <t>28/05/2026 14:23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>17/06/2026 01:20</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0040432-21.2016.8.16.0021</t>
+          <t>0077248-55.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>27/05/2026 13:23</t>
+          <t>26/05/2026 16:33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>27/05/2026 13:23</t>
+          <t>26/05/2026 16:33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>18/06/2026 09:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0013575-85.2022.8.16.0001</t>
+          <t>0083330-68.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Imissão</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>04/09/2024</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>08/06/2026 16:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>08/06/2026 16:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>17/06/2026 00:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0089105-30.2024.8.16.0000</t>
+          <t>0090734-39.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Classificação e/ou Preterição | Anulação e Correção de Provas / Questões</t>
+          <t>Incorporação Imobiliária | Enriquecimento sem Causa | Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>28/05/2026 14:53</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>28/05/2026 14:53</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/06/2026 23:32</t>
+          <t>17/06/2026 05:22</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0005682-75.2024.8.16.0000</t>
+          <t>0099021-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/06/2026 23:40</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0000524-83.2023.8.16.0126</t>
+          <t>0108975-95.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Cédula de Crédito Rural | Cessão de Crédito</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>29/05/2026 16:43</t>
+          <t>16/06/2026 16:43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>29/05/2026 16:43</t>
+          <t>16/06/2026 16:43</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>17/06/2026 23:50</t>
+          <t>16/06/2026 22:51</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0014750-24.2022.8.16.0031</t>
+          <t>0109367-35.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>21/05/2026 15:43</t>
+          <t>09/06/2026 19:53</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>21/05/2026 15:43</t>
+          <t>09/06/2026 19:53</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/06/2026 23:50</t>
+          <t>17/06/2026 00:12</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0003496-27.2019.8.16.0074</t>
+          <t>0118099-68.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Espécies de Contratos | Direitos e Títulos de Crédito</t>
+          <t>Tráfico de Drogas e Condutas Afins | Cerceamento de Defesa | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17/03/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29/05/2026 13:23</t>
+          <t>09/06/2026 18:53</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>29/05/2026 13:23</t>
+          <t>09/06/2026 18:53</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17/06/2026 23:50</t>
+          <t>17/06/2026 05:22</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0017293-88.2025.8.16.0000</t>
+          <t>0123907-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/06/2026 00:00</t>
+          <t>17/06/2026 21:40</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0025380-55.2020.8.16.0017</t>
+          <t>0129384-58.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Títulos de Crédito | Nulidade</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>22/05/2026 13:33</t>
+          <t>16/06/2026 14:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>22/05/2026 13:33</t>
+          <t>16/06/2026 14:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/06/2026 00:00</t>
+          <t>17/06/2026 01:30</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0052023-33.2022.8.16.0000</t>
+          <t>0131308-07.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>11/08/2023</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/06/2026 00:10</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0002140-07.2015.8.16.0116</t>
+          <t>0133988-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Reintegração ou Readmissão</t>
+          <t>Tráfico de Drogas e Condutas Afins | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>16/06/2026 15:13</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>16/06/2026 15:13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/06/2026 00:30</t>
+          <t>17/06/2026 02:50</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0015612-98.2016.8.16.0000</t>
+          <t>4003768-06.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/06/2026 00:50</t>
+          <t>17/06/2026 03:40</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4476,711 +4476,6 @@
         </is>
       </c>
       <c r="I86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>0000192-37.2022.8.16.0099</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Anulação</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>12/12/2024</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>25/05/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>25/05/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>18/06/2026 01:00</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>0003761-91.2024.8.16.0126</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Homicídio Qualificado</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>16/03/2026</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>17/06/2026 08:43</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>17/06/2026 08:43</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>18/06/2026 01:30</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>0012927-54.2018.8.16.0031</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Previdência privada</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>14/09/2023</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>20/05/2026 19:43</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>20/05/2026 19:43</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>18/06/2026 01:41</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0037437-46.2022.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Rescisão / Resolução | Despejo por Inadimplemento</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>25/05/2026 15:13</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>25/05/2026 15:13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>18/06/2026 01:41</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>0003468-89.2019.8.16.0064</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>27/03/2026</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>10/06/2026 17:13</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>10/06/2026 17:13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>18/06/2026 02:01</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>0000797-55.2023.8.16.0096</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Promessa de Compra e Venda</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>17/06/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>17/06/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>18/06/2026 02:01</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>0005963-31.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Acidente de Trânsito</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>11/09/2025</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>20/05/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>20/05/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>18/06/2026 02:11</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>0004556-02.2002.8.16.0019</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Depósito</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>29/11/2024</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>10/06/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>10/06/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>18/06/2026 02:20</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>0020425-61.2022.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Promessa de Compra e Venda | Antecipação de Tutela / Recebimento como Cautelar</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>29/01/2025</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>26/05/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>26/05/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>18/06/2026 02:20</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>0003657-60.2022.8.16.0194</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Compra e Venda</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>22/10/2025</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>21/05/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>21/05/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>18/06/2026 02:30</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0000108-47.2019.8.16.0194</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>20/09/2023</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>28/05/2026 15:43</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>28/05/2026 15:43</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>18/06/2026 03:00</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>0046717-35.2012.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>09/04/2025</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>16/06/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>16/06/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>18/06/2026 03:13</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>0006192-28.2024.8.16.0117</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Vícios Formais da Sentença</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>02/06/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>02/06/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>18/06/2026 03:30</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>0082972-35.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Promessa de Compra e Venda</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>20/05/2026 13:43</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>20/05/2026 13:43</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>18/06/2026 03:30</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0017760-67.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Vícios de Construção</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>16/06/2026 15:03</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>16/06/2026 15:03</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>18/06/2026 04:23</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000243-05.2022.8.16.0081</t>
+          <t>0004515-55.2023.8.16.0130</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>26/05/2026 13:33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>26/05/2026 13:33</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17/06/2026 16:40</t>
+          <t>22/06/2026 15:31</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000311-95.1995.8.16.0017</t>
+          <t>0001444-85.2024.8.16.0170</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Industrial</t>
+          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03</t>
+          <t>16/06/2026 14:43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03</t>
+          <t>16/06/2026 14:43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17/06/2026 18:11</t>
+          <t>22/06/2026 15:21</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000431-64.2024.8.16.0101</t>
+          <t>0001206-21.2008.8.16.0043</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Fato Atípico</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>27/05/2026 15:43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>27/05/2026 15:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18/06/2026 08:50</t>
+          <t>22/06/2026 15:23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000478-26.2022.8.16.0160</t>
+          <t>0000612-02.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>09/06/2026 17:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>09/06/2026 17:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17/06/2026 00:21</t>
+          <t>22/06/2026 15:23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000841-39.2017.8.16.0014</t>
+          <t>0013538-45.2018.8.16.0083</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fato Gerador/Incidência | Honorários Advocatícios | IPTU/ Imposto Predial e Territorial Urbano</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10/07/2024</t>
+          <t>27/07/2021</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27/05/2026 13:13</t>
+          <t>03/06/2026 15:53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27/05/2026 13:13</t>
+          <t>03/06/2026 15:53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>17/06/2026 00:12</t>
+          <t>22/06/2026 15:27</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000844-14.2020.8.16.0038</t>
+          <t>0002984-96.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Divisão e Demarcação</t>
+          <t>Inventário e Partilha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>03/06/2026 14:36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>03/06/2026 14:36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>22/06/2026 15:27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,37 +771,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0038288-93.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>08/03/2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>22/06/2026 15:15</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000869-34.2022.8.16.0110</t>
+          <t>0016517-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26/05/2026 17:43</t>
+          <t>19/06/2026 15:33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26/05/2026 17:43</t>
+          <t>19/06/2026 15:33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>22/06/2026 14:59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0026929-78.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>16/06/2026 15:23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>16/06/2026 15:23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>22/06/2026 14:59</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001213-13.2021.8.16.0025</t>
+          <t>0001930-24.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21/03/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09/06/2026 19:53</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>09/06/2026 19:53</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18/06/2026 08:30</t>
+          <t>22/06/2026 15:01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,37 +959,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001222-82.2021.8.16.0054</t>
+          <t>0026844-97.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Erro Médico | Erro Médico | COVID-19 | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/07/2023</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>29/05/2026 15:03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>29/05/2026 15:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>22/06/2026 15:02</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001544-72.2020.8.16.0043</t>
+          <t>0015641-72.2018.8.16.0035</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida | Inexequibilidade do Título / Inexigibilidade da Obrigação</t>
+          <t>Troca ou Permuta</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/12/2023</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>29/05/2026 16:03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>29/05/2026 16:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17/06/2026 01:10</t>
+          <t>22/06/2026 15:03</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001689-46.2023.8.16.0004</t>
+          <t>0001674-72.2015.8.16.0064</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Pagamento com Sub-rogação</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>02/06/2026 15:03</t>
+          <t>09/06/2026 09:50</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>02/06/2026 15:03</t>
+          <t>09/06/2026 09:50</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18/06/2026 07:20</t>
+          <t>22/06/2026 15:05</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0002350-52.2009.8.16.0089</t>
+          <t>0001221-83.2023.8.16.0133</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Cheque</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>28/05/2026 14:03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>28/05/2026 14:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18/06/2026 08:21</t>
+          <t>22/06/2026 15:05</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0002424-23.2025.8.16.0000</t>
+          <t>0026917-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Servidão Administrativa | Efeito Suspensivo a Recurso</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12/06/2026 14:33</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12/06/2026 14:33</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>17/06/2026 00:30</t>
+          <t>22/06/2026 15:07</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0002487-19.2023.8.16.0097</t>
+          <t>0005432-43.2020.8.16.0045</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17/06/2026 17:00</t>
+          <t>22/06/2026 15:07</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0002519-06.2019.8.16.0019</t>
+          <t>0007445-24.2018.8.16.0194</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Dever de Informação</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>20/07/2023</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29/05/2026 13:53</t>
+          <t>29/05/2026 16:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29/05/2026 13:53</t>
+          <t>29/05/2026 16:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17/06/2026 15:30</t>
+          <t>22/06/2026 15:08</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0002649-45.2014.8.16.0124</t>
+          <t>0033187-72.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17/06/2026 16:10</t>
+          <t>22/06/2026 14:26</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002958-19.2022.8.16.0049</t>
+          <t>0003490-45.2019.8.16.0098</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26/05/2026 15:23</t>
+          <t>08/06/2026 11:27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26/05/2026 15:23</t>
+          <t>08/06/2026 11:27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17/06/2026 00:30</t>
+          <t>22/06/2026 14:29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002960-81.2022.8.16.0083</t>
+          <t>0001333-61.2004.8.16.0119</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27/05/2026 14:25</t>
+          <t>28/05/2026 14:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27/05/2026 14:25</t>
+          <t>28/05/2026 14:33</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17/06/2026 02:10</t>
+          <t>22/06/2026 14:29</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0003010-91.2018.8.16.0069</t>
+          <t>0026995-26.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Prestação de Serviços | Honorários Advocatícios | Tutela Inibitória (Obrigação de Fazer e Não Fazer) | Planos de saúde</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25/05/2026 18:13</t>
+          <t>28/05/2026 16:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25/05/2026 18:13</t>
+          <t>28/05/2026 16:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18/06/2026 08:00</t>
+          <t>22/06/2026 14:33</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0003017-48.2024.8.16.0045</t>
+          <t>0000194-40.2023.8.16.0206</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Fornecimento de medicamentos | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>01/06/2026 15:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>01/06/2026 15:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>22/06/2026 14:34</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0003085-33.2024.8.16.0001</t>
+          <t>0016955-34.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>02/06/2026 17:03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>02/06/2026 17:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17/06/2026 18:10</t>
+          <t>22/06/2026 14:35</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0003259-74.2026.8.16.0000</t>
+          <t>0014113-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Prestação de Serviços | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>16/06/2026 23:40</t>
+          <t>22/06/2026 14:35</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0003261-17.2020.8.16.0174</t>
+          <t>0001368-54.2020.8.16.0153</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17/06/2026 15:20</t>
+          <t>22/06/2026 14:43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003490-45.2019.8.16.0098</t>
+          <t>0004453-02.2015.8.16.0031</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>17/03/2021</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08/06/2026 11:27</t>
+          <t>25/05/2026 18:23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>08/06/2026 11:27</t>
+          <t>25/05/2026 18:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17/06/2026 01:02</t>
+          <t>22/06/2026 14:54</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003530-51.2014.8.16.0179</t>
+          <t>0031444-40.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Prescrição e Decadência | Corretagem | Atraso na Entrega do Imóvel</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17/01/2022</t>
+          <t>19/03/2021</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17/06/2026 15:30</t>
+          <t>22/06/2026 14:54</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0001161-62.2020.8.16.0086</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Defeito, nulidade ou anulação | Doação</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>22/06/2026 14:55</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004654-85.2017.8.16.0075</t>
+          <t>0014789-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17/06/2026 04:30</t>
+          <t>22/06/2026 14:19</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0005159-54.2019.8.16.0189</t>
+          <t>0008021-14.2018.8.16.0001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17/06/2026 14:53</t>
+          <t>26/05/2026 11:08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17/06/2026 14:53</t>
+          <t>26/05/2026 11:08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>22/06/2026 14:23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0005542-20.2019.8.16.0193</t>
+          <t>0015429-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20/11/2023</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29/05/2026 14:33</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29/05/2026 14:33</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>17/06/2026 01:10</t>
+          <t>22/06/2026 14:23</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0005666-18.2024.8.16.0196</t>
+          <t>0006470-24.2023.8.16.0130</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Práticas Abusivas | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15/06/2026 16:33</t>
+          <t>29/05/2026 17:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15/06/2026 16:33</t>
+          <t>29/05/2026 17:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17/06/2026 01:41</t>
+          <t>19/06/2026 17:11</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0007014-41.2023.8.16.0185</t>
+          <t>4003768-06.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17/06/2026 02:20</t>
+          <t>19/06/2026 17:22</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0007643-78.2006.8.16.0001</t>
+          <t>0104155-33.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento | Causas Supervenientes à Sentença</t>
+          <t>Arrendamento Mercantil</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>05/12/2023</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29/05/2026 18:23</t>
+          <t>29/05/2026 17:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29/05/2026 18:23</t>
+          <t>29/05/2026 17:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17/06/2026 00:42</t>
+          <t>19/06/2026 15:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0007831-95.2021.8.16.0017</t>
+          <t>0029980-89.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Indenização por Dano Moral | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>02/06/2026 14:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>02/06/2026 14:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17/06/2026 04:11</t>
+          <t>19/06/2026 15:13</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0007962-53.2023.8.16.0194</t>
+          <t>0010287-32.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23/07/2025</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>19/06/2026 15:41</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0008125-21.2023.8.16.0004</t>
+          <t>0002960-81.2022.8.16.0083</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prova Subjetiva | Anulação e Correção de Provas / Questões</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28/05/2026 17:13</t>
+          <t>27/05/2026 14:25</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>28/05/2026 17:13</t>
+          <t>27/05/2026 14:25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17/06/2026 05:18</t>
+          <t>19/06/2026 15:51</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0009138-72.2012.8.16.0026</t>
+          <t>0007959-52.2010.8.16.0001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>17/02/2023</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>29/05/2026 14:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>29/05/2026 14:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>19/06/2026 16:01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0009827-23.2022.8.16.0170</t>
+          <t>0133603-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>19/06/2026 16:30</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0009888-66.2023.8.16.0001</t>
+          <t>0010638-75.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Aquisição</t>
+          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28/08/2024</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18/06/2026 07:20</t>
+          <t>19/06/2026 12:11</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0010170-10.2023.8.16.0000</t>
+          <t>0002948-75.2012.8.16.0129</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+          <t>Indenização por Dano Ambiental</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>02/06/2026 14:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>02/06/2026 14:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>19/06/2026 12:20</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0011157-95.2012.8.16.0173</t>
+          <t>0045791-34.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dissolução</t>
+          <t>Indenização por Dano Material | Seguro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>25/05/2026 12:11</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25/05/2026 12:11</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17/06/2026 04:20</t>
+          <t>19/06/2026 12:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0109062-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>25/05/2026 15:43</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>25/05/2026 15:43</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>19/06/2026 12:50</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0012558-24.2016.8.16.0001</t>
+          <t>0054268-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02/06/2026 16:23</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/06/2026 16:23</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>17/06/2026 02:50</t>
+          <t>19/06/2026 13:21</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0013333-39.2016.8.16.0001</t>
+          <t>0005394-95.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22/10/2024</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17/06/2026 15:50</t>
+          <t>19/06/2026 13:32</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0015088-72.2014.8.16.0000</t>
+          <t>0058662-67.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
+          <t>Indenização por Dano Material | Execução - Cumprimento de Sentença | Dever de Informação | Causas Supervenientes à Sentença</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>29/05/2026 14:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>29/05/2026 14:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17/06/2026 21:02</t>
+          <t>19/06/2026 13:32</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0015514-75.2020.8.16.0129</t>
+          <t>0051733-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14/12/2023</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29/05/2026 13:43</t>
+          <t>03/06/2026 14:13</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29/05/2026 13:43</t>
+          <t>03/06/2026 14:13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>17/06/2026 00:42</t>
+          <t>19/06/2026 14:01</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0025343-06.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0016083-36.2023.8.16.0173</t>
+          <t>0039522-68.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Cobrança | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0016432-10.2022.8.16.0000</t>
+          <t>0003261-17.2020.8.16.0174</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Espécies de Contratos | Contratos Bancários</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>23/01/2024</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>29/05/2026 15:13</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>29/05/2026 15:13</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17/06/2026 01:50</t>
+          <t>17/06/2026 15:20</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0016824-42.2021.8.16.0013</t>
+          <t>0003590-95.2022.8.16.0194</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>21/02/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15/06/2026 16:13</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>15/06/2026 16:13</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17/06/2026 00:50</t>
+          <t>19/06/2026 11:20</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0018234-64.2023.8.16.0014</t>
+          <t>0044118-45.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Desapropriação Indireta | Ação Rescisória</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>02/09/2022</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>28/05/2026 14:48</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>01/06/2026 14:33</t>
+          <t>28/05/2026 14:48</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>19/06/2026 11:30</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0021100-55.2021.8.16.0001</t>
+          <t>0000588-76.2020.8.16.0004</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16/06/2026 13:53</t>
+          <t>12/06/2026 13:03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>16/06/2026 13:53</t>
+          <t>12/06/2026 13:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17/06/2026 00:00</t>
+          <t>19/06/2026 11:40</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022746-98.2024.8.16.0000</t>
+          <t>0016042-12.2020.8.16.0129</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Transporte Aquaviário</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>04/10/2022</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>29/05/2026 14:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>29/05/2026 14:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>19/06/2026 12:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0023839-67.2022.8.16.0000</t>
+          <t>0004131-72.2012.8.16.0035</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Suspensão | Crimes contra o Meio Ambiente e o Patrimônio Genético</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15/08/2022</t>
+          <t>02/07/2024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>28/05/2026 15:43</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>28/05/2026 15:43</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17/06/2026 05:18</t>
+          <t>19/06/2026 12:03</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0024646-82.2025.8.16.0000</t>
+          <t>0074775-28.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>19/06/2026 12:10</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0026334-16.2024.8.16.0000</t>
+          <t>0010676-76.2024.8.16.0185</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>25/05/2026 14:53</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>25/05/2026 14:53</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17/06/2026 16:50</t>
+          <t>19/06/2026 08:55</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0030231-62.2019.8.16.0021</t>
+          <t>0093845-31.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24/04/2025 08:54</t>
+          <t>10/06/2026 17:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>02/06/2026 12:47</t>
+          <t>10/06/2026 17:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>17/06/2026 21:00</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0034028-70.2023.8.16.0000</t>
+          <t>0002402-77.2008.8.16.0026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>22/06/2022</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0034729-86.2023.8.16.0014</t>
+          <t>0011249-17.2016.8.16.0017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>24/06/2022</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>27/05/2026 13:13</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>27/05/2026 13:13</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17/06/2026 01:41</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0036070-97.2020.8.16.0000</t>
+          <t>0062898-11.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Serviços Profissionais | Indenização por Dano Moral | Indenização por Dano Material | Inadimplemento | Sucumbenciais</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02/07/2021</t>
+          <t>27/06/2022</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>09/06/2026 18:33</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>09/06/2026 18:33</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>19/06/2026 10:20</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0041785-52.2022.8.16.0000</t>
+          <t>0001650-47.2023.8.16.0037</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Promessa de Compra e Venda</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>26/05/2026 16:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>26/05/2026 16:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>19/06/2026 10:30</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0043186-18.2024.8.16.0000</t>
+          <t>0015769-90.2020.8.16.0013</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Classificação de créditos</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>27/05/2026 16:13</t>
+          <t>02/06/2026 17:13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>27/05/2026 16:13</t>
+          <t>02/06/2026 17:13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/06/2026 06:03</t>
+          <t>19/06/2026 07:11</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0049261-10.2023.8.16.0000</t>
+          <t>0004318-36.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Despejo por Inadimplemento</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>26/05/2026 14:33</t>
+          <t>03/06/2026 14:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>26/05/2026 14:33</t>
+          <t>03/06/2026 14:33</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18/06/2026 09:00</t>
+          <t>19/06/2026 07:11</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0051298-73.2024.8.16.0000</t>
+          <t>0026896-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29/05/2026 18:13</t>
+          <t>09/06/2026 13:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>29/05/2026 18:13</t>
+          <t>09/06/2026 13:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>19/06/2026 07:20</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0054268-12.2025.8.16.0000</t>
+          <t>0014258-55.2014.8.16.0017</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>16/06/2026 22:40</t>
+          <t>19/06/2026 07:20</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0055779-45.2025.8.16.0000</t>
+          <t>0003888-32.2019.8.16.0117</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>29/03/2022</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>16/06/2026 23:50</t>
+          <t>19/06/2026 08:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0056809-52.2024.8.16.0000</t>
+          <t>0004559-93.2020.8.16.0190</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>09/06/2026 14:13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>09/06/2026 14:13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17/06/2026 03:01</t>
+          <t>19/06/2026 08:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0057283-15.2023.8.16.0014</t>
+          <t>0000144-94.2003.8.16.0115</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Duplicata | Sustação de Protesto</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>12/05/2022</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>29/05/2026 18:03</t>
+          <t>25/05/2026 13:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>29/05/2026 18:03</t>
+          <t>25/05/2026 13:23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17/06/2026 21:50</t>
+          <t>19/06/2026 08:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0057438-89.2025.8.16.0000</t>
+          <t>0055779-45.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Divisão e Demarcação | Multa Cominatória / Astreintes | Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>25/02/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16/06/2026 18:53</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>16/06/2026 18:53</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17/06/2026 02:50</t>
+          <t>19/06/2026 08:30</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0060779-60.2024.8.16.0000</t>
+          <t>0006438-80.2018.8.16.0037</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Responsabilidade dos sócios e administradores | Antecipação de Tutela / Recebimento como Cautelar</t>
+          <t>Troca ou Permuta | Rescisão / Resolução | Perdas e Danos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17/06/2026 05:18</t>
+          <t>19/06/2026 08:30</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0071507-34.2022.8.16.0000</t>
+          <t>0018213-14.2016.8.16.0021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Promoção / Ascensão</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>28/05/2026 17:43</t>
+          <t>27/05/2026 14:53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>28/05/2026 17:43</t>
+          <t>27/05/2026 14:53</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17/06/2026 16:33</t>
+          <t>19/06/2026 05:13</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0077125-23.2023.8.16.0000</t>
+          <t>0009778-70.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bens Públicos | Inventário e Partilha</t>
+          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>28/05/2026 14:23</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>28/05/2026 14:23</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>17/06/2026 01:20</t>
+          <t>19/06/2026 05:51</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0077248-55.2022.8.16.0000</t>
+          <t>0098136-74.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>26/05/2026 16:33</t>
+          <t>10/06/2026 17:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>26/05/2026 16:33</t>
+          <t>10/06/2026 17:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/06/2026 09:00</t>
+          <t>19/06/2026 06:10</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0083330-68.2023.8.16.0000</t>
+          <t>0008894-41.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Imissão</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04/09/2024</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08/06/2026 16:03</t>
+          <t>28/05/2026 13:53</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>08/06/2026 16:03</t>
+          <t>28/05/2026 13:53</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17/06/2026 00:00</t>
+          <t>19/06/2026 06:10</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0090734-39.2024.8.16.0000</t>
+          <t>0128388-26.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Incorporação Imobiliária | Enriquecimento sem Causa | Confissão/Composição de Dívida</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/06/2026 05:22</t>
+          <t>19/06/2026 06:30</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0099021-88.2024.8.16.0000</t>
+          <t>0015403-44.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>08/06/2026 13:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>08/06/2026 13:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>19/06/2026 03:01</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0108975-95.2023.8.16.0000</t>
+          <t>0024911-63.2015.8.16.0185</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural | Cessão de Crédito</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>03/09/2024</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16/06/2026 16:43</t>
+          <t>25/05/2026 14:03</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>16/06/2026 16:43</t>
+          <t>25/05/2026 14:03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>16/06/2026 22:51</t>
+          <t>19/06/2026 03:21</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0109367-35.2023.8.16.0000</t>
+          <t>0070336-42.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>27/11/2024</t>
+          <t>03/06/2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>09/06/2026 19:53</t>
+          <t>09/06/2026 19:43</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>09/06/2026 19:53</t>
+          <t>09/06/2026 19:43</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/06/2026 00:12</t>
+          <t>19/06/2026 03:21</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0118099-68.2024.8.16.0000</t>
+          <t>0003259-74.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Cerceamento de Defesa | Aplicação da Pena</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>09/06/2026 18:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>09/06/2026 18:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17/06/2026 05:22</t>
+          <t>19/06/2026 04:42</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0123907-54.2024.8.16.0000</t>
+          <t>0008238-79.2018.8.16.0026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
+          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>19/10/2021</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>27/05/2026 15:33</t>
+          <t>16/06/2026 19:23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>27/05/2026 15:33</t>
+          <t>16/06/2026 19:23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17/06/2026 21:40</t>
+          <t>19/06/2026 04:42</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0129384-58.2024.8.16.0000</t>
+          <t>0002402-80.2023.8.16.0146</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Títulos de Crédito | Nulidade</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16/06/2026 14:53</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>16/06/2026 14:53</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>17/06/2026 01:30</t>
+          <t>19/06/2026 02:01</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0131308-07.2024.8.16.0000</t>
+          <t>0028980-21.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>26/05/2026 18:03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>26/05/2026 18:03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>19/06/2026 02:10</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0133988-28.2025.8.16.0000</t>
+          <t>0016878-42.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prisão Preventiva</t>
+          <t>Indenização por Dano Ambiental | Tutela Inibitória (Obrigação de Fazer e Não Fazer)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16/06/2026 15:13</t>
+          <t>25/05/2026 16:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>16/06/2026 15:13</t>
+          <t>25/05/2026 16:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>17/06/2026 02:50</t>
+          <t>19/06/2026 02:20</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,45 +4437,750 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4003768-06.2025.8.16.4321</t>
+          <t>0000945-84.2018.8.16.0179</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Alienação Fiduciária</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>26/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>26/05/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>19/06/2026 02:30</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0011340-51.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Perda da Propriedade</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>05/09/2024</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>19/06/2026 02:30</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0001450-02.2020.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>Recurso Especial</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>09/06/2026 16:53</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>09/06/2026 16:53</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>17/06/2026 03:40</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Telefonia</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>04/10/2024</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>16/06/2026 11:33</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>16/06/2026 11:33</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>19/06/2026 02:40</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0022321-08.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Adimplemento e Extinção</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>31/07/2024</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>01/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>01/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:12</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0007024-81.2010.8.16.0075</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Anulação</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>09/06/2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>29/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>29/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:12</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0000261-24.2024.8.16.0156</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Crimes de Trânsito</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:20</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0000649-40.2018.8.16.0057</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:42</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0041907-94.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Repetição de indébito</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>02/06/2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:42</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0008067-29.2012.8.16.0028</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Água e/ou Esgoto | Indenização por Dano Moral | Indenização por Dano Ambiental</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>26/05/2026 17:53</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>26/05/2026 17:53</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:42</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0002292-90.2021.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Descontos Indevidos | Servidores Inativos</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>01/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>01/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:11</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0005147-62.2013.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:22</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0001330-11.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:22</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0035567-23.2013.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>25/05/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>25/05/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:41</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0001427-66.2015.8.16.0137</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:41</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0007827-80.2022.8.16.0160</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Limitação de Juros</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>01/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>01/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0010400-52.2022.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Crimes de Trânsito</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0003590-95.2022.8.16.0194</t>
+          <t>0003530-51.2014.8.16.0179</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Promessa de Compra e Venda | Prescrição e Decadência | Corretagem | Atraso na Entrega do Imóvel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>17/01/2022</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19/06/2026 11:20</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0044118-45.2020.8.16.0000</t>
+          <t>0002519-06.2019.8.16.0019</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Desapropriação Indireta | Ação Rescisória</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>28/05/2026 14:48</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>28/05/2026 14:48</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19/06/2026 11:30</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0000588-76.2020.8.16.0004</t>
+          <t>0013333-39.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>22/10/2024</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/06/2026 11:40</t>
+          <t>17/06/2026 15:50</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0016042-12.2020.8.16.0129</t>
+          <t>0002649-45.2014.8.16.0124</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Transporte Aquaviário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04/10/2022</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>29/05/2026 14:53</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>29/05/2026 14:53</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19/06/2026 12:00</t>
+          <t>17/06/2026 16:10</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0004131-72.2012.8.16.0035</t>
+          <t>0003017-48.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02/07/2024</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/06/2026 12:03</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0074775-28.2024.8.16.0000</t>
+          <t>0041785-52.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19/06/2026 12:10</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0010676-76.2024.8.16.0185</t>
+          <t>0071507-34.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25/05/2026 14:53</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25/05/2026 14:53</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/06/2026 08:55</t>
+          <t>17/06/2026 16:33</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0093845-31.2024.8.16.0000</t>
+          <t>0000243-05.2022.8.16.0081</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>17/06/2026 16:40</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0002402-77.2008.8.16.0026</t>
+          <t>0026334-16.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22/06/2022</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>17/06/2026 16:50</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0011249-17.2016.8.16.0017</t>
+          <t>0002487-19.2023.8.16.0097</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>24/06/2022</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>17/06/2026 17:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0062898-11.2012.8.16.0001</t>
+          <t>0003085-33.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serviços Profissionais | Indenização por Dano Moral | Indenização por Dano Material | Inadimplemento | Sucumbenciais</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>27/06/2022</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>09/06/2026 18:33</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>09/06/2026 18:33</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>19/06/2026 10:20</t>
+          <t>17/06/2026 18:10</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0001650-47.2023.8.16.0037</t>
+          <t>0000311-95.1995.8.16.0017</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda</t>
+          <t>Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26/05/2026 16:03</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>26/05/2026 16:03</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>19/06/2026 10:30</t>
+          <t>17/06/2026 18:11</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0015769-90.2020.8.16.0013</t>
+          <t>0000863-07.2022.8.16.0052</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19/06/2026 07:11</t>
+          <t>17/06/2026 18:12</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0004318-36.2022.8.16.0001</t>
+          <t>0015887-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>03/06/2026 14:33</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>03/06/2026 14:33</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19/06/2026 07:11</t>
+          <t>17/06/2026 18:20</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0026896-88.2025.8.16.0000</t>
+          <t>0010170-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>09/06/2026 13:23</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>09/06/2026 13:23</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>17/06/2026 19:11</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0014258-55.2014.8.16.0017</t>
+          <t>0012526-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0003888-32.2019.8.16.0117</t>
+          <t>0000869-34.2022.8.16.0110</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>29/03/2022</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0004559-93.2020.8.16.0190</t>
+          <t>0000936-38.2011.8.16.0060</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0000144-94.2003.8.16.0115</t>
+          <t>0022746-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Duplicata | Sustação de Protesto</t>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12/05/2022</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>25/05/2026 13:23</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25/05/2026 13:23</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>17/06/2026 20:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0055779-45.2025.8.16.0000</t>
+          <t>0099021-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>19/06/2026 08:30</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0006438-80.2018.8.16.0037</t>
+          <t>0004046-67.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Troca ou Permuta | Rescisão / Resolução | Perdas e Danos</t>
+          <t>Pagamento Indevido</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19/06/2026 08:30</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0018213-14.2016.8.16.0021</t>
+          <t>0036070-97.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Promoção / Ascensão</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>02/07/2021</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>27/05/2026 14:53</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>27/05/2026 14:53</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/06/2026 05:13</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0009778-70.2023.8.16.0194</t>
+          <t>0009138-72.2012.8.16.0026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>19/06/2026 05:51</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0098136-74.2024.8.16.0000</t>
+          <t>0030231-62.2019.8.16.0021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>24/04/2025 08:54</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>02/06/2026 12:47</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19/06/2026 06:10</t>
+          <t>17/06/2026 21:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0008894-41.2023.8.16.0194</t>
+          <t>0015088-72.2014.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>11/04/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>28/05/2026 13:53</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>28/05/2026 13:53</t>
+          <t>25/05/2026 18:03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19/06/2026 06:10</t>
+          <t>17/06/2026 21:02</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0128388-26.2025.8.16.0000</t>
+          <t>0016083-36.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19/06/2026 06:30</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0015403-44.2025.8.16.0185</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>08/06/2026 13:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>08/06/2026 13:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19/06/2026 03:01</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0024911-63.2015.8.16.0185</t>
+          <t>0123907-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>03/09/2024</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>25/05/2026 14:03</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>25/05/2026 14:03</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>19/06/2026 03:21</t>
+          <t>17/06/2026 21:40</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0070336-42.2022.8.16.0000</t>
+          <t>0057283-15.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>03/06/2024</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>09/06/2026 19:43</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>09/06/2026 19:43</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>19/06/2026 03:21</t>
+          <t>17/06/2026 21:50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0003259-74.2026.8.16.0000</t>
+          <t>0000844-14.2020.8.16.0038</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Divisão e Demarcação</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0008238-79.2018.8.16.0026</t>
+          <t>0024646-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>19/10/2021</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0002402-80.2023.8.16.0146</t>
+          <t>0000679-63.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Promoção</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>19/06/2026 02:01</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0028980-21.2019.8.16.0017</t>
+          <t>0118728-42.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20/05/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>26/05/2026 18:03</t>
+          <t>25/05/2026 14:03</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>26/05/2026 18:03</t>
+          <t>25/05/2026 14:03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19/06/2026 02:10</t>
+          <t>17/06/2026 22:30</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0016878-42.2024.8.16.0000</t>
+          <t>0004034-22.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental | Tutela Inibitória (Obrigação de Fazer e Não Fazer)</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>25/05/2026 16:53</t>
+          <t>27/05/2026 13:03</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>25/05/2026 16:53</t>
+          <t>27/05/2026 13:03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19/06/2026 02:20</t>
+          <t>17/06/2026 22:30</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0000945-84.2018.8.16.0179</t>
+          <t>0000375-09.2022.8.16.0034</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26/05/2026 14:43</t>
+          <t>25/05/2026 13:43</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>26/05/2026 14:43</t>
+          <t>25/05/2026 13:43</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19/06/2026 02:30</t>
+          <t>17/06/2026 22:41</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0011340-51.2022.8.16.0194</t>
+          <t>0007390-80.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Perda da Propriedade</t>
+          <t>Indenização Trabalhista</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
+          <t>02/09/2020</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>03/06/2026 14:23</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>03/06/2026 14:23</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19/06/2026 02:30</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0001450-02.2020.8.16.0019</t>
+          <t>0075901-50.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telefonia</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>13/08/2024</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>29/05/2026 16:13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>29/05/2026 16:13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>19/06/2026 02:40</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0022321-08.2023.8.16.0000</t>
+          <t>0112463-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Adimplemento e Extinção</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01/06/2026 15:13</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01/06/2026 15:13</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19/06/2026 01:12</t>
+          <t>17/06/2026 23:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0007024-81.2010.8.16.0075</t>
+          <t>0003565-73.2023.8.16.0024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Anulação</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29/05/2026 14:03</t>
+          <t>28/05/2026 17:23</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>29/05/2026 14:03</t>
+          <t>28/05/2026 17:23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>19/06/2026 01:12</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0000261-24.2024.8.16.0156</t>
+          <t>0040432-21.2016.8.16.0021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>19/06/2026 01:20</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0000649-40.2018.8.16.0057</t>
+          <t>0013575-85.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0041907-94.2024.8.16.0000</t>
+          <t>0089105-30.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição de indébito</t>
+          <t>Classificação e/ou Preterição | Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>28/05/2026 14:53</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>28/05/2026 14:53</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>17/06/2026 23:32</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0008067-29.2012.8.16.0028</t>
+          <t>0005682-75.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Água e/ou Esgoto | Indenização por Dano Moral | Indenização por Dano Ambiental</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>26/05/2026 17:53</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>26/05/2026 17:53</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>17/06/2026 23:40</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0002292-90.2021.8.16.0004</t>
+          <t>0000524-83.2023.8.16.0126</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Descontos Indevidos | Servidores Inativos</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>01/06/2026 13:33</t>
+          <t>29/05/2026 16:43</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>01/06/2026 13:33</t>
+          <t>29/05/2026 16:43</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/06/2026 23:11</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,37 +4907,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0005147-62.2013.8.16.0185</t>
+          <t>0003496-27.2019.8.16.0074</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Espécies de Contratos | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>17/03/2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>25/05/2026 17:33</t>
+          <t>29/05/2026 13:23</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>25/05/2026 17:33</t>
+          <t>29/05/2026 13:23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>18/06/2026 23:22</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0001330-11.2023.8.16.0000</t>
+          <t>0017293-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/06/2026 23:22</t>
+          <t>18/06/2026 00:00</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0035567-23.2013.8.16.0000</t>
+          <t>0052023-33.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>11/08/2023</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>25/05/2026 16:23</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>25/05/2026 16:23</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/06/2026 23:41</t>
+          <t>18/06/2026 00:10</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,7 +5048,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0001427-66.2015.8.16.0137</t>
+          <t>0002140-07.2015.8.16.0116</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5058,27 +5058,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+          <t>Reintegração ou Readmissão</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/06/2026 23:41</t>
+          <t>18/06/2026 00:30</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,37 +5095,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0007827-80.2022.8.16.0160</t>
+          <t>0015612-98.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01/06/2026 13:53</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18/06/2026 23:50</t>
+          <t>18/06/2026 00:50</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0010400-52.2022.8.16.0173</t>
+          <t>0000192-37.2022.8.16.0099</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5152,27 +5152,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Anulação</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>25/05/2026 13:13</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>25/05/2026 13:13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18/06/2026 23:50</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0004453-02.2015.8.16.0031</t>
+          <t>0031444-40.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,22 +1674,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17/03/2021</t>
+          <t>19/03/2021</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>25/05/2026 18:23</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25/05/2026 18:23</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0031444-40.2017.8.16.0000</t>
+          <t>0001161-62.2020.8.16.0086</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Defeito, nulidade ou anulação | Doação</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19/03/2021</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>27/05/2026 13:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22/06/2026 14:54</t>
+          <t>22/06/2026 14:55</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0001161-62.2020.8.16.0086</t>
+          <t>0014789-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Doação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27/05/2026 13:13</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27/05/2026 13:13</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22/06/2026 14:55</t>
+          <t>22/06/2026 14:19</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0014789-12.2025.8.16.0000</t>
+          <t>0008021-14.2018.8.16.0001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>26/05/2026 11:08</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>26/05/2026 11:08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22/06/2026 14:19</t>
+          <t>22/06/2026 14:23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0008021-14.2018.8.16.0001</t>
+          <t>0015429-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,22 +1862,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26/05/2026 11:08</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26/05/2026 11:08</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0015429-80.2023.8.16.0001</t>
+          <t>0006470-24.2023.8.16.0130</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Práticas Abusivas | Tutela de Urgência</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>29/05/2026 17:43</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>29/05/2026 17:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22/06/2026 14:23</t>
+          <t>19/06/2026 17:11</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0006470-24.2023.8.16.0130</t>
+          <t>4003768-06.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Práticas Abusivas | Tutela de Urgência</t>
+          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29/05/2026 17:43</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>29/05/2026 17:43</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/06/2026 17:11</t>
+          <t>19/06/2026 17:22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4003768-06.2025.8.16.4321</t>
+          <t>0104155-33.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
+          <t>Arrendamento Mercantil</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>29/05/2026 17:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>29/05/2026 17:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19/06/2026 17:22</t>
+          <t>19/06/2026 15:00</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0104155-33.2023.8.16.0000</t>
+          <t>0029980-89.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arrendamento Mercantil</t>
+          <t>Indenização por Dano Moral | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29/05/2026 17:03</t>
+          <t>02/06/2026 14:13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29/05/2026 17:03</t>
+          <t>02/06/2026 14:13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19/06/2026 15:00</t>
+          <t>19/06/2026 15:13</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0029980-89.2024.8.16.0014</t>
+          <t>0010287-32.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Repetição do Indébito</t>
+          <t>Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02/06/2026 14:13</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02/06/2026 14:13</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19/06/2026 15:13</t>
+          <t>19/06/2026 15:41</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0010287-32.2022.8.16.0001</t>
+          <t>0002960-81.2022.8.16.0083</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pagamento em Consignação</t>
+          <t>PIS/PASEP | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>27/05/2026 14:25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>27/05/2026 14:25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19/06/2026 15:41</t>
+          <t>19/06/2026 15:51</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0002960-81.2022.8.16.0083</t>
+          <t>0007959-52.2010.8.16.0001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PIS/PASEP | Indenização por Dano Material</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>17/02/2023</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27/05/2026 14:25</t>
+          <t>29/05/2026 14:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27/05/2026 14:25</t>
+          <t>29/05/2026 14:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/06/2026 15:51</t>
+          <t>19/06/2026 16:01</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0007959-52.2010.8.16.0001</t>
+          <t>0133603-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17/02/2023</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29/05/2026 14:53</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29/05/2026 14:53</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19/06/2026 16:01</t>
+          <t>19/06/2026 16:30</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0133603-17.2024.8.16.0000</t>
+          <t>0010638-75.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
+          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19/06/2026 16:30</t>
+          <t>19/06/2026 12:11</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0010638-75.2023.8.16.0031</t>
+          <t>0002948-75.2012.8.16.0129</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
+          <t>Indenização por Dano Ambiental</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>02/06/2026 14:23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>02/06/2026 14:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19/06/2026 12:11</t>
+          <t>19/06/2026 12:20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0002948-75.2012.8.16.0129</t>
+          <t>0045791-34.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,22 +2379,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental</t>
+          <t>Indenização por Dano Material | Seguro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02/06/2026 14:23</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>02/06/2026 14:23</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0045791-34.2024.8.16.0000</t>
+          <t>0054268-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Seguro</t>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/06/2026 12:20</t>
+          <t>19/06/2026 13:21</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0109062-17.2024.8.16.0000</t>
+          <t>0005394-95.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2478,22 +2478,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>25/05/2026 15:43</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25/05/2026 15:43</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/06/2026 12:50</t>
+          <t>19/06/2026 13:32</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0054268-12.2025.8.16.0000</t>
+          <t>0058662-67.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+          <t>Indenização por Dano Material | Execução - Cumprimento de Sentença | Dever de Informação | Causas Supervenientes à Sentença</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>29/05/2026 14:33</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>29/05/2026 14:33</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19/06/2026 13:21</t>
+          <t>19/06/2026 13:32</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0005394-95.2022.8.16.0001</t>
+          <t>0051733-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Concurso de Credores</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>03/06/2026 14:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>03/06/2026 14:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19/06/2026 13:32</t>
+          <t>19/06/2026 14:01</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0058662-67.2022.8.16.0000</t>
+          <t>0025343-06.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Execução - Cumprimento de Sentença | Dever de Informação | Causas Supervenientes à Sentença</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29/05/2026 14:33</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29/05/2026 14:33</t>
+          <t>29/05/2026 18:13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/06/2026 13:32</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0051733-47.2024.8.16.0000</t>
+          <t>0039522-68.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Cobrança | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>19/06/2026 14:01</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0025343-06.2025.8.16.0000</t>
+          <t>0003261-17.2020.8.16.0174</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>29/05/2026 18:13</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>29/05/2026 18:13</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>17/06/2026 15:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0039522-68.2023.8.16.0014</t>
+          <t>0003530-51.2014.8.16.0179</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cobrança | Honorários Advocatícios</t>
+          <t>Promessa de Compra e Venda | Prescrição e Decadência | Corretagem | Atraso na Entrega do Imóvel</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>17/01/2022</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0003261-17.2020.8.16.0174</t>
+          <t>0002519-06.2019.8.16.0019</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>20/01/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>29/05/2026 13:53</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17/06/2026 15:20</t>
+          <t>17/06/2026 15:30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0003530-51.2014.8.16.0179</t>
+          <t>0013333-39.2016.8.16.0001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Prescrição e Decadência | Corretagem | Atraso na Entrega do Imóvel</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17/01/2022</t>
+          <t>22/10/2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17/06/2026 15:30</t>
+          <t>17/06/2026 15:50</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0002519-06.2019.8.16.0019</t>
+          <t>0002649-45.2014.8.16.0124</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20/01/2025</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>29/05/2026 13:53</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>29/05/2026 13:53</t>
+          <t>26/05/2026 13:03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17/06/2026 15:30</t>
+          <t>17/06/2026 16:10</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0013333-39.2016.8.16.0001</t>
+          <t>0003017-48.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22/10/2024</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>03/06/2026 15:33</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17/06/2026 15:50</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0002649-45.2014.8.16.0124</t>
+          <t>0041785-52.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>09/06/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>26/05/2026 13:03</t>
+          <t>28/05/2026 13:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17/06/2026 16:10</t>
+          <t>17/06/2026 16:20</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0003017-48.2024.8.16.0045</t>
+          <t>0071507-34.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3042,22 +3042,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>03/06/2026 15:33</t>
+          <t>28/05/2026 17:43</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>17/06/2026 16:33</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0041785-52.2022.8.16.0000</t>
+          <t>0000243-05.2022.8.16.0081</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>09/06/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>28/05/2026 13:33</t>
+          <t>28/05/2026 15:23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17/06/2026 16:20</t>
+          <t>17/06/2026 16:40</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0071507-34.2022.8.16.0000</t>
+          <t>0026334-16.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28/05/2026 17:43</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>28/05/2026 17:43</t>
+          <t>02/06/2026 16:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17/06/2026 16:33</t>
+          <t>17/06/2026 16:50</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0000243-05.2022.8.16.0081</t>
+          <t>0002487-19.2023.8.16.0097</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito | Desobediência | Desacato | Ameaça</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>28/05/2026 15:23</t>
+          <t>09/06/2026 11:07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>17/06/2026 16:40</t>
+          <t>17/06/2026 17:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0026334-16.2024.8.16.0000</t>
+          <t>0003085-33.2024.8.16.0001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Alienação Fiduciária</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>02/06/2026 16:43</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>17/06/2026 16:50</t>
+          <t>17/06/2026 18:10</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0002487-19.2023.8.16.0097</t>
+          <t>0000311-95.1995.8.16.0017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>09/06/2026 11:07</t>
+          <t>28/05/2026 18:03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17/06/2026 17:00</t>
+          <t>17/06/2026 18:11</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0003085-33.2024.8.16.0001</t>
+          <t>0000863-07.2022.8.16.0052</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alienação Fiduciária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17/06/2026 18:10</t>
+          <t>17/06/2026 18:12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0000311-95.1995.8.16.0017</t>
+          <t>0015887-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Industrial</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3376,17 +3376,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>28/05/2026 18:03</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17/06/2026 18:11</t>
+          <t>17/06/2026 18:20</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,37 +3403,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0010170-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>17/06/2026 19:11</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0012526-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0010170-10.2023.8.16.0000</t>
+          <t>0000869-34.2022.8.16.0110</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>26/05/2026 17:43</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0000936-38.2011.8.16.0060</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,22 +3554,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0000869-34.2022.8.16.0110</t>
+          <t>0022746-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26/05/2026 17:43</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>26/05/2026 17:43</t>
+          <t>03/06/2026 16:03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>17/06/2026 20:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0099021-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0022746-98.2024.8.16.0000</t>
+          <t>0004046-67.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Pagamento Indevido</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0099021-88.2024.8.16.0000</t>
+          <t>0036070-97.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>02/07/2021</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0009138-72.2012.8.16.0026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0036070-97.2020.8.16.0000</t>
+          <t>0030231-62.2019.8.16.0021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>02/07/2021</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>24/04/2025 08:54</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>02/06/2026 12:47</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>17/06/2026 21:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0009138-72.2012.8.16.0026</t>
+          <t>0016083-36.2023.8.16.0173</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Limitação de Juros</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>06/05/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>01/06/2026 14:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0030231-62.2019.8.16.0021</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>24/04/2025 08:54</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02/06/2026 12:47</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17/06/2026 21:00</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0015088-72.2014.8.16.0000</t>
+          <t>0123907-54.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro | Vícios de Construção</t>
+          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>11/04/2025</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>25/05/2026 18:03</t>
+          <t>27/05/2026 15:33</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17/06/2026 21:02</t>
+          <t>17/06/2026 21:40</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0016083-36.2023.8.16.0173</t>
+          <t>0057283-15.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Limitação de Juros</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>06/05/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>01/06/2026 14:03</t>
+          <t>29/05/2026 18:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>17/06/2026 21:50</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0009827-23.2022.8.16.0170</t>
+          <t>0000844-14.2020.8.16.0038</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+          <t>Divisão e Demarcação</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>27/05/2026 16:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0123907-54.2024.8.16.0000</t>
+          <t>0024646-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Ônus da Prova | Assistência Judiciária Gratuita | Obrigação de Fazer / Não Fazer</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>27/05/2026 15:33</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>27/05/2026 15:33</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>17/06/2026 21:40</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0057283-15.2023.8.16.0014</t>
+          <t>0000679-63.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Promoção</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>29/05/2026 18:03</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>29/05/2026 18:03</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/06/2026 21:50</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0000844-14.2020.8.16.0038</t>
+          <t>0004034-22.2024.8.16.0045</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Divisão e Demarcação</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>27/05/2026 13:03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>27/05/2026 16:03</t>
+          <t>27/05/2026 13:03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>17/06/2026 22:30</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,37 +4249,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0024646-82.2025.8.16.0000</t>
+          <t>0007390-80.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Indenização Trabalhista</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/09/2020</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0000679-63.2022.8.16.0048</t>
+          <t>0075901-50.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Promoção</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>13/08/2024</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>29/05/2026 16:13</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>29/05/2026 16:13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0118728-42.2024.8.16.0000</t>
+          <t>0112463-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>25/05/2026 14:03</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>25/05/2026 14:03</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>17/06/2026 22:30</t>
+          <t>17/06/2026 23:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0004034-22.2024.8.16.0045</t>
+          <t>0003565-73.2023.8.16.0024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>27/05/2026 13:03</t>
+          <t>28/05/2026 17:23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>27/05/2026 13:03</t>
+          <t>28/05/2026 17:23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>17/06/2026 22:30</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0000375-09.2022.8.16.0034</t>
+          <t>0040432-21.2016.8.16.0021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>25/05/2026 13:43</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>25/05/2026 13:43</t>
+          <t>27/05/2026 13:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>17/06/2026 22:41</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0007390-80.2018.8.16.0030</t>
+          <t>0013575-85.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indenização Trabalhista</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>02/09/2020</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>17/06/2026 22:50</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0075901-50.2023.8.16.0000</t>
+          <t>0089105-30.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Classificação e/ou Preterição | Anulação e Correção de Provas / Questões</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>13/08/2024</t>
+          <t>05/02/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>29/05/2026 16:13</t>
+          <t>28/05/2026 14:53</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>29/05/2026 16:13</t>
+          <t>28/05/2026 14:53</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>17/06/2026 22:50</t>
+          <t>17/06/2026 23:32</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0112463-58.2023.8.16.0000</t>
+          <t>0005682-75.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>17/06/2026 23:40</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0003565-73.2023.8.16.0024</t>
+          <t>0000524-83.2023.8.16.0126</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>28/05/2026 17:23</t>
+          <t>29/05/2026 16:43</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>28/05/2026 17:23</t>
+          <t>29/05/2026 16:43</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,37 +4672,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0040432-21.2016.8.16.0021</t>
+          <t>0003496-27.2019.8.16.0074</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Espécies de Contratos | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>17/03/2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>27/05/2026 13:23</t>
+          <t>29/05/2026 13:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>27/05/2026 13:23</t>
+          <t>29/05/2026 13:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>17/06/2026 23:50</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0013575-85.2022.8.16.0001</t>
+          <t>0017293-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>18/06/2026 00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0089105-30.2024.8.16.0000</t>
+          <t>0052023-33.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Classificação e/ou Preterição | Anulação e Correção de Provas / Questões</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>05/02/2026</t>
+          <t>11/08/2023</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>28/05/2026 14:53</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>28/05/2026 14:53</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>17/06/2026 23:32</t>
+          <t>18/06/2026 00:10</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0005682-75.2024.8.16.0000</t>
+          <t>0002140-07.2015.8.16.0116</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Reintegração ou Readmissão</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>02/06/2026 16:53</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>17/06/2026 23:40</t>
+          <t>18/06/2026 00:30</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,37 +4860,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0000524-83.2023.8.16.0126</t>
+          <t>0015612-98.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>29/05/2026 16:43</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>29/05/2026 16:43</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>17/06/2026 23:50</t>
+          <t>18/06/2026 00:50</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0003496-27.2019.8.16.0074</t>
+          <t>0003761-91.2024.8.16.0126</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4917,27 +4917,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Espécies de Contratos | Direitos e Títulos de Crédito</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>17/03/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>29/05/2026 13:23</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>29/05/2026 13:23</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>17/06/2026 23:50</t>
+          <t>18/06/2026 01:30</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0017293-88.2025.8.16.0000</t>
+          <t>0003468-89.2019.8.16.0064</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/06/2026 00:00</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0052023-33.2022.8.16.0000</t>
+          <t>0000797-55.2023.8.16.0096</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5011,27 +5011,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Promessa de Compra e Venda</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11/08/2023</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/06/2026 00:10</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,7 +5048,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0002140-07.2015.8.16.0116</t>
+          <t>0004556-02.2002.8.16.0019</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5058,27 +5058,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Reintegração ou Readmissão</t>
+          <t>Depósito</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/06/2026 00:30</t>
+          <t>18/06/2026 02:20</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0015612-98.2016.8.16.0000</t>
+          <t>0020425-61.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Promessa de Compra e Venda | Antecipação de Tutela / Recebimento como Cautelar</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>29/01/2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>26/05/2026 14:03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>26/05/2026 14:03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18/06/2026 00:50</t>
+          <t>18/06/2026 02:20</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0000192-37.2022.8.16.0099</t>
+          <t>0000108-47.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5152,27 +5152,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Anulação</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/09/2023</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>25/05/2026 13:13</t>
+          <t>28/05/2026 15:43</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>25/05/2026 13:13</t>
+          <t>28/05/2026 15:43</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 03:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -486,6 +486,4706 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0019169-66.2011.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>23/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>01/07/2026 07:50</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0006159-21.2024.8.16.0058</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01/07/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0009293-49.2009.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pensão</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>11/12/2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>24/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01/07/2026 08:51</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0006993-31.2021.8.16.0025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Previdência privada</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:14</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0000615-03.2021.8.16.0076</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12/07/2024</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:14</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0100788-64.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>23/10/2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01/07/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0000431-64.2024.8.16.0101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>03/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>03/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01/07/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0000763-58.2023.8.16.0168</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>23/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01/07/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0001056-42.2015.8.16.0060</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Crime Tentado</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01/07/2026 06:50</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0051733-47.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Concurso de Credores</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01/07/2026 04:30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0026162-57.2023.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01/07/2026 04:30</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0000994-81.2021.8.16.0095</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>24/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>24/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01/07/2026 05:10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0071243-12.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>19/06/2026 13:34</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>19/06/2026 13:34</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01/07/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0014974-89.2021.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16/04/2022</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>26/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>26/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01/07/2026 06:01</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0002415-17.2024.8.16.0123</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Edital</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>23/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>23/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01/07/2026 06:20</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0128373-91.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>23/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>23/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01/07/2026 03:50</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0000740-41.2019.8.16.0043</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Peculato | Regime inicial | Desclassificação</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>02/09/2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01/07/2026 04:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0148132-07.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Latrocínio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26/06/2026 18:53</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>26/06/2026 18:53</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01/07/2026 03:22</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0006558-86.2022.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias | Alíquota</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12/02/2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01/07/2026 03:22</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0074775-28.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01/07/2026 03:22</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0001444-85.2024.8.16.0170</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:21</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0000612-02.2023.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0013538-45.2018.8.16.0083</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>27/07/2021</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>03/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>03/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0002984-96.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Inventário e Partilha</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>24/09/2024</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:36</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:27</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0016517-88.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>19/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>19/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:59</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0026929-78.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Prova Oral</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:59</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0001930-24.2022.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Furto Qualificado</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>15/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:01</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0001674-72.2015.8.16.0064</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Crime Tentado</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>15/05/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:50</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:50</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:05</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0026917-64.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Prova Oral</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:53</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:53</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:07</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0005432-43.2020.8.16.0045</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Acidente de Trânsito</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:07</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0038288-93.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>08/03/2024</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>22/06/2026 15:15</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0033187-72.2023.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:26</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0003490-45.2019.8.16.0098</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Preconceituosa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>08/06/2026 11:27</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>08/06/2026 11:27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:29</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0016955-34.2023.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rescisão / Resolução</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:35</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0001368-54.2020.8.16.0153</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:43</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0031444-40.2017.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>19/03/2021</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>16/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:54</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4003768-06.2025.8.16.4321</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>09/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>09/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>19/06/2026 17:22</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0014789-12.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>24/02/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>19/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:19</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0015429-80.2023.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>22/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0029980-89.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Repetição do Indébito</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>19/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0010287-32.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pagamento em Consignação</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:43</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:43</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>19/06/2026 15:41</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0133603-17.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>19/06/2026 16:30</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0010638-75.2023.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>24/10/2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>11/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>19/06/2026 12:11</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0002948-75.2012.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Ambiental</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>02/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>19/06/2026 12:20</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0045791-34.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Seguro</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>19/06/2026 12:20</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0054268-12.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>15/06/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>19/06/2026 13:21</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0005394-95.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>19/06/2026 13:32</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0039522-68.2023.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cobrança | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>19/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0007014-41.2023.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:53</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>19/06/2026 10:50</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0003590-95.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>19/06/2026 11:20</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0000588-76.2020.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ISS/ Imposto sobre Serviços</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>19/06/2026 11:40</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0004131-72.2012.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>02/07/2024</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>19/06/2026 12:03</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0093845-31.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>10/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19/06/2026 09:40</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0002402-77.2008.8.16.0026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22/06/2022</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:43</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>17/06/2026 14:43</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>19/06/2026 09:40</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0011249-17.2016.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>24/06/2022</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>16/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>19/06/2026 09:40</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0062898-11.2012.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Serviços Profissionais | Indenização por Dano Moral | Indenização por Dano Material | Inadimplemento | Sucumbenciais</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>27/06/2022</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>09/06/2026 18:33</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>09/06/2026 18:33</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>19/06/2026 10:20</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0015769-90.2020.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Crimes de Trânsito</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>19/06/2026 07:11</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0004318-36.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Despejo por Inadimplemento</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>19/06/2026 07:11</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0026896-88.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Prova Oral</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>09/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>09/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>19/06/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0014258-55.2014.8.16.0017</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>30/12/1899</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>16/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>19/06/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0003888-32.2019.8.16.0117</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>29/03/2022</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>15/06/2026 11:59</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>15/06/2026 11:59</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>19/06/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0004559-93.2020.8.16.0190</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ISS/ Imposto sobre Serviços</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>09/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>09/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>19/06/2026 08:00</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0055779-45.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>19/06/2026 08:30</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0009778-70.2023.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>19/06/2026 05:51</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0098136-74.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>19/06/2026 06:10</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0128388-26.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Condomínio</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>09/06/2026 20:13</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>19/06/2026 06:30</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0015403-44.2025.8.16.0185</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>08/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>08/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>19/06/2026 03:01</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0070336-42.2022.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>03/06/2024</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:43</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:43</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>19/06/2026 03:21</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0003259-74.2026.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>19/06/2026 04:42</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0008238-79.2018.8.16.0026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19/10/2021</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>19/06/2026 04:42</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0002402-80.2023.8.16.0146</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>09/07/2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>19/06/2026 02:01</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0011340-51.2022.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Perda da Propriedade</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>05/09/2024</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>19/06/2026 02:30</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0001450-02.2020.8.16.0019</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Telefonia</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04/10/2024</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>16/06/2026 11:33</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>16/06/2026 11:33</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>19/06/2026 02:40</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0000261-24.2024.8.16.0156</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Crimes de Trânsito</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:53</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:20</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0000649-40.2018.8.16.0057</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:42</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0041907-94.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Contratos Bancários | Repetição de indébito</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>02/06/2025</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:23</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:42</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0001330-11.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>24/02/2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>16/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:22</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0001427-66.2015.8.16.0137</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>16/06/2026 18:13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:41</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0010400-52.2022.8.16.0173</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Crimes de Trânsito</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>02/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>18/06/2026 23:50</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0004806-25.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Compra e Venda | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>02/06/2026 17:23</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>19/06/2026 00:10</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0003045-83.2022.8.16.0013</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Estelionato</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>18/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>18/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>19/06/2026 00:10</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0093262-46.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Ambiental | Processo Legislativo</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>12/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>12/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>19/06/2026 00:31</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0001860-37.2022.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>08/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>08/06/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>19/06/2026 00:31</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0070693-17.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Recurso Ordinário em Habeas Corpus</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>17/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>17/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>19/06/2026 00:51</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0001955-93.2025.8.16.0026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Homicídio Qualificado</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>18/06/2026 22:31</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0057279-49.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel | Assistência Judiciária Gratuita</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>15/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>15/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>18/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0062635-59.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Despesas Condominiais</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>01/04/2025</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>17/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>17/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>18/06/2026 19:20</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0001946-21.2024.8.16.0074</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Confissão/Composição de Dívida</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>12/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>12/06/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>18/06/2026 18:51</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0123195-64.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Prestação de Contas</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>23/03/2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>03/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>03/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>18/06/2026 18:51</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0024088-13.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Locação de Imóvel</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>12/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>18/06/2026 17:50</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0001101-82.2025.8.16.0064</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Cédula Hipotecária</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>12/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>18/06/2026 17:50</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0009489-18.2015.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Previdência privada</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>14/08/2023</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>09/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>09/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>18/06/2026 18:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0000863-07.2022.8.16.0052</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>11/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:12</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0015887-32.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>11/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>17/06/2026 18:20</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0010170-10.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>21/07/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:11</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0012526-07.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:50</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0000936-38.2011.8.16.0060</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>16/03/2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>10/06/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>17/06/2026 19:50</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0022746-98.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>03/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>03/06/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0099021-88.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:33</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>09/06/2026 17:33</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:10</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0004046-67.2021.8.16.0004</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Pagamento Indevido</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10/06/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:10</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000431-64.2024.8.16.0101</t>
+          <t>0000763-58.2023.8.16.0168</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>03/06/2026 13:13</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000763-58.2023.8.16.0168</t>
+          <t>0026162-57.2023.8.16.0017</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Moral | Contratos Bancários</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01/07/2026 06:50</t>
+          <t>01/07/2026 04:30</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,37 +865,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001056-42.2015.8.16.0060</t>
+          <t>0000994-81.2021.8.16.0095</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01/07/2026 06:50</t>
+          <t>01/07/2026 05:10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0051733-47.2024.8.16.0000</t>
+          <t>0071243-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Concurso de Credores</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>19/06/2026 13:34</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>03/06/2026 14:13</t>
+          <t>19/06/2026 13:34</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01/07/2026 04:30</t>
+          <t>01/07/2026 05:40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0026162-57.2023.8.16.0017</t>
+          <t>0014974-89.2021.8.16.0000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Contratos Bancários</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/04/2022</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>26/06/2026 15:33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>26/06/2026 15:33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01/07/2026 04:30</t>
+          <t>01/07/2026 06:01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0002415-17.2024.8.16.0123</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Edital</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01/07/2026 05:10</t>
+          <t>01/07/2026 06:20</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0071243-12.2025.8.16.0000</t>
+          <t>0128373-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19/06/2026 13:34</t>
+          <t>23/06/2026 14:33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19/06/2026 13:34</t>
+          <t>23/06/2026 14:33</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01/07/2026 05:40</t>
+          <t>01/07/2026 03:50</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0014974-89.2021.8.16.0000</t>
+          <t>0000740-41.2019.8.16.0043</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Peculato | Regime inicial | Desclassificação</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16/04/2022</t>
+          <t>02/09/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26/06/2026 15:33</t>
+          <t>23/06/2026 16:03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26/06/2026 15:33</t>
+          <t>23/06/2026 16:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01/07/2026 06:01</t>
+          <t>01/07/2026 04:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0002415-17.2024.8.16.0123</t>
+          <t>0148132-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edital</t>
+          <t>Latrocínio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>26/06/2026 18:53</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>26/06/2026 18:53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01/07/2026 06:20</t>
+          <t>01/07/2026 03:22</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0128373-91.2024.8.16.0000</t>
+          <t>0001444-85.2024.8.16.0170</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23/06/2026 14:33</t>
+          <t>16/06/2026 14:43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23/06/2026 14:33</t>
+          <t>16/06/2026 14:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01/07/2026 03:50</t>
+          <t>22/06/2026 15:21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0000740-41.2019.8.16.0043</t>
+          <t>0000612-02.2023.8.16.0004</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peculato | Regime inicial | Desclassificação</t>
+          <t>Aposentadoria Especial (Art. 57/8)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>02/09/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23/06/2026 16:03</t>
+          <t>09/06/2026 17:23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23/06/2026 16:03</t>
+          <t>09/06/2026 17:23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01/07/2026 04:00</t>
+          <t>22/06/2026 15:23</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0148132-07.2025.8.16.0000</t>
+          <t>0016517-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latrocínio</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26/06/2026 18:53</t>
+          <t>19/06/2026 15:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26/06/2026 18:53</t>
+          <t>19/06/2026 15:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01/07/2026 03:22</t>
+          <t>22/06/2026 14:59</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0006558-86.2022.8.16.0004</t>
+          <t>0026929-78.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias | Alíquota</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12/02/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02/06/2026 16:05</t>
+          <t>16/06/2026 15:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>02/06/2026 16:05</t>
+          <t>16/06/2026 15:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01/07/2026 03:22</t>
+          <t>22/06/2026 14:59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0074775-28.2024.8.16.0000</t>
+          <t>0001930-24.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01/07/2026 03:22</t>
+          <t>22/06/2026 15:01</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001444-85.2024.8.16.0170</t>
+          <t>0001674-72.2015.8.16.0064</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
+          <t>Homicídio Qualificado | Crime Tentado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16/06/2026 14:43</t>
+          <t>09/06/2026 09:50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16/06/2026 14:43</t>
+          <t>09/06/2026 09:50</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22/06/2026 15:21</t>
+          <t>22/06/2026 15:05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0000612-02.2023.8.16.0004</t>
+          <t>0026917-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aposentadoria Especial (Art. 57/8)</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>09/06/2026 17:23</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>09/06/2026 17:23</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22/06/2026 15:23</t>
+          <t>22/06/2026 15:07</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0013538-45.2018.8.16.0083</t>
+          <t>0005432-43.2020.8.16.0045</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>27/07/2021</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>03/06/2026 15:53</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>03/06/2026 15:53</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22/06/2026 15:27</t>
+          <t>22/06/2026 15:07</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002984-96.2024.8.16.0000</t>
+          <t>0038288-93.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inventário e Partilha</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>08/03/2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>03/06/2026 14:36</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>03/06/2026 14:36</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22/06/2026 15:27</t>
+          <t>22/06/2026 15:15</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0016517-88.2025.8.16.0000</t>
+          <t>0033187-72.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19/06/2026 15:33</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19/06/2026 15:33</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22/06/2026 14:59</t>
+          <t>22/06/2026 14:26</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0026929-78.2025.8.16.0000</t>
+          <t>0003490-45.2019.8.16.0098</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>08/06/2026 11:27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>08/06/2026 11:27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22/06/2026 14:59</t>
+          <t>22/06/2026 14:29</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0001930-24.2022.8.16.0014</t>
+          <t>0001368-54.2020.8.16.0153</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22/06/2026 15:01</t>
+          <t>22/06/2026 14:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0001674-72.2015.8.16.0064</t>
+          <t>0031444-40.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>19/03/2021</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>09/06/2026 09:50</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>09/06/2026 09:50</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22/06/2026 15:05</t>
+          <t>22/06/2026 14:54</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0026917-64.2025.8.16.0000</t>
+          <t>4003768-06.2025.8.16.4321</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>09/06/2026 16:53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>22/06/2026 15:07</t>
+          <t>19/06/2026 17:22</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0005432-43.2020.8.16.0045</t>
+          <t>0014789-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22/06/2026 15:07</t>
+          <t>22/06/2026 14:19</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0038288-93.2023.8.16.0000</t>
+          <t>0015429-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08/03/2024</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22/06/2026 15:15</t>
+          <t>22/06/2026 14:23</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0033187-72.2023.8.16.0001</t>
+          <t>0010287-32.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>22/06/2026 14:26</t>
+          <t>19/06/2026 15:41</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0003490-45.2019.8.16.0098</t>
+          <t>0133603-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08/06/2026 11:27</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>08/06/2026 11:27</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22/06/2026 14:29</t>
+          <t>19/06/2026 16:30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0016955-34.2023.8.16.0017</t>
+          <t>0010638-75.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02/06/2026 17:03</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>02/06/2026 17:03</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22/06/2026 14:35</t>
+          <t>19/06/2026 12:11</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,37 +2087,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0001368-54.2020.8.16.0153</t>
+          <t>0045791-34.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Indenização por Dano Material | Seguro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22/06/2026 14:43</t>
+          <t>19/06/2026 12:20</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,37 +2134,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0031444-40.2017.8.16.0000</t>
+          <t>0054268-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19/03/2021</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22/06/2026 14:54</t>
+          <t>19/06/2026 13:21</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,37 +2181,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4003768-06.2025.8.16.4321</t>
+          <t>0005394-95.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/06/2026 17:22</t>
+          <t>19/06/2026 13:32</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0014789-12.2025.8.16.0000</t>
+          <t>0039522-68.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Cobrança | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>16/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>16/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>19/06/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>19/06/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>22/06/2026 14:19</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0015429-80.2023.8.16.0001</t>
+          <t>0007014-41.2023.8.16.0185</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>22/06/2026 14:23</t>
+          <t>19/06/2026 10:50</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,37 +2322,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0029980-89.2024.8.16.0014</t>
+          <t>0003590-95.2022.8.16.0194</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Repetição do Indébito</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02/06/2026 14:13</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>02/06/2026 14:13</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19/06/2026 15:13</t>
+          <t>19/06/2026 11:20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0010287-32.2022.8.16.0001</t>
+          <t>0000588-76.2020.8.16.0004</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pagamento em Consignação</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>12/06/2026 13:03</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>12/06/2026 13:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19/06/2026 15:41</t>
+          <t>19/06/2026 11:40</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0133603-17.2024.8.16.0000</t>
+          <t>0004131-72.2012.8.16.0035</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>02/07/2024</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/06/2026 16:30</t>
+          <t>19/06/2026 12:03</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0010638-75.2023.8.16.0031</t>
+          <t>0093845-31.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
+          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>10/06/2026 17:03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>10/06/2026 17:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/06/2026 12:11</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0002948-75.2012.8.16.0129</t>
+          <t>0002402-77.2008.8.16.0026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental</t>
+          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>22/06/2022</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02/06/2026 14:23</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/06/2026 14:23</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19/06/2026 12:20</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0045791-34.2024.8.16.0000</t>
+          <t>0011249-17.2016.8.16.0017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Seguro</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>24/06/2022</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19/06/2026 12:20</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0054268-12.2025.8.16.0000</t>
+          <t>0062898-11.2012.8.16.0001</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+          <t>Serviços Profissionais | Indenização por Dano Moral | Indenização por Dano Material | Inadimplemento | Sucumbenciais</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>27/06/2022</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>09/06/2026 18:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>09/06/2026 18:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/06/2026 13:21</t>
+          <t>19/06/2026 10:20</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0005394-95.2022.8.16.0001</t>
+          <t>0026896-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>09/06/2026 13:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>09/06/2026 13:23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>19/06/2026 13:32</t>
+          <t>19/06/2026 07:20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0039522-68.2023.8.16.0014</t>
+          <t>0014258-55.2014.8.16.0017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cobrança | Honorários Advocatícios</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>19/06/2026 07:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0007014-41.2023.8.16.0185</t>
+          <t>0003888-32.2019.8.16.0117</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>29/03/2022</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/06/2026 10:50</t>
+          <t>19/06/2026 08:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0003590-95.2022.8.16.0194</t>
+          <t>0004559-93.2020.8.16.0190</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>09/06/2026 14:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>09/06/2026 14:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19/06/2026 11:20</t>
+          <t>19/06/2026 08:00</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0000588-76.2020.8.16.0004</t>
+          <t>0055779-45.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19/06/2026 11:40</t>
+          <t>19/06/2026 08:30</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0004131-72.2012.8.16.0035</t>
+          <t>0009778-70.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02/07/2024</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19/06/2026 12:03</t>
+          <t>19/06/2026 05:51</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0093845-31.2024.8.16.0000</t>
+          <t>0098136-74.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>10/06/2026 17:23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>10/06/2026 17:23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>19/06/2026 06:10</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0002402-77.2008.8.16.0026</t>
+          <t>0128388-26.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22/06/2022</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>19/06/2026 06:30</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0011249-17.2016.8.16.0017</t>
+          <t>0015403-44.2025.8.16.0185</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>24/06/2022</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>08/06/2026 13:03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>08/06/2026 13:03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>19/06/2026 03:01</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0062898-11.2012.8.16.0001</t>
+          <t>0070336-42.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serviços Profissionais | Indenização por Dano Moral | Indenização por Dano Material | Inadimplemento | Sucumbenciais</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>27/06/2022</t>
+          <t>03/06/2024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>09/06/2026 18:33</t>
+          <t>09/06/2026 19:43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>09/06/2026 18:33</t>
+          <t>09/06/2026 19:43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19/06/2026 10:20</t>
+          <t>19/06/2026 03:21</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0015769-90.2020.8.16.0013</t>
+          <t>0003259-74.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/06/2026 17:13</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/06/2026 07:11</t>
+          <t>19/06/2026 04:42</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0004318-36.2022.8.16.0001</t>
+          <t>0008238-79.2018.8.16.0026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Despejo por Inadimplemento</t>
+          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>19/10/2021</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>03/06/2026 14:33</t>
+          <t>16/06/2026 19:23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>03/06/2026 14:33</t>
+          <t>16/06/2026 19:23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19/06/2026 07:11</t>
+          <t>19/06/2026 04:42</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0026896-88.2025.8.16.0000</t>
+          <t>0002402-80.2023.8.16.0146</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>09/06/2026 13:23</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>09/06/2026 13:23</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>19/06/2026 02:01</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0014258-55.2014.8.16.0017</t>
+          <t>0001450-02.2020.8.16.0019</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Telefonia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>04/10/2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>16/06/2026 11:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>16/06/2026 11:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>19/06/2026 02:40</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0003888-32.2019.8.16.0117</t>
+          <t>0041907-94.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Contratos Bancários | Repetição de indébito</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>29/03/2022</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>16/06/2026 18:23</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>16/06/2026 18:23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>19/06/2026 01:42</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0004559-93.2020.8.16.0190</t>
+          <t>0001330-11.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>16/06/2026 16:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>16/06/2026 16:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>18/06/2026 23:22</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0055779-45.2025.8.16.0000</t>
+          <t>0001427-66.2015.8.16.0137</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
+          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>19/06/2026 08:30</t>
+          <t>18/06/2026 23:41</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0009778-70.2023.8.16.0194</t>
+          <t>0003045-83.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Estelionato</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>18/06/2026 13:13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>18/06/2026 13:13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19/06/2026 05:51</t>
+          <t>19/06/2026 00:10</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0098136-74.2024.8.16.0000</t>
+          <t>0093262-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
+          <t>Indenização por Dano Ambiental | Processo Legislativo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/06/2026 06:10</t>
+          <t>19/06/2026 00:31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0128388-26.2025.8.16.0000</t>
+          <t>0001860-37.2022.8.16.0004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>08/06/2026 13:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>08/06/2026 13:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19/06/2026 06:30</t>
+          <t>19/06/2026 00:31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0015403-44.2025.8.16.0185</t>
+          <t>0070693-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08/06/2026 13:03</t>
+          <t>17/06/2026 13:03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>08/06/2026 13:03</t>
+          <t>17/06/2026 13:03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/06/2026 03:01</t>
+          <t>19/06/2026 00:51</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0070336-42.2022.8.16.0000</t>
+          <t>0001955-93.2025.8.16.0026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>03/06/2024</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>09/06/2026 19:43</t>
+          <t>08/06/2026 14:03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>09/06/2026 19:43</t>
+          <t>08/06/2026 14:03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>19/06/2026 03:21</t>
+          <t>18/06/2026 22:31</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0003259-74.2026.8.16.0000</t>
+          <t>0057279-49.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Locação de Imóvel | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>15/06/2026 15:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>15/06/2026 15:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>18/06/2026 19:11</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0008238-79.2018.8.16.0026</t>
+          <t>0062635-59.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19/10/2021</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>17/06/2026 13:43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>17/06/2026 13:43</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>18/06/2026 19:20</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0002402-80.2023.8.16.0146</t>
+          <t>0001946-21.2024.8.16.0074</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>19/06/2026 02:01</t>
+          <t>18/06/2026 18:51</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0011340-51.2022.8.16.0194</t>
+          <t>0024088-13.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Perda da Propriedade</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>05/09/2024</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>03/06/2026 14:23</t>
+          <t>12/06/2026 13:33</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>03/06/2026 14:23</t>
+          <t>12/06/2026 13:33</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>19/06/2026 02:30</t>
+          <t>18/06/2026 17:50</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0001450-02.2020.8.16.0019</t>
+          <t>0001101-82.2025.8.16.0064</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telefonia</t>
+          <t>Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>19/06/2026 02:40</t>
+          <t>18/06/2026 17:50</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0000261-24.2024.8.16.0156</t>
+          <t>0009489-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>14/08/2023</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>09/06/2026 14:33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02/06/2026 16:53</t>
+          <t>09/06/2026 14:33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>19/06/2026 01:20</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0000649-40.2018.8.16.0057</t>
+          <t>0000863-07.2022.8.16.0052</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>17/06/2026 18:12</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0041907-94.2024.8.16.0000</t>
+          <t>0015887-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição de indébito</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>17/06/2026 18:20</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0001330-11.2023.8.16.0000</t>
+          <t>0010170-10.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>09/06/2026 17:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18/06/2026 23:22</t>
+          <t>17/06/2026 19:11</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0001427-66.2015.8.16.0137</t>
+          <t>0012526-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/06/2026 23:41</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0010400-52.2022.8.16.0173</t>
+          <t>0000936-38.2011.8.16.0060</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>02/06/2026 15:53</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/06/2026 23:50</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0004806-25.2021.8.16.0001</t>
+          <t>0099021-88.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização por Dano Material</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>02/06/2026 17:23</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>02/06/2026 17:23</t>
+          <t>09/06/2026 17:33</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19/06/2026 00:10</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0003045-83.2022.8.16.0013</t>
+          <t>0004046-67.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Estelionato</t>
+          <t>Pagamento Indevido</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>19/06/2026 00:10</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0093262-46.2024.8.16.0000</t>
+          <t>0036070-97.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental | Processo Legislativo</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>02/07/2021</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>19/06/2026 00:31</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0001860-37.2022.8.16.0004</t>
+          <t>0009138-72.2012.8.16.0026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>08/06/2026 13:13</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>08/06/2026 13:13</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19/06/2026 00:31</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0070693-17.2025.8.16.0000</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Prisão Preventiva</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19/06/2026 00:51</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0001955-93.2025.8.16.0026</t>
+          <t>0024646-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/06/2026 22:31</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0057279-49.2025.8.16.0000</t>
+          <t>0000679-63.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Assistência Judiciária Gratuita</t>
+          <t>Promoção</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15/06/2026 15:03</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>15/06/2026 15:03</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/06/2026 19:11</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0062635-59.2024.8.16.0000</t>
+          <t>0007390-80.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Indenização Trabalhista</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>02/09/2020</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>09/06/2026 13:43</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/06/2026 19:20</t>
+          <t>17/06/2026 22:50</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0001946-21.2024.8.16.0074</t>
+          <t>0112463-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18/06/2026 18:51</t>
+          <t>17/06/2026 23:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0123195-64.2024.8.16.0000</t>
+          <t>0013575-85.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prestação de Contas</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>03/06/2026 13:43</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>03/06/2026 13:43</t>
+          <t>09/06/2026 20:13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/06/2026 18:51</t>
+          <t>17/06/2026 23:14</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0024088-13.2025.8.16.0000</t>
+          <t>0005682-75.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/06/2026 17:50</t>
+          <t>17/06/2026 23:40</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0001101-82.2025.8.16.0064</t>
+          <t>0017293-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cédula Hipotecária</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/06/2026 17:50</t>
+          <t>18/06/2026 00:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0009489-18.2015.8.16.0001</t>
+          <t>0052023-33.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14/08/2023</t>
+          <t>11/08/2023</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>09/06/2026 14:33</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>09/06/2026 14:33</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>18/06/2026 00:10</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0015612-98.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>18/06/2026 00:50</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,37 +4860,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0003761-91.2024.8.16.0126</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>18/06/2026 01:30</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,37 +4907,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0010170-10.2023.8.16.0000</t>
+          <t>0003468-89.2019.8.16.0064</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0000797-55.2023.8.16.0096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Promessa de Compra e Venda</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0004556-02.2002.8.16.0019</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5011,27 +5011,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Depósito</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>18/06/2026 02:20</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0022746-98.2024.8.16.0000</t>
+          <t>0046717-35.2012.8.16.0000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal) | ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>03/06/2026 16:03</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>18/06/2026 03:13</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0099021-88.2024.8.16.0000</t>
+          <t>0017760-67.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Vícios de Construção</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>16/06/2026 15:03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>16/06/2026 15:03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>18/06/2026 04:23</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,37 +5142,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0000105-96.2020.8.16.0052</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>14/01/2022</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>18/06/2026 04:30</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0000612-02.2023.8.16.0004</t>
+          <t>0016517-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aposentadoria Especial (Art. 57/8)</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>09/06/2026 17:23</t>
+          <t>19/06/2026 15:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09/06/2026 17:23</t>
+          <t>19/06/2026 15:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22/06/2026 15:23</t>
+          <t>22/06/2026 14:59</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,32 +1288,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0016517-88.2025.8.16.0000</t>
+          <t>0026929-78.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19/06/2026 15:33</t>
+          <t>16/06/2026 15:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19/06/2026 15:33</t>
+          <t>16/06/2026 15:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0026929-78.2025.8.16.0000</t>
+          <t>0001930-24.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22/06/2026 14:59</t>
+          <t>22/06/2026 15:01</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001930-24.2022.8.16.0014</t>
+          <t>0026917-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22/06/2026 15:01</t>
+          <t>22/06/2026 15:07</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001674-72.2015.8.16.0064</t>
+          <t>0005432-43.2020.8.16.0045</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Crime Tentado</t>
+          <t>Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09/06/2026 09:50</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>09/06/2026 09:50</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22/06/2026 15:05</t>
+          <t>22/06/2026 15:07</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0026917-64.2025.8.16.0000</t>
+          <t>0038288-93.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>08/03/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22/06/2026 15:07</t>
+          <t>22/06/2026 15:15</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0005432-43.2020.8.16.0045</t>
+          <t>0033187-72.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22/06/2026 15:07</t>
+          <t>22/06/2026 14:26</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0038288-93.2023.8.16.0000</t>
+          <t>0001368-54.2020.8.16.0153</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08/03/2024</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22/06/2026 15:15</t>
+          <t>22/06/2026 14:43</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0033187-72.2023.8.16.0001</t>
+          <t>0031444-40.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>19/03/2021</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22/06/2026 14:26</t>
+          <t>22/06/2026 14:54</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003490-45.2019.8.16.0098</t>
+          <t>0014789-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08/06/2026 11:27</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>08/06/2026 11:27</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22/06/2026 14:29</t>
+          <t>22/06/2026 14:19</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,37 +1711,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0001368-54.2020.8.16.0153</t>
+          <t>0015429-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>16/06/2026 16:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22/06/2026 14:43</t>
+          <t>22/06/2026 14:23</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0031444-40.2017.8.16.0000</t>
+          <t>0010287-32.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Pagamento em Consignação</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19/03/2021</t>
+          <t>15/10/2024</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>16/06/2026 18:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22/06/2026 14:54</t>
+          <t>19/06/2026 15:41</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4003768-06.2025.8.16.4321</t>
+          <t>0133603-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pena Privativa de Liberdade | Crimes de Trânsito | Intimação</t>
+          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>09/06/2026 16:53</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19/06/2026 17:22</t>
+          <t>19/06/2026 16:30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0014789-12.2025.8.16.0000</t>
+          <t>0010638-75.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>11/06/2026 15:33</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22/06/2026 14:19</t>
+          <t>19/06/2026 12:11</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0015429-80.2023.8.16.0001</t>
+          <t>0045791-34.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Material | Seguro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22/06/2026 14:23</t>
+          <t>19/06/2026 12:20</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,37 +1946,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0010287-32.2022.8.16.0001</t>
+          <t>0054268-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pagamento em Consignação</t>
+          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>15/06/2026 16:23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/06/2026 15:41</t>
+          <t>19/06/2026 13:21</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0133603-17.2024.8.16.0000</t>
+          <t>0005394-95.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19/06/2026 16:30</t>
+          <t>19/06/2026 13:32</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0010638-75.2023.8.16.0031</t>
+          <t>0039522-68.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
+          <t>Cobrança | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19/06/2026 12:11</t>
+          <t>19/06/2026 14:13</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0045791-34.2024.8.16.0000</t>
+          <t>0007014-41.2023.8.16.0185</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Seguro</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19/06/2026 12:20</t>
+          <t>19/06/2026 10:50</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0054268-12.2025.8.16.0000</t>
+          <t>0003590-95.2022.8.16.0194</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>10/06/2026 15:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19/06/2026 13:21</t>
+          <t>19/06/2026 11:20</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0005394-95.2022.8.16.0001</t>
+          <t>0000588-76.2020.8.16.0004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>12/06/2026 13:03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>12/06/2026 13:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/06/2026 13:32</t>
+          <t>19/06/2026 11:40</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0039522-68.2023.8.16.0014</t>
+          <t>0004131-72.2012.8.16.0035</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cobrança | Honorários Advocatícios</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>02/07/2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>19/06/2026 12:03</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0007014-41.2023.8.16.0185</t>
+          <t>0093845-31.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>10/06/2026 17:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>10/06/2026 17:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19/06/2026 10:50</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0003590-95.2022.8.16.0194</t>
+          <t>0002402-77.2008.8.16.0026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>22/06/2022</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19/06/2026 11:20</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0000588-76.2020.8.16.0004</t>
+          <t>0011249-17.2016.8.16.0017</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/06/2022</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19/06/2026 11:40</t>
+          <t>19/06/2026 09:40</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0004131-72.2012.8.16.0035</t>
+          <t>0014258-55.2014.8.16.0017</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02/07/2024</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/06/2026 12:03</t>
+          <t>19/06/2026 07:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0093845-31.2024.8.16.0000</t>
+          <t>0003888-32.2019.8.16.0117</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>29/03/2022</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>19/06/2026 08:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0002402-77.2008.8.16.0026</t>
+          <t>0009778-70.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
+          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22/06/2022</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>19/06/2026 05:51</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0011249-17.2016.8.16.0017</t>
+          <t>0098136-74.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24/06/2022</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>10/06/2026 17:23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>10/06/2026 17:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>19/06/2026 06:10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0062898-11.2012.8.16.0001</t>
+          <t>0003259-74.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serviços Profissionais | Indenização por Dano Moral | Indenização por Dano Material | Inadimplemento | Sucumbenciais</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27/06/2022</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>09/06/2026 18:33</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>09/06/2026 18:33</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/06/2026 10:20</t>
+          <t>19/06/2026 04:42</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0026896-88.2025.8.16.0000</t>
+          <t>0008238-79.2018.8.16.0026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>19/10/2021</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>09/06/2026 13:23</t>
+          <t>16/06/2026 19:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>09/06/2026 13:23</t>
+          <t>16/06/2026 19:23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>19/06/2026 04:42</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0014258-55.2014.8.16.0017</t>
+          <t>0002402-80.2023.8.16.0146</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>09/07/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>19/06/2026 02:01</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0003888-32.2019.8.16.0117</t>
+          <t>0001450-02.2020.8.16.0019</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Telefonia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>29/03/2022</t>
+          <t>04/10/2024</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>16/06/2026 11:33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>16/06/2026 11:33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>19/06/2026 02:40</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0004559-93.2020.8.16.0190</t>
+          <t>0041907-94.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Contratos Bancários | Repetição de indébito</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>16/06/2026 18:23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>09/06/2026 14:13</t>
+          <t>16/06/2026 18:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>19/06/2026 01:42</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0055779-45.2025.8.16.0000</t>
+          <t>0001330-11.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Corrupção ativa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>16/06/2026 16:03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>16/06/2026 16:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>19/06/2026 08:30</t>
+          <t>18/06/2026 23:22</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0009778-70.2023.8.16.0194</t>
+          <t>0001427-66.2015.8.16.0137</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>19/06/2026 05:51</t>
+          <t>18/06/2026 23:41</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0098136-74.2024.8.16.0000</t>
+          <t>0003045-83.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
+          <t>Estelionato</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>18/06/2026 13:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>18/06/2026 13:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/06/2026 06:10</t>
+          <t>19/06/2026 00:10</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0128388-26.2025.8.16.0000</t>
+          <t>0093262-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Indenização por Dano Ambiental | Processo Legislativo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19/06/2026 06:30</t>
+          <t>19/06/2026 00:31</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0015403-44.2025.8.16.0185</t>
+          <t>0070693-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08/06/2026 13:03</t>
+          <t>17/06/2026 13:03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>08/06/2026 13:03</t>
+          <t>17/06/2026 13:03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/06/2026 03:01</t>
+          <t>19/06/2026 00:51</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0070336-42.2022.8.16.0000</t>
+          <t>0057279-49.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Locação de Imóvel | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>03/06/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>09/06/2026 19:43</t>
+          <t>15/06/2026 15:03</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>09/06/2026 19:43</t>
+          <t>15/06/2026 15:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19/06/2026 03:21</t>
+          <t>18/06/2026 19:11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0003259-74.2026.8.16.0000</t>
+          <t>0062635-59.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>17/06/2026 13:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>17/06/2026 13:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>18/06/2026 19:20</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0008238-79.2018.8.16.0026</t>
+          <t>0001946-21.2024.8.16.0074</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19/10/2021</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>12/06/2026 15:13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>18/06/2026 18:51</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0002402-80.2023.8.16.0146</t>
+          <t>0024088-13.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>12/06/2026 13:33</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>12/06/2026 13:33</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19/06/2026 02:01</t>
+          <t>18/06/2026 17:50</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0001450-02.2020.8.16.0019</t>
+          <t>0001101-82.2025.8.16.0064</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telefonia</t>
+          <t>Cédula Hipotecária</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>12/06/2026 14:23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19/06/2026 02:40</t>
+          <t>18/06/2026 17:50</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0041907-94.2024.8.16.0000</t>
+          <t>0000863-07.2022.8.16.0052</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição de indébito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>11/06/2026 13:43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>17/06/2026 18:12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0001330-11.2023.8.16.0000</t>
+          <t>0015887-32.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>11/06/2026 14:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18/06/2026 23:22</t>
+          <t>17/06/2026 18:20</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0001427-66.2015.8.16.0137</t>
+          <t>0012526-07.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>10/06/2026 14:23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18/06/2026 23:41</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0003045-83.2022.8.16.0013</t>
+          <t>0000936-38.2011.8.16.0060</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Estelionato</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19/06/2026 00:10</t>
+          <t>17/06/2026 19:50</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0093262-46.2024.8.16.0000</t>
+          <t>0004046-67.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental | Processo Legislativo</t>
+          <t>Pagamento Indevido</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>10/06/2026 15:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/06/2026 00:31</t>
+          <t>17/06/2026 20:10</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0001860-37.2022.8.16.0004</t>
+          <t>0036070-97.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ICMS/ Imposto sobre Circulação de Mercadorias</t>
+          <t>Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>02/07/2021</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08/06/2026 13:13</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>08/06/2026 13:13</t>
+          <t>16/06/2026 14:13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19/06/2026 00:31</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0070693-17.2025.8.16.0000</t>
+          <t>0009138-72.2012.8.16.0026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Prisão Preventiva</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>31/08/2021</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>17/06/2026 14:33</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>19/06/2026 00:51</t>
+          <t>17/06/2026 20:40</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0001955-93.2025.8.16.0026</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>08/06/2026 14:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18/06/2026 22:31</t>
+          <t>17/06/2026 21:12</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0057279-49.2025.8.16.0000</t>
+          <t>0024646-82.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Assistência Judiciária Gratuita</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15/06/2026 15:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>15/06/2026 15:03</t>
+          <t>10/06/2026 16:33</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18/06/2026 19:11</t>
+          <t>17/06/2026 21:51</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0062635-59.2024.8.16.0000</t>
+          <t>0000679-63.2022.8.16.0048</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Promoção</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>15/06/2026 13:53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18/06/2026 19:20</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0001946-21.2024.8.16.0074</t>
+          <t>0112463-58.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>12/06/2026 13:23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18/06/2026 18:51</t>
+          <t>17/06/2026 23:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0024088-13.2025.8.16.0000</t>
+          <t>0005682-75.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>16/06/2026 14:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18/06/2026 17:50</t>
+          <t>17/06/2026 23:40</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0001101-82.2025.8.16.0064</t>
+          <t>0017293-88.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cédula Hipotecária</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>12/06/2026 15:03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/06/2026 17:50</t>
+          <t>18/06/2026 00:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0009489-18.2015.8.16.0001</t>
+          <t>0052023-33.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>14/08/2023</t>
+          <t>11/08/2023</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>09/06/2026 14:33</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>09/06/2026 14:33</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>18/06/2026 00:10</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0015612-98.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Sistema Financeiro da Habitação | Seguro</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>15/06/2026 12:16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>18/06/2026 00:50</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0003761-91.2024.8.16.0126</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>18/06/2026 01:30</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0010170-10.2023.8.16.0000</t>
+          <t>0003468-89.2019.8.16.0064</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda | Legitimidade Ativa e Passiva | Honorários Advocatícios</t>
+          <t>Parceria Agrícola e/ou pecuária</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>09/06/2026 17:03</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17/06/2026 19:11</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0000797-55.2023.8.16.0096</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Promessa de Compra e Venda</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>18/06/2026 02:01</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0004556-02.2002.8.16.0019</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Depósito</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>10/06/2026 13:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>18/06/2026 02:20</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0099021-88.2024.8.16.0000</t>
+          <t>0046717-35.2012.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>09/06/2026 17:33</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>18/06/2026 03:13</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0017760-67.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Vícios de Construção</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>16/06/2026 15:03</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>16/06/2026 15:03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>18/06/2026 04:23</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0036070-97.2020.8.16.0000</t>
+          <t>0000105-96.2020.8.16.0052</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>02/07/2021</t>
+          <t>14/01/2022</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>12/06/2026 14:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>18/06/2026 04:30</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0009138-72.2012.8.16.0026</t>
+          <t>0005159-54.2019.8.16.0189</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>17/06/2026 14:53</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>18/06/2026 06:05</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0009827-23.2022.8.16.0170</t>
+          <t>0131308-07.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>18/06/2026 06:50</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0024646-82.2025.8.16.0000</t>
+          <t>0009888-66.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Aquisição</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>28/08/2024</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>16/06/2026 13:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>18/06/2026 07:20</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0000679-63.2022.8.16.0048</t>
+          <t>0002350-52.2009.8.16.0089</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Promoção</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>10/06/2026 16:03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 08:21</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0007390-80.2018.8.16.0030</t>
+          <t>0034028-70.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indenização Trabalhista</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>02/09/2020</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>09/06/2026 13:43</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>17/06/2026 22:50</t>
+          <t>18/06/2026 09:11</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0112463-58.2023.8.16.0000</t>
+          <t>0031761-15.2016.8.16.0019</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Usucapião Extraordinária</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>11/06/2026 14:13</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>11/06/2026 14:13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>18/06/2026 12:14</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0013575-85.2022.8.16.0001</t>
+          <t>0000395-70.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/04/2023</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>09/06/2026 20:13</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>17/06/2026 23:14</t>
+          <t>18/06/2026 12:22</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0005682-75.2024.8.16.0000</t>
+          <t>0002667-23.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4687,22 +4687,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>11/05/2023</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>10/06/2026 17:13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>17/06/2026 23:40</t>
+          <t>18/06/2026 12:22</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0017293-88.2025.8.16.0000</t>
+          <t>0000881-90.2009.8.16.0114</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>23/07/2024</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>16/06/2026 13:43</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>16/06/2026 13:43</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/06/2026 00:00</t>
+          <t>18/06/2026 12:35</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0052023-33.2022.8.16.0000</t>
+          <t>0090734-39.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Incorporação Imobiliária | Enriquecimento sem Causa | Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>11/08/2023</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/06/2026 00:10</t>
+          <t>18/06/2026 12:44</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0015612-98.2016.8.16.0000</t>
+          <t>0009124-78.2023.8.16.0131</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Corretagem</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>10/06/2026 14:03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/06/2026 00:50</t>
+          <t>18/06/2026 13:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,37 +4860,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0003761-91.2024.8.16.0126</t>
+          <t>0002519-94.2018.8.16.0001</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>01/06/2023</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17/06/2026 08:43</t>
+          <t>17/06/2026 15:03</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>17/06/2026 08:43</t>
+          <t>17/06/2026 15:03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/06/2026 01:30</t>
+          <t>18/06/2026 13:40</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0003468-89.2019.8.16.0064</t>
+          <t>0004654-85.2017.8.16.0075</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4917,27 +4917,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>10/06/2026 15:43</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>10/06/2026 15:43</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>18/06/2026 02:01</t>
+          <t>18/06/2026 15:30</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0000797-55.2023.8.16.0096</t>
+          <t>0097171-33.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda</t>
+          <t>Prestação de Serviços | Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>28/01/2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17/06/2026 14:23</t>
+          <t>10/06/2026 15:43</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>17/06/2026 14:23</t>
+          <t>10/06/2026 15:43</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/06/2026 02:01</t>
+          <t>18/06/2026 16:31</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0004556-02.2002.8.16.0019</t>
+          <t>0108975-95.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5011,27 +5011,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Depósito</t>
+          <t>Cédula de Crédito Rural | Cessão de Crédito</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>10/06/2026 13:33</t>
+          <t>16/06/2026 16:43</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>10/06/2026 13:33</t>
+          <t>16/06/2026 16:43</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/06/2026 02:20</t>
+          <t>16/06/2026 22:51</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0046717-35.2012.8.16.0000</t>
+          <t>0021100-55.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
+          <t>Tratamento médico-hospitalar</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>16/06/2026 13:53</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>16/06/2026 13:53</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/06/2026 03:13</t>
+          <t>17/06/2026 00:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0017760-67.2025.8.16.0000</t>
+          <t>0000478-26.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>11/06/2026 13:53</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>18/06/2026 04:23</t>
+          <t>17/06/2026 00:21</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,37 +5142,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0000105-96.2020.8.16.0052</t>
+          <t>0002424-23.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Servidão Administrativa | Efeito Suspensivo a Recurso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>14/01/2022</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>12/06/2026 14:33</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>12/06/2026 14:33</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18/06/2026 04:30</t>
+          <t>17/06/2026 00:30</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0019169-66.2011.8.16.0001</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23/06/2026 13:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23/06/2026 13:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:50</t>
+          <t>05/07/2026 07:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,37 +536,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0006159-21.2024.8.16.0058</t>
+          <t>0031444-40.2017.8.16.0000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>19/03/2021</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>16/06/2026 15:53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>05/07/2026 07:43</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0009293-49.2009.8.16.0004</t>
+          <t>0037607-38.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pensão</t>
+          <t>Previdência privada | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>27/01/2021</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01/07/2026 08:51</t>
+          <t>05/07/2026 07:22</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0006993-31.2021.8.16.0025</t>
+          <t>0033187-72.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>16/06/2026 16:13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01/07/2026 09:14</t>
+          <t>05/07/2026 07:23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000615-03.2021.8.16.0076</t>
+          <t>0001330-11.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>16/06/2026 16:03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>16/06/2026 16:03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01/07/2026 09:14</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0100788-64.2024.8.16.0000</t>
+          <t>0123109-93.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Crédito Rural</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16/06/2026 14:33</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16/06/2026 14:33</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01/07/2026 06:50</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000763-58.2023.8.16.0168</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01/07/2026 06:50</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0026162-57.2023.8.16.0017</t>
+          <t>0001427-66.2015.8.16.0137</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Contratos Bancários</t>
+          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>16/06/2026 18:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01/07/2026 04:30</t>
+          <t>05/07/2026 00:09</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01/07/2026 05:10</t>
+          <t>05/07/2026 00:19</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0071243-12.2025.8.16.0000</t>
+          <t>0006993-31.2021.8.16.0025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19/06/2026 13:34</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19/06/2026 13:34</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01/07/2026 05:40</t>
+          <t>05/07/2026 00:23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0014974-89.2021.8.16.0000</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16/04/2022</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26/06/2026 15:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26/06/2026 15:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01/07/2026 06:01</t>
+          <t>05/07/2026 00:24</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0002415-17.2024.8.16.0123</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Edital</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01/07/2026 06:20</t>
+          <t>05/07/2026 00:40</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0128373-91.2024.8.16.0000</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23/06/2026 14:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23/06/2026 14:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01/07/2026 03:50</t>
+          <t>05/07/2026 00:47</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0000740-41.2019.8.16.0043</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Peculato | Regime inicial | Desclassificação</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>02/09/2025</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23/06/2026 16:03</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23/06/2026 16:03</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01/07/2026 04:00</t>
+          <t>05/07/2026 00:54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0148132-07.2025.8.16.0000</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latrocínio</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26/06/2026 18:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26/06/2026 18:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01/07/2026 03:22</t>
+          <t>05/07/2026 00:56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001444-85.2024.8.16.0170</t>
+          <t>0049892-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cartão de Crédito | Práticas Abusivas | Indenização por Dano Moral | Dever de Informação</t>
+          <t>Desapropriação Indireta</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16/06/2026 14:43</t>
+          <t>22/06/2026 14:03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16/06/2026 14:43</t>
+          <t>22/06/2026 14:03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22/06/2026 15:21</t>
+          <t>05/07/2026 01:02</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0016517-88.2025.8.16.0000</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19/06/2026 15:33</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19/06/2026 15:33</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22/06/2026 14:59</t>
+          <t>05/07/2026 01:07</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0026929-78.2025.8.16.0000</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16/06/2026 15:23</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22/06/2026 14:59</t>
+          <t>05/07/2026 01:15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001930-24.2022.8.16.0014</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22/06/2026 15:01</t>
+          <t>05/07/2026 01:16</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0026917-64.2025.8.16.0000</t>
+          <t>0012630-20.2024.8.16.0069</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22/06/2026 15:07</t>
+          <t>05/07/2026 01:28</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0005432-43.2020.8.16.0045</t>
+          <t>0026917-64.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito</t>
+          <t>Prova Oral</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>16/06/2026 19:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>22/06/2026 15:07</t>
+          <t>05/07/2026 01:29</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0038288-93.2023.8.16.0000</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08/03/2024</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22/06/2026 15:15</t>
+          <t>05/07/2026 01:41</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0033187-72.2023.8.16.0001</t>
+          <t>0062635-59.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Despesas Condominiais</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>01/04/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>17/06/2026 13:43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>17/06/2026 13:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>22/06/2026 14:26</t>
+          <t>05/07/2026 01:46</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,37 +1570,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0001368-54.2020.8.16.0153</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22/06/2026 14:43</t>
+          <t>05/07/2026 01:48</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0031444-40.2017.8.16.0000</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19/03/2021</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22/06/2026 14:54</t>
+          <t>05/07/2026 02:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0014789-12.2025.8.16.0000</t>
+          <t>0041907-94.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Aplicação da Pena</t>
+          <t>Contratos Bancários | Repetição de indébito</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>16/06/2026 18:23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>16/06/2026 18:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22/06/2026 14:19</t>
+          <t>05/07/2026 02:01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0015429-80.2023.8.16.0001</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16/06/2026 16:53</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22/06/2026 14:23</t>
+          <t>05/07/2026 02:08</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0010287-32.2022.8.16.0001</t>
+          <t>0097321-77.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pagamento em Consignação</t>
+          <t>Execução Contratual</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15/10/2024</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>19/06/2026 14:33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16/06/2026 18:43</t>
+          <t>19/06/2026 14:33</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19/06/2026 15:41</t>
+          <t>05/07/2026 02:09</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0133603-17.2024.8.16.0000</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seguro | Cláusulas Abusivas | Cumprimento Provisório de Sentença</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19/06/2026 16:30</t>
+          <t>05/07/2026 02:20</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0010638-75.2023.8.16.0031</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Controle de Constitucionalidade | Nulidade - Intimação Sem Observância das Prescrições Legais</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11/06/2026 15:33</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19/06/2026 12:11</t>
+          <t>05/07/2026 02:25</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0045791-34.2024.8.16.0000</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Seguro</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19/06/2026 12:20</t>
+          <t>05/07/2026 02:27</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0054268-12.2025.8.16.0000</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Industrial</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>15/06/2026 16:23</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19/06/2026 13:21</t>
+          <t>05/07/2026 02:33</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0005394-95.2022.8.16.0001</t>
+          <t>0003045-83.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Estelionato</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>07/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>18/06/2026 13:13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>18/06/2026 13:13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19/06/2026 13:32</t>
+          <t>05/07/2026 02:38</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0039522-68.2023.8.16.0014</t>
+          <t>0070693-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cobrança | Honorários Advocatícios</t>
+          <t>Homicídio Qualificado | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>17/06/2026 13:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>17/06/2026 13:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19/06/2026 14:13</t>
+          <t>05/07/2026 02:39</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0007014-41.2023.8.16.0185</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19/06/2026 10:50</t>
+          <t>05/07/2026 02:40</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0003590-95.2022.8.16.0194</t>
+          <t>0045791-34.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Indenização por Dano Material | Seguro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10/06/2026 15:53</t>
+          <t>16/06/2026 17:43</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19/06/2026 11:20</t>
+          <t>05/07/2026 02:44</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,37 +2181,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0000588-76.2020.8.16.0004</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12/06/2026 13:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19/06/2026 11:40</t>
+          <t>05/07/2026 02:50</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0004131-72.2012.8.16.0035</t>
+          <t>0001450-02.2020.8.16.0019</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Telefonia</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>02/07/2024</t>
+          <t>04/10/2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>16/06/2026 11:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>16/06/2026 11:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19/06/2026 12:03</t>
+          <t>05/07/2026 02:52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0093845-31.2024.8.16.0000</t>
+          <t>0062792-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Assistência Judiciária Gratuita</t>
+          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10/06/2026 17:03</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>05/07/2026 02:52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0002402-77.2008.8.16.0026</t>
+          <t>0021859-82.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária | Defeito, nulidade ou anulação | Nulidade - Ausência de publicidade de decisão</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22/06/2022</t>
+          <t>23/09/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>17/06/2026 14:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>05/07/2026 02:56</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0011249-17.2016.8.16.0017</t>
+          <t>0099764-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Cheque</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>24/06/2022</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>19/06/2026 15:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>19/06/2026 15:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19/06/2026 09:40</t>
+          <t>05/07/2026 02:56</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0014258-55.2014.8.16.0017</t>
+          <t>0000763-58.2023.8.16.0168</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>19/06/2026 07:20</t>
+          <t>05/07/2026 02:57</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0003888-32.2019.8.16.0117</t>
+          <t>0036579-57.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>29/03/2022</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>19/06/2026 16:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>19/06/2026 16:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>19/06/2026 08:00</t>
+          <t>05/07/2026 02:58</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0009778-70.2023.8.16.0194</t>
+          <t>0105436-87.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>19/06/2026 05:51</t>
+          <t>05/07/2026 03:06</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0098136-74.2024.8.16.0000</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Transferência de cotas | Indenização por Dano Material | Honorários Advocatícios | Provas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10/06/2026 17:23</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>19/06/2026 06:10</t>
+          <t>05/07/2026 03:14</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,37 +2604,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0003259-74.2026.8.16.0000</t>
+          <t>0000634-51.2021.8.16.0062</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>16/06/2026 14:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>16/06/2026 14:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>05/07/2026 03:16</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0008238-79.2018.8.16.0026</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Enriquecimento sem Causa | Práticas Abusivas | Indenização por Dano Material | Cédula de Crédito Bancário</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19/10/2021</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>16/06/2026 19:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>19/06/2026 04:42</t>
+          <t>05/07/2026 03:18</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0002402-80.2023.8.16.0146</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09/07/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19/06/2026 02:01</t>
+          <t>05/07/2026 03:19</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0001450-02.2020.8.16.0019</t>
+          <t>0083802-27.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telefonia</t>
+          <t>Cessão de Crédito | Consórcio</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19/06/2026 02:40</t>
+          <t>05/07/2026 03:22</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0041907-94.2024.8.16.0000</t>
+          <t>0100788-64.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição de indébito</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>16/06/2026 14:33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>16/06/2026 14:33</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>19/06/2026 01:42</t>
+          <t>05/07/2026 03:23</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0001330-11.2023.8.16.0000</t>
+          <t>0066804-47.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Empréstimo consignado</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>18/06/2026 13:33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>18/06/2026 13:33</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18/06/2026 23:22</t>
+          <t>05/07/2026 03:23</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0001427-66.2015.8.16.0137</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18/06/2026 23:41</t>
+          <t>05/07/2026 03:35</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0003045-83.2022.8.16.0013</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estelionato</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>19/06/2026 00:10</t>
+          <t>05/07/2026 03:38</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0093262-46.2024.8.16.0000</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Ambiental | Processo Legislativo</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19/06/2026 00:31</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0070693-17.2025.8.16.0000</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Prisão Preventiva</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19/06/2026 00:51</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0057279-49.2025.8.16.0000</t>
+          <t>0009827-23.2022.8.16.0170</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Assistência Judiciária Gratuita</t>
+          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>15/06/2026 15:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>15/06/2026 15:03</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18/06/2026 19:11</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0062635-59.2024.8.16.0000</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>18/06/2026 19:20</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0001946-21.2024.8.16.0074</t>
+          <t>0006810-30.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>12/06/2026 15:13</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18/06/2026 18:51</t>
+          <t>05/07/2026 03:47</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0024088-13.2025.8.16.0000</t>
+          <t>0017760-67.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Vícios de Construção</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>16/06/2026 15:03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>12/06/2026 13:33</t>
+          <t>16/06/2026 15:03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18/06/2026 17:50</t>
+          <t>05/07/2026 03:49</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0001101-82.2025.8.16.0064</t>
+          <t>0001874-75.2022.8.16.0083</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cédula Hipotecária</t>
+          <t>Crimes do Sistema Nacional de Armas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>19/06/2026 16:53</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>12/06/2026 14:23</t>
+          <t>19/06/2026 16:53</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18/06/2026 17:50</t>
+          <t>05/07/2026 03:50</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0000863-07.2022.8.16.0052</t>
+          <t>0016569-38.2022.8.16.0017</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11/06/2026 13:43</t>
+          <t>17/06/2026 14:43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17/06/2026 18:12</t>
+          <t>05/07/2026 03:59</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0015887-32.2025.8.16.0000</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>11/06/2026 14:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17/06/2026 18:20</t>
+          <t>05/07/2026 04:02</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0012526-07.2025.8.16.0000</t>
+          <t>0036612-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>10/06/2026 14:23</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>05/07/2026 04:02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0000936-38.2011.8.16.0060</t>
+          <t>0016824-42.2021.8.16.0013</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>21/02/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>15/06/2026 16:13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>15/06/2026 16:13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17/06/2026 19:50</t>
+          <t>05/07/2026 04:04</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0004046-67.2021.8.16.0004</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pagamento Indevido</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10/06/2026 15:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>17/06/2026 20:10</t>
+          <t>05/07/2026 04:13</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0036070-97.2020.8.16.0000</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>02/07/2021</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>16/06/2026 14:13</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>05/07/2026 04:14</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0009138-72.2012.8.16.0026</t>
+          <t>0001987-07.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>31/08/2021</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17/06/2026 14:33</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17/06/2026 20:40</t>
+          <t>05/07/2026 04:14</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0009827-23.2022.8.16.0170</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17/06/2026 21:12</t>
+          <t>05/07/2026 04:17</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0024646-82.2025.8.16.0000</t>
+          <t>0082420-09.2017.8.16.0014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Usucapião Extraordinária</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>19/06/2026 13:53</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10/06/2026 16:33</t>
+          <t>19/06/2026 13:53</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17/06/2026 21:51</t>
+          <t>05/07/2026 04:25</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0000679-63.2022.8.16.0048</t>
+          <t>0000813-54.2024.8.16.0102</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Promoção</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21/09/2023</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>15/06/2026 13:53</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>05/07/2026 04:36</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0112463-58.2023.8.16.0000</t>
+          <t>0059414-60.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>12/06/2026 13:23</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>05/07/2026 04:44</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0005682-75.2024.8.16.0000</t>
+          <t>0001417-61.2021.8.16.0056</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>16/06/2026 14:23</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17/06/2026 23:40</t>
+          <t>05/07/2026 04:45</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0017293-88.2025.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>12/06/2026 15:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18/06/2026 00:00</t>
+          <t>05/07/2026 04:48</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0052023-33.2022.8.16.0000</t>
+          <t>0030402-77.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Corretagem</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>11/08/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18/06/2026 00:10</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0015612-98.2016.8.16.0000</t>
+          <t>0131308-07.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>15/06/2026 12:16</t>
+          <t>16/06/2026 13:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>18/06/2026 00:50</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0003761-91.2024.8.16.0126</t>
+          <t>0000083-06.2025.8.16.0103</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Reivindicação | Provas</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17/06/2026 08:43</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17/06/2026 08:43</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18/06/2026 01:30</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0003468-89.2019.8.16.0064</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Parceria Agrícola e/ou pecuária</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18/06/2026 02:01</t>
+          <t>05/07/2026 04:54</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0000797-55.2023.8.16.0096</t>
+          <t>0029998-84.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Promessa de Compra e Venda</t>
+          <t>Tráfico de Drogas e Condutas Afins | Resistência</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17/06/2026 14:23</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>17/06/2026 14:23</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18/06/2026 02:01</t>
+          <t>05/07/2026 04:55</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0004556-02.2002.8.16.0019</t>
+          <t>0128112-29.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Depósito</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>10/06/2026 13:33</t>
+          <t>18/06/2026 13:23</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10/06/2026 13:33</t>
+          <t>18/06/2026 13:23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18/06/2026 02:20</t>
+          <t>05/07/2026 04:55</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,37 +4202,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0046717-35.2012.8.16.0000</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gratificações Por Atividades Específicas | Abuso de Poder</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18/06/2026 03:13</t>
+          <t>05/07/2026 05:08</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0017760-67.2025.8.16.0000</t>
+          <t>0021062-79.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Oferta e Publicidade</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18/06/2026 04:23</t>
+          <t>05/07/2026 05:17</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0000105-96.2020.8.16.0052</t>
+          <t>0019201-83.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Liquidação</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>14/01/2022</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>12/06/2026 14:53</t>
+          <t>15/06/2026 13:33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18/06/2026 04:30</t>
+          <t>05/07/2026 05:17</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0005159-54.2019.8.16.0189</t>
+          <t>0003761-91.2024.8.16.0126</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Posse | Requerimento de Reintegração de Posse | Provas | Cerceamento de Defesa</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/06/2026 14:53</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/06/2026 14:53</t>
+          <t>17/06/2026 08:43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18/06/2026 06:05</t>
+          <t>05/07/2026 05:17</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0131308-07.2024.8.16.0000</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18/06/2026 06:50</t>
+          <t>05/07/2026 05:23</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0009888-66.2023.8.16.0001</t>
+          <t>0024386-41.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Aquisição</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>28/08/2024</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>16/06/2026 13:13</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18/06/2026 07:20</t>
+          <t>05/07/2026 05:25</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0002350-52.2009.8.16.0089</t>
+          <t>0109651-43.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>10/06/2026 16:03</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18/06/2026 08:21</t>
+          <t>05/07/2026 05:27</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0034028-70.2023.8.16.0000</t>
+          <t>0002415-17.2024.8.16.0123</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Edital</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30/10/2024</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>18/06/2026 09:11</t>
+          <t>05/07/2026 05:29</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0031761-15.2016.8.16.0019</t>
+          <t>0002669-34.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Registrado na ANVISA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>11/06/2026 14:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>11/06/2026 14:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18/06/2026 12:14</t>
+          <t>05/07/2026 05:33</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0000395-70.2020.8.16.0001</t>
+          <t>0000994-81.2021.8.16.0095</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>27/04/2023</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18/06/2026 12:22</t>
+          <t>05/07/2026 05:39</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0002667-23.2019.8.16.0017</t>
+          <t>0020770-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>11/05/2023</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>10/06/2026 17:13</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18/06/2026 12:22</t>
+          <t>05/07/2026 05:40</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0000881-90.2009.8.16.0114</t>
+          <t>0073849-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>23/07/2024</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16/06/2026 13:43</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>16/06/2026 13:43</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/06/2026 12:35</t>
+          <t>05/07/2026 05:50</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,37 +4766,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0090734-39.2024.8.16.0000</t>
+          <t>0001590-04.2023.8.16.0028</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Incorporação Imobiliária | Enriquecimento sem Causa | Confissão/Composição de Dívida</t>
+          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>18/07/2024</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/06/2026 12:44</t>
+          <t>05/07/2026 05:51</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0009124-78.2023.8.16.0131</t>
+          <t>0003888-32.2019.8.16.0117</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>29/03/2022</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>10/06/2026 14:03</t>
+          <t>15/06/2026 11:59</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>18/06/2026 13:00</t>
+          <t>05/07/2026 05:54</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0002519-94.2018.8.16.0001</t>
+          <t>0001988-16.2008.8.16.0047</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01/06/2023</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>17/06/2026 15:03</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>17/06/2026 15:03</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18/06/2026 13:40</t>
+          <t>05/07/2026 05:54</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0004654-85.2017.8.16.0075</t>
+          <t>0041235-44.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4922,22 +4922,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>18/06/2026 15:30</t>
+          <t>05/07/2026 05:56</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0097171-33.2023.8.16.0000</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Prescrição e Decadência</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>28/01/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>10/06/2026 15:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>18/06/2026 16:31</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0108975-95.2023.8.16.0000</t>
+          <t>0017946-36.2021.8.16.0031</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5011,27 +5011,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural | Cessão de Crédito</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>16/06/2026 16:43</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>16/06/2026 16:43</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>16/06/2026 22:51</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0021100-55.2021.8.16.0001</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>16/06/2026 13:53</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>16/06/2026 13:53</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>17/06/2026 00:00</t>
+          <t>05/07/2026 06:21</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0000478-26.2022.8.16.0160</t>
+          <t>0000209-04.2022.8.16.0122</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>21/05/2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>23/06/2026 15:23</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>11/06/2026 13:53</t>
+          <t>23/06/2026 15:23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>17/06/2026 00:21</t>
+          <t>05/07/2026 06:30</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0002424-23.2025.8.16.0000</t>
+          <t>0039522-68.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5152,27 +5152,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Servidão Administrativa | Efeito Suspensivo a Recurso</t>
+          <t>Cobrança | Honorários Advocatícios</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>12/06/2026 14:33</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>12/06/2026 14:33</t>
+          <t>16/06/2026 19:03</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>17/06/2026 00:30</t>
+          <t>05/07/2026 06:32</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0051057-70.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Mandado de Segurança</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Concurso para serventia extrajudicial | Prova Oral</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>08/11/2023</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>18/06/2026 13:33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>18/06/2026 13:33</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/07/2026 07:40</t>
+          <t>05/07/2026 07:34</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,37 +536,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0031444-40.2017.8.16.0000</t>
+          <t>0008465-36.2019.8.16.0058</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19/03/2021</t>
+          <t>27/10/2023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>16/06/2026 15:33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16/06/2026 15:53</t>
+          <t>16/06/2026 15:33</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/07/2026 07:43</t>
+          <t>05/07/2026 07:34</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0037607-38.2014.8.16.0001</t>
+          <t>0014508-95.2022.8.16.0021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Previdência privada | Indenização por Dano Material</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27/01/2021</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>23/06/2026 18:33</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>23/06/2026 18:33</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/07/2026 07:22</t>
+          <t>05/07/2026 07:24</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0033187-72.2023.8.16.0001</t>
+          <t>0017750-30.2019.8.16.0001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>23/09/2024</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>17/06/2026 13:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16/06/2026 16:13</t>
+          <t>17/06/2026 13:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/07/2026 07:23</t>
+          <t>05/07/2026 07:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0001330-11.2023.8.16.0000</t>
+          <t>0009828-64.2017.8.16.0014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>28/01/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16/06/2026 16:03</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>04/07/2026 23:55</t>
+          <t>05/07/2026 07:02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0123109-93.2024.8.16.0000</t>
+          <t>0000190-14.2016.8.16.0120</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Crédito Rural</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>04/07/2026 23:55</t>
+          <t>05/07/2026 07:12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0102296-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Subsídios</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>04/07/2026 23:55</t>
+          <t>05/07/2026 07:20</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001427-66.2015.8.16.0137</t>
+          <t>0015385-64.2023.8.16.0194</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Legitimidade Ativa e Passiva | Prestação de Serviços</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16/06/2026 18:13</t>
+          <t>17/06/2026 14:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/07/2026 00:09</t>
+          <t>05/07/2026 07:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0016204-47.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>19/11/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>23/06/2026 14:43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>23/06/2026 14:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/07/2026 00:19</t>
+          <t>05/07/2026 07:02</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0006993-31.2021.8.16.0025</t>
+          <t>0001833-80.2021.8.16.0039</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Cédula de Crédito Rural | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>01/07/2026 17:14</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>01/07/2026 17:14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/07/2026 00:23</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0089794-11.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Arrendamento Mercantil</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>23/06/2026 16:23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>23/06/2026 16:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/07/2026 00:24</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0005325-15.2021.8.16.0190</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>26/07/2024</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>23/06/2026 06:27</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>23/06/2026 06:27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/07/2026 00:40</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0084393-31.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/07/2026 00:47</t>
+          <t>05/07/2026 06:13</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0100507-45.2023.8.16.0000</t>
+          <t>0116067-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Contratos Bancários | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/07/2026 00:54</t>
+          <t>05/07/2026 06:14</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0017774-66.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Sistema Financeiro da Habitação | Seguro | Obrigação de Fazer / Não Fazer | Ônus da Prova | Competência Territorial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>12/09/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>26/06/2026 13:43</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>26/06/2026 13:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/07/2026 00:56</t>
+          <t>05/07/2026 06:15</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0049892-17.2024.8.16.0000</t>
+          <t>0046721-18.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Desapropriação Indireta</t>
+          <t>Descontos Indevidos | Servidores Inativos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22/06/2026 14:03</t>
+          <t>26/06/2026 15:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22/06/2026 14:03</t>
+          <t>26/06/2026 15:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/07/2026 01:02</t>
+          <t>05/07/2026 06:21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0000616-29.2022.8.16.0148</t>
+          <t>0035161-50.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Contrato Administrativo | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/04/2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>15/06/2026 14:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>15/06/2026 14:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/07/2026 01:07</t>
+          <t>05/07/2026 06:22</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0134270-66.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Tráfico de Drogas e Condutas Afins | Jurisdição e Competência</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>16/06/2026 15:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>16/06/2026 15:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/07/2026 01:15</t>
+          <t>05/07/2026 06:32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0011577-68.2008.8.16.0035</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Sustação de Protesto</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>10/02/2023</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/07/2026 01:16</t>
+          <t>05/07/2026 06:32</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0012630-20.2024.8.16.0069</t>
+          <t>0008464-98.2020.8.16.0031</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>24/06/2026 13:53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>24/06/2026 13:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/07/2026 01:28</t>
+          <t>05/07/2026 06:02</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0026917-64.2025.8.16.0000</t>
+          <t>0004522-78.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prova Oral</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16/06/2026 19:53</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/07/2026 01:29</t>
+          <t>05/07/2026 05:53</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0007600-54.2020.8.16.0130</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Acidente de Trânsito | Acidente de Trânsito</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>29/06/2026 13:43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>29/06/2026 13:43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/07/2026 01:41</t>
+          <t>05/07/2026 05:53</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0062635-59.2024.8.16.0000</t>
+          <t>0053452-98.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Despesas Condominiais</t>
+          <t>Prestação de Serviços | Liminar | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>29/09/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17/06/2026 13:43</t>
+          <t>16/06/2026 13:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/07/2026 01:46</t>
+          <t>05/07/2026 05:54</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0007160-21.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/07/2026 01:48</t>
+          <t>05/07/2026 06:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0017789-20.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>19/06/2026 15:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>19/06/2026 15:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/07/2026 02:00</t>
+          <t>05/07/2026 05:39</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0041907-94.2024.8.16.0000</t>
+          <t>0043615-93.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição de indébito</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>16/06/2026 18:23</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/07/2026 02:01</t>
+          <t>05/07/2026 05:40</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0000877-47.2012.8.16.0179</t>
+          <t>0101840-95.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>19/06/2026 16:23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>19/06/2026 16:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/07/2026 02:08</t>
+          <t>05/07/2026 05:43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0097321-77.2024.8.16.0000</t>
+          <t>0034472-52.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Execução Contratual</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19/06/2026 14:33</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19/06/2026 14:33</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/07/2026 02:09</t>
+          <t>05/07/2026 05:43</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0011983-24.2013.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Sistema Financeiro da Habitação | Seguro | Competência Territorial</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>18/06/2026 14:03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>18/06/2026 14:03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/07/2026 02:20</t>
+          <t>05/07/2026 05:46</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0070733-33.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/07/2026 02:25</t>
+          <t>05/07/2026 05:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0103089-81.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05/07/2026 02:27</t>
+          <t>05/07/2026 05:51</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0121007-98.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>23/06/2026 18:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>23/06/2026 18:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>05/07/2026 02:33</t>
+          <t>05/07/2026 05:29</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0003045-83.2022.8.16.0013</t>
+          <t>0007434-83.2020.8.16.0045</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estelionato</t>
+          <t>Perdas e Danos | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>18/06/2026 13:13</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>05/07/2026 02:38</t>
+          <t>05/07/2026 05:30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0070693-17.2025.8.16.0000</t>
+          <t>0002217-04.2021.8.16.0149</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado | Prisão Preventiva</t>
+          <t>Furto Privilegiado</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>13/03/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>16/06/2026 17:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17/06/2026 13:03</t>
+          <t>16/06/2026 17:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>05/07/2026 02:39</t>
+          <t>05/07/2026 05:26</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0073464-02.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Expurgos Inflacionários / Planos Econômicos | Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>15/06/2026 14:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>15/06/2026 14:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>05/07/2026 02:40</t>
+          <t>05/07/2026 05:27</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0045791-34.2024.8.16.0000</t>
+          <t>0132112-72.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Seguro</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>02/07/2026 13:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16/06/2026 17:43</t>
+          <t>02/07/2026 13:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>05/07/2026 02:44</t>
+          <t>05/07/2026 05:02</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,37 +2181,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0017978-39.2024.8.16.0030</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>17/06/2026 13:33</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>17/06/2026 13:33</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>05/07/2026 02:50</t>
+          <t>05/07/2026 05:12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,37 +2228,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0001450-02.2020.8.16.0019</t>
+          <t>0023893-74.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Telefonia</t>
+          <t>Capitalização e Previdência Privada</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04/10/2024</t>
+          <t>25/01/2023</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>23/06/2026 14:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16/06/2026 11:33</t>
+          <t>23/06/2026 14:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05/07/2026 02:52</t>
+          <t>05/07/2026 05:13</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0062792-32.2024.8.16.0000</t>
+          <t>0011082-92.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
+          <t>Seguro | Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>20/06/2024</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>24/06/2026 15:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>24/06/2026 15:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/07/2026 02:52</t>
+          <t>05/07/2026 05:15</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0021859-82.2022.8.16.0001</t>
+          <t>0014013-60.2020.8.16.0170</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>23/09/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17/06/2026 14:23</t>
+          <t>23/06/2026 20:03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17/06/2026 14:23</t>
+          <t>23/06/2026 20:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/07/2026 02:56</t>
+          <t>05/07/2026 04:47</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0099764-98.2024.8.16.0000</t>
+          <t>0037519-90.2020.8.16.0000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cheque</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>01/09/2022</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19/06/2026 15:23</t>
+          <t>01/07/2026 14:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>19/06/2026 15:23</t>
+          <t>01/07/2026 14:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05/07/2026 02:56</t>
+          <t>05/07/2026 04:50</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0000763-58.2023.8.16.0168</t>
+          <t>0004625-96.2019.8.16.0129</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>16/06/2026 17:03</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>16/06/2026 17:03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05/07/2026 02:57</t>
+          <t>05/07/2026 04:51</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0036579-57.2023.8.16.0021</t>
+          <t>0009860-43.2022.8.16.0160</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Dever de Informação | Práticas Abusivas | Oferta e Publicidade | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19/06/2026 16:13</t>
+          <t>16/06/2026 13:53</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>19/06/2026 16:13</t>
+          <t>16/06/2026 13:53</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05/07/2026 02:58</t>
+          <t>05/07/2026 04:56</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0105436-87.2024.8.16.0000</t>
+          <t>0009680-17.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Previdência privada | Juros</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05/07/2026 03:06</t>
+          <t>05/07/2026 04:58</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0005231-42.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>16/06/2026 13:03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/07/2026 03:14</t>
+          <t>05/07/2026 04:26</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0000634-51.2021.8.16.0062</t>
+          <t>0000083-40.2023.8.16.0082</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Crimes de Trânsito</t>
+          <t>Seguro | Pagamento</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16/06/2026 14:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>16/06/2026 14:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/07/2026 03:16</t>
+          <t>05/07/2026 04:29</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0114332-22.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>23/06/2026 16:03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>23/06/2026 16:03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>05/07/2026 03:18</t>
+          <t>05/07/2026 04:31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0000587-56.2022.8.16.0090</t>
+          <t>0007662-86.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Crimes da Lei de licitações</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>26/06/2026 18:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>26/06/2026 18:53</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>05/07/2026 03:19</t>
+          <t>05/07/2026 04:32</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0012449-59.2024.8.16.0185</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>04/07/2026 21:38</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0017946-36.2021.8.16.0031</t>
+          <t>0015948-47.2007.8.16.0185</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5011,27 +5011,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>23/02/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>04/07/2026 21:41</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0000862-06.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Descontos Indevidos | Contribuições Previdenciárias | Decadência/Prescrição | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>05/07/2026 06:21</t>
+          <t>04/07/2026 21:41</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0000209-04.2022.8.16.0122</t>
+          <t>0011335-31.2019.8.16.0001</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>21/05/2025</t>
+          <t>05/08/2024</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>23/06/2026 15:23</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>23/06/2026 15:23</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>05/07/2026 06:30</t>
+          <t>04/07/2026 21:42</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,37 +5142,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0039522-68.2023.8.16.0014</t>
+          <t>0000944-73.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cobrança | Honorários Advocatícios</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>02/07/2026 17:13</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>16/06/2026 19:03</t>
+          <t>02/07/2026 17:13</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>05/07/2026 06:32</t>
+          <t>04/07/2026 21:44</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0051057-70.2022.8.16.0000</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Mandado de Segurança</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Concurso para serventia extrajudicial | Prova Oral</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>08/11/2023</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18/06/2026 13:33</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18/06/2026 13:33</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/07/2026 07:34</t>
+          <t>05/07/2026 07:40</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,37 +536,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0008465-36.2019.8.16.0058</t>
+          <t>0037607-38.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Previdência privada | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27/10/2023</t>
+          <t>27/01/2021</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16/06/2026 15:33</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16/06/2026 15:33</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/07/2026 07:34</t>
+          <t>05/07/2026 07:22</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0014508-95.2022.8.16.0021</t>
+          <t>0123109-93.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Crédito Rural</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23/06/2026 18:33</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23/06/2026 18:33</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/07/2026 07:24</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0017750-30.2019.8.16.0001</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23/09/2024</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17/06/2026 13:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17/06/2026 13:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/07/2026 07:33</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0009828-64.2017.8.16.0014</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28/01/2025</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/07/2026 07:02</t>
+          <t>05/07/2026 00:19</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000190-14.2016.8.16.0120</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/07/2026 07:12</t>
+          <t>05/07/2026 00:24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0102296-45.2024.8.16.0000</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Subsídios</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/07/2026 07:20</t>
+          <t>05/07/2026 00:40</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0015385-64.2023.8.16.0194</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/07/2026 07:00</t>
+          <t>05/07/2026 00:47</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0016204-47.2013.8.16.0001</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Obrigação de Fazer / Não Fazer | Indenização por Dano Material</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19/11/2024</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23/06/2026 14:43</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23/06/2026 14:43</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/07/2026 07:02</t>
+          <t>05/07/2026 00:54</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001833-80.2021.8.16.0039</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01/07/2026 17:14</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/07/2026 17:14</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>05/07/2026 00:56</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0089794-11.2023.8.16.0000</t>
+          <t>0049892-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arrendamento Mercantil</t>
+          <t>Desapropriação Indireta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23/06/2026 16:23</t>
+          <t>22/06/2026 14:03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23/06/2026 16:23</t>
+          <t>22/06/2026 14:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>05/07/2026 01:02</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0005325-15.2021.8.16.0190</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26/07/2024</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23/06/2026 06:27</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23/06/2026 06:27</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>05/07/2026 01:07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0084393-31.2023.8.16.0000</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/07/2026 06:13</t>
+          <t>05/07/2026 01:15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0116067-90.2024.8.16.0000</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/07/2026 06:14</t>
+          <t>05/07/2026 01:16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0017774-66.2016.8.16.0000</t>
+          <t>0012630-20.2024.8.16.0069</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro | Obrigação de Fazer / Não Fazer | Ônus da Prova | Competência Territorial</t>
+          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26/06/2026 13:43</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26/06/2026 13:43</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/07/2026 06:15</t>
+          <t>05/07/2026 01:28</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0046721-18.2025.8.16.0000</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Descontos Indevidos | Servidores Inativos</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26/06/2026 15:23</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26/06/2026 15:23</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/07/2026 06:21</t>
+          <t>05/07/2026 01:41</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0035161-50.2023.8.16.0000</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contrato Administrativo | Indenização por Dano Moral</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30/04/2024</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15/06/2026 14:43</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15/06/2026 14:43</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/07/2026 06:22</t>
+          <t>05/07/2026 01:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0134270-66.2025.8.16.0000</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Jurisdição e Competência</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16/06/2026 15:13</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16/06/2026 15:13</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/07/2026 06:32</t>
+          <t>05/07/2026 02:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0011577-68.2008.8.16.0035</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sustação de Protesto</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10/02/2023</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/07/2026 06:32</t>
+          <t>05/07/2026 02:08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0008464-98.2020.8.16.0031</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24/06/2026 13:53</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24/06/2026 13:53</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/07/2026 06:02</t>
+          <t>05/07/2026 02:20</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0004522-78.2025.8.16.0000</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/07/2026 05:53</t>
+          <t>05/07/2026 02:25</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0007600-54.2020.8.16.0130</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Acidente de Trânsito | Acidente de Trânsito</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29/06/2026 13:43</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29/06/2026 13:43</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/07/2026 05:53</t>
+          <t>05/07/2026 02:27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0053452-98.2023.8.16.0000</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prestação de Serviços | Liminar | Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16/06/2026 13:33</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/07/2026 05:54</t>
+          <t>05/07/2026 02:33</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0007160-21.2024.8.16.0000</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/07/2026 06:00</t>
+          <t>05/07/2026 02:40</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0017789-20.2025.8.16.0000</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19/06/2026 15:43</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19/06/2026 15:43</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/07/2026 05:39</t>
+          <t>05/07/2026 02:50</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0043615-93.2022.8.16.0019</t>
+          <t>0062792-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/07/2026 05:40</t>
+          <t>05/07/2026 02:52</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0101840-95.2024.8.16.0000</t>
+          <t>0000763-58.2023.8.16.0168</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19/06/2026 16:23</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19/06/2026 16:23</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/07/2026 05:43</t>
+          <t>05/07/2026 02:57</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0034472-52.2013.8.16.0001</t>
+          <t>0105436-87.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/07/2026 05:43</t>
+          <t>05/07/2026 03:06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0011983-24.2013.8.16.0000</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sistema Financeiro da Habitação | Seguro | Competência Territorial</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15/09/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18/06/2026 14:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18/06/2026 14:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/07/2026 05:46</t>
+          <t>05/07/2026 03:14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0070733-33.2024.8.16.0000</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/07/2026 05:47</t>
+          <t>05/07/2026 03:18</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0103089-81.2024.8.16.0000</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05/07/2026 05:51</t>
+          <t>05/07/2026 03:19</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0121007-98.2024.8.16.0000</t>
+          <t>0083802-27.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Cessão de Crédito | Consórcio</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23/06/2026 18:53</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>23/06/2026 18:53</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>05/07/2026 05:29</t>
+          <t>05/07/2026 03:22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0007434-83.2020.8.16.0045</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Perdas e Danos | Indenização por Dano Material</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>05/07/2026 05:30</t>
+          <t>05/07/2026 03:35</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,37 +2040,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0002217-04.2021.8.16.0149</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Furto Privilegiado</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13/03/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16/06/2026 17:03</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16/06/2026 17:03</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>05/07/2026 05:26</t>
+          <t>05/07/2026 03:38</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0073464-02.2024.8.16.0000</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Expurgos Inflacionários / Planos Econômicos | Cédula de Crédito Rural</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15/06/2026 14:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15/06/2026 14:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>05/07/2026 05:27</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0132112-72.2024.8.16.0000</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>02/07/2026 13:53</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>02/07/2026 13:53</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>05/07/2026 05:02</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0017978-39.2024.8.16.0030</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17/06/2026 13:33</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17/06/2026 13:33</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>05/07/2026 05:12</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0023893-74.2015.8.16.0001</t>
+          <t>0006810-30.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Capitalização e Previdência Privada</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25/01/2023</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23/06/2026 14:43</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>23/06/2026 14:43</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05/07/2026 05:13</t>
+          <t>05/07/2026 03:47</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0011082-92.2019.8.16.0017</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seguro | Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20/06/2024</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24/06/2026 15:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24/06/2026 15:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/07/2026 05:15</t>
+          <t>05/07/2026 04:02</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0014013-60.2020.8.16.0170</t>
+          <t>0036612-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23/06/2026 20:03</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23/06/2026 20:03</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/07/2026 04:47</t>
+          <t>05/07/2026 04:02</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0037519-90.2020.8.16.0000</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>01/09/2022</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01/07/2026 14:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01/07/2026 14:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05/07/2026 04:50</t>
+          <t>05/07/2026 04:13</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0004625-96.2019.8.16.0129</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08/05/2024</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>16/06/2026 17:03</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>16/06/2026 17:03</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05/07/2026 04:51</t>
+          <t>05/07/2026 04:14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0009860-43.2022.8.16.0160</t>
+          <t>0001987-07.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dever de Informação | Práticas Abusivas | Oferta e Publicidade | Indenização por Dano Moral</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16/06/2026 13:53</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>16/06/2026 13:53</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05/07/2026 04:56</t>
+          <t>05/07/2026 04:14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0009680-17.2025.8.16.0000</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Previdência privada | Juros</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05/07/2026 04:58</t>
+          <t>05/07/2026 04:17</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0005231-42.2023.8.16.0014</t>
+          <t>0000813-54.2024.8.16.0102</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>16/06/2026 13:03</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/07/2026 04:26</t>
+          <t>05/07/2026 04:36</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0000083-40.2023.8.16.0082</t>
+          <t>0059414-60.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seguro | Pagamento</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/07/2026 04:29</t>
+          <t>05/07/2026 04:44</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0114332-22.2024.8.16.0000</t>
+          <t>0001417-61.2021.8.16.0056</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cobrança de Aluguéis - Sem despejo</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23/06/2026 16:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>23/06/2026 16:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>05/07/2026 04:31</t>
+          <t>05/07/2026 04:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0007662-86.2026.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Crimes da Lei de licitações</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26/06/2026 18:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26/06/2026 18:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>05/07/2026 04:32</t>
+          <t>05/07/2026 04:48</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0083802-27.2023.8.16.0014</t>
+          <t>0030402-77.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cessão de Crédito | Consórcio</t>
+          <t>Corretagem</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>05/07/2026 03:22</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,37 +2792,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0100788-64.2024.8.16.0000</t>
+          <t>0000083-06.2025.8.16.0103</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Reivindicação | Provas</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>16/06/2026 14:33</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>16/06/2026 14:33</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>05/07/2026 03:23</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0066804-47.2024.8.16.0014</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Empréstimo consignado</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18/06/2026 13:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>18/06/2026 13:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>05/07/2026 03:23</t>
+          <t>05/07/2026 04:54</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>05/07/2026 03:35</t>
+          <t>05/07/2026 05:08</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0072332-62.2024.8.16.0014</t>
+          <t>0021062-79.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Oferta e Publicidade</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>05/07/2026 03:38</t>
+          <t>05/07/2026 05:17</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>05/07/2026 05:23</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0024386-41.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>05/07/2026 05:25</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0009827-23.2022.8.16.0170</t>
+          <t>0109651-43.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação | Indenização por Dano Moral</t>
+          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17/06/2026 14:13</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>05/07/2026 05:27</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0002415-17.2024.8.16.0123</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Edital</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>05/07/2026 05:29</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0006810-30.2021.8.16.0035</t>
+          <t>0002669-34.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
+          <t>Registrado na ANVISA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>05/07/2026 03:47</t>
+          <t>05/07/2026 05:33</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0017760-67.2025.8.16.0000</t>
+          <t>0000994-81.2021.8.16.0095</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vícios de Construção</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>16/06/2026 15:03</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>05/07/2026 03:49</t>
+          <t>05/07/2026 05:39</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0001874-75.2022.8.16.0083</t>
+          <t>0020770-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Crimes do Sistema Nacional de Armas</t>
+          <t>Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19/06/2026 16:53</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>19/06/2026 16:53</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>05/07/2026 03:50</t>
+          <t>05/07/2026 05:40</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0016569-38.2022.8.16.0017</t>
+          <t>0073849-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Inclusão Indevida em Cadastro de Inadimplentes</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17/06/2026 14:43</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>05/07/2026 03:59</t>
+          <t>05/07/2026 05:50</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0001590-04.2023.8.16.0028</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>18/07/2024</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>05/07/2026 04:02</t>
+          <t>05/07/2026 05:51</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0036612-13.2023.8.16.0000</t>
+          <t>0001988-16.2008.8.16.0047</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>05/07/2026 04:02</t>
+          <t>05/07/2026 05:54</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0016824-42.2021.8.16.0013</t>
+          <t>0041235-44.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>21/02/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>15/06/2026 16:13</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>15/06/2026 16:13</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05/07/2026 04:04</t>
+          <t>05/07/2026 05:56</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05/07/2026 04:13</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0017946-36.2021.8.16.0031</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05/07/2026 04:14</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0001987-07.2023.8.16.0079</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05/07/2026 04:14</t>
+          <t>05/07/2026 06:21</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0000657-31.2008.8.16.0004</t>
+          <t>0000209-04.2022.8.16.0122</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10/02/2022</t>
+          <t>21/05/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>23/06/2026 15:23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>23/06/2026 15:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05/07/2026 04:17</t>
+          <t>05/07/2026 06:30</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0082420-09.2017.8.16.0014</t>
+          <t>0001883-03.1996.8.16.0001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Usucapião Extraordinária</t>
+          <t>Agência e Distribuição</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>01/07/2024</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19/06/2026 13:53</t>
+          <t>23/06/2026 20:43</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>19/06/2026 13:53</t>
+          <t>23/06/2026 20:43</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05/07/2026 04:25</t>
+          <t>05/07/2026 06:42</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0000813-54.2024.8.16.0102</t>
+          <t>0030423-58.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Superendividamento</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05/07/2026 04:36</t>
+          <t>05/07/2026 07:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0059414-60.2023.8.16.0014</t>
+          <t>0076200-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>13/06/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>23/06/2026 16:33</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>23/06/2026 16:33</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>05/07/2026 04:44</t>
+          <t>05/07/2026 07:12</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0001417-61.2021.8.16.0056</t>
+          <t>0075641-07.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>29/08/2023</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 14:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 14:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>05/07/2026 04:45</t>
+          <t>05/07/2026 07:15</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0024826-81.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>05/07/2026 04:48</t>
+          <t>05/07/2026 07:15</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0030402-77.2022.8.16.0000</t>
+          <t>0020134-32.2021.8.16.0021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 14:13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 14:13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>05/07/2026 07:15</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,12 +3967,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0131308-07.2024.8.16.0000</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3982,22 +3982,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>16/06/2026 13:23</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>04/07/2026 14:13</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0000083-06.2025.8.16.0103</t>
+          <t>0020692-30.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Reivindicação | Provas</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>04/07/2026 14:18</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0023601-84.2015.8.16.0035</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>05/07/2026 04:54</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0029998-84.2026.8.16.0000</t>
+          <t>0001665-35.2024.8.16.0084</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Resistência</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>22/06/2026 15:33</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>22/06/2026 15:33</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>05/07/2026 04:55</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0128112-29.2024.8.16.0000</t>
+          <t>0001218-93.2020.8.16.0114</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18/06/2026 13:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18/06/2026 13:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>05/07/2026 04:55</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0121535-35.2024.8.16.0000</t>
+          <t>0014658-88.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>05/07/2026 05:08</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0021062-79.2023.8.16.0031</t>
+          <t>0006751-45.2021.8.16.0034</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade</t>
+          <t>Esbulho / Turbação / Ameaça</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>05/07/2026 05:17</t>
+          <t>04/07/2026 14:30</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0019201-83.2025.8.16.0000</t>
+          <t>0001243-07.2021.8.16.0071</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Liquidação</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>15/06/2026 13:33</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>05/07/2026 05:17</t>
+          <t>04/07/2026 14:33</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0003761-91.2024.8.16.0126</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17/06/2026 08:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>17/06/2026 08:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>05/07/2026 05:17</t>
+          <t>04/07/2026 14:40</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0019503-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>05/07/2026 05:23</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0024386-41.2021.8.16.0001</t>
+          <t>0000916-70.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>05/07/2026 05:25</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0109651-43.2023.8.16.0000</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>05/07/2026 05:27</t>
+          <t>04/07/2026 14:51</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0002415-17.2024.8.16.0123</t>
+          <t>0057622-45.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Edital</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>05/07/2026 05:29</t>
+          <t>04/07/2026 15:09</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,37 +4578,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0002669-34.2025.8.16.0000</t>
+          <t>0039625-20.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Registrado na ANVISA</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>05/07/2026 05:33</t>
+          <t>04/07/2026 15:13</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0000016-67.1996.8.16.0132</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>05/07/2026 05:39</t>
+          <t>04/07/2026 15:14</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0020770-22.2025.8.16.0000</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>05/07/2026 05:40</t>
+          <t>04/07/2026 15:17</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,37 +4719,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0073849-47.2024.8.16.0000</t>
+          <t>0128373-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>23/06/2026 14:33</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>23/06/2026 14:33</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>05/07/2026 05:50</t>
+          <t>04/07/2026 15:51</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,37 +4766,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0001590-04.2023.8.16.0028</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>18/07/2024</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>05/07/2026 05:51</t>
+          <t>04/07/2026 16:08</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,37 +4813,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0003888-32.2019.8.16.0117</t>
+          <t>0000615-03.2021.8.16.0076</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes Previstos no Estatuto da criança e do adolescente | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>29/03/2022</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>15/06/2026 11:59</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>05/07/2026 05:54</t>
+          <t>04/07/2026 16:17</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0001988-16.2008.8.16.0047</t>
+          <t>0006011-56.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>05/07/2026 05:54</t>
+          <t>04/07/2026 16:21</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0014490-80.2018.8.16.0129</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4917,27 +4917,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Roubo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>05/07/2026 05:56</t>
+          <t>04/07/2026 16:58</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0012449-59.2024.8.16.0185</t>
+          <t>0002286-77.2021.8.16.0103</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>04/07/2026 21:38</t>
+          <t>04/07/2026 17:04</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0015948-47.2007.8.16.0185</t>
+          <t>0002617-90.2023.8.16.0167</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
+          <t>Feminicídio | Crime Tentado</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>23/02/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>04/07/2026 21:41</t>
+          <t>04/07/2026 17:05</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,7 +5048,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0000862-06.2021.8.16.0004</t>
+          <t>0000857-02.2023.8.16.0040</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5058,27 +5058,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Descontos Indevidos | Contribuições Previdenciárias | Decadência/Prescrição | Cumprimento Provisório de Sentença</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>04/07/2026 21:41</t>
+          <t>04/07/2026 17:08</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0011335-31.2019.8.16.0001</t>
+          <t>0086943-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>05/08/2024</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>04/07/2026 21:42</t>
+          <t>04/07/2026 17:08</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,37 +5142,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0000944-73.2026.8.16.0000</t>
+          <t>0056285-13.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contra a Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>02/07/2026 17:13</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>02/07/2026 17:13</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>04/07/2026 21:44</t>
+          <t>04/07/2026 17:10</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0000016-67.1996.8.16.0132</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,27 +499,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/07/2026 07:40</t>
+          <t>04/07/2026 15:14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,37 +536,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0037607-38.2014.8.16.0001</t>
+          <t>0000083-06.2025.8.16.0103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Previdência privada | Indenização por Dano Material</t>
+          <t>Reivindicação | Provas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27/01/2021</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/07/2026 07:22</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0123109-93.2024.8.16.0000</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Crédito Rural</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>04/07/2026 23:55</t>
+          <t>05/07/2026 03:19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0000615-03.2021.8.16.0076</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>04/07/2026 23:55</t>
+          <t>04/07/2026 16:17</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/07/2026 00:19</t>
+          <t>05/07/2026 01:07</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/07/2026 00:24</t>
+          <t>05/07/2026 04:17</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/07/2026 00:40</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0000763-58.2023.8.16.0168</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/07/2026 00:47</t>
+          <t>05/07/2026 02:57</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0100507-45.2023.8.16.0000</t>
+          <t>0000813-54.2024.8.16.0102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/07/2026 00:54</t>
+          <t>05/07/2026 04:36</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0000857-02.2023.8.16.0040</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/07/2026 00:56</t>
+          <t>04/07/2026 17:08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0049892-17.2024.8.16.0000</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Desapropriação Indireta</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22/06/2026 14:03</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22/06/2026 14:03</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/07/2026 01:02</t>
+          <t>05/07/2026 02:08</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0000616-29.2022.8.16.0148</t>
+          <t>0000916-70.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/07/2026 01:07</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0000994-81.2021.8.16.0095</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/07/2026 01:15</t>
+          <t>05/07/2026 05:39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0001218-93.2020.8.16.0114</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/07/2026 01:16</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0012630-20.2024.8.16.0069</t>
+          <t>0001243-07.2021.8.16.0071</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/07/2026 01:28</t>
+          <t>04/07/2026 14:33</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0001417-61.2021.8.16.0056</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/07/2026 01:41</t>
+          <t>05/07/2026 04:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/07/2026 01:48</t>
+          <t>05/07/2026 02:33</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0001590-04.2023.8.16.0028</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>18/07/2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/07/2026 02:00</t>
+          <t>05/07/2026 05:51</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0000877-47.2012.8.16.0179</t>
+          <t>0001665-35.2024.8.16.0084</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>22/06/2026 15:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>22/06/2026 15:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/07/2026 02:08</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,37 +1382,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0001987-07.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/07/2026 02:20</t>
+          <t>05/07/2026 04:14</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0001988-16.2008.8.16.0047</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/07/2026 02:25</t>
+          <t>05/07/2026 05:54</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/07/2026 02:27</t>
+          <t>04/07/2026 14:40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1538,22 +1538,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/07/2026 02:33</t>
+          <t>05/07/2026 00:47</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0002415-17.2024.8.16.0123</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Edital</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>23/06/2026 15:33</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/07/2026 02:40</t>
+          <t>05/07/2026 05:29</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0002617-90.2023.8.16.0167</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Feminicídio | Crime Tentado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/07/2026 02:50</t>
+          <t>04/07/2026 17:05</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0062792-32.2024.8.16.0000</t>
+          <t>0002669-34.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
+          <t>Registrado na ANVISA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/07/2026 02:52</t>
+          <t>05/07/2026 05:33</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0000763-58.2023.8.16.0168</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/07/2026 02:57</t>
+          <t>04/07/2026 16:08</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0105436-87.2024.8.16.0000</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/07/2026 03:06</t>
+          <t>05/07/2026 02:20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0004396-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1820,22 +1820,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/07/2026 03:14</t>
+          <t>04/07/2026 17:49</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/07/2026 03:18</t>
+          <t>05/07/2026 00:40</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0000587-56.2022.8.16.0090</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1914,22 +1914,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05/07/2026 03:19</t>
+          <t>05/07/2026 03:14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0083802-27.2023.8.16.0014</t>
+          <t>0004582-39.2022.8.16.0038</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cessão de Crédito | Consórcio</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>05/07/2026 03:22</t>
+          <t>04/07/2026 17:34</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>0006011-56.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>05/07/2026 03:35</t>
+          <t>04/07/2026 16:21</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0072332-62.2024.8.16.0014</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>05/07/2026 03:38</t>
+          <t>05/07/2026 01:16</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0006751-45.2021.8.16.0034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Esbulho / Turbação / Ameaça</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>04/07/2026 14:30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0006810-30.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>05/07/2026 03:47</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>05/07/2026 04:13</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0006810-30.2021.8.16.0035</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05/07/2026 03:47</t>
+          <t>05/07/2026 02:27</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0008506-04.2023.8.16.0174</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Correção Monetária</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>23/06/2026 17:14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>23/06/2026 17:15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/07/2026 04:02</t>
+          <t>04/07/2026 13:41</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0036612-13.2023.8.16.0000</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/07/2026 04:02</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05/07/2026 04:13</t>
+          <t>05/07/2026 00:24</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05/07/2026 04:14</t>
+          <t>05/07/2026 03:18</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0001987-07.2023.8.16.0079</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05/07/2026 04:14</t>
+          <t>05/07/2026 02:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0000657-31.2008.8.16.0004</t>
+          <t>0012630-20.2024.8.16.0069</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10/02/2022</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05/07/2026 04:17</t>
+          <t>05/07/2026 01:28</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0000813-54.2024.8.16.0102</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Superendividamento</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/07/2026 04:36</t>
+          <t>05/07/2026 01:15</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0059414-60.2023.8.16.0014</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/07/2026 04:44</t>
+          <t>05/07/2026 07:40</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0001417-61.2021.8.16.0056</t>
+          <t>0014658-88.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>05/07/2026 04:45</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0019503-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>05/07/2026 04:48</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0030402-77.2022.8.16.0000</t>
+          <t>0020692-30.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>04/07/2026 14:18</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0000083-06.2025.8.16.0103</t>
+          <t>0020770-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Reivindicação | Provas</t>
+          <t>Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>05/07/2026 05:40</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0021062-79.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Oferta e Publicidade</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>05/07/2026 04:54</t>
+          <t>05/07/2026 05:17</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0121535-35.2024.8.16.0000</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>05/07/2026 05:08</t>
+          <t>05/07/2026 01:41</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0021062-79.2023.8.16.0031</t>
+          <t>0023601-84.2015.8.16.0035</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>05/07/2026 05:17</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0024386-41.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>05/07/2026 05:23</t>
+          <t>05/07/2026 05:25</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0024386-41.2021.8.16.0001</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>05/07/2026 05:25</t>
+          <t>05/07/2026 00:19</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0109651-43.2023.8.16.0000</t>
+          <t>0030402-77.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Corretagem</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>05/07/2026 05:27</t>
+          <t>05/07/2026 04:52</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0002415-17.2024.8.16.0123</t>
+          <t>0036612-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Edital</t>
+          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>05/07/2026 05:29</t>
+          <t>05/07/2026 04:02</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0002669-34.2025.8.16.0000</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Registrado na ANVISA</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>05/07/2026 05:33</t>
+          <t>05/07/2026 00:56</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0037607-38.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Previdência privada | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>27/01/2021</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>05/07/2026 05:39</t>
+          <t>05/07/2026 07:22</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0020770-22.2025.8.16.0000</t>
+          <t>0039625-20.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>05/07/2026 05:40</t>
+          <t>04/07/2026 15:13</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0073849-47.2024.8.16.0000</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>05/07/2026 05:50</t>
+          <t>04/07/2026 15:17</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0001590-04.2023.8.16.0028</t>
+          <t>0041235-44.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18/07/2024</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>05/07/2026 05:51</t>
+          <t>05/07/2026 05:56</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0001988-16.2008.8.16.0047</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>05/07/2026 05:54</t>
+          <t>05/07/2026 04:54</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05/07/2026 05:56</t>
+          <t>05/07/2026 04:02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>05/07/2026 04:48</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0017946-36.2021.8.16.0031</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>05/07/2026 04:14</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05/07/2026 06:21</t>
+          <t>05/07/2026 05:23</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0000209-04.2022.8.16.0122</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21/05/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>23/06/2026 15:23</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>23/06/2026 15:23</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05/07/2026 06:30</t>
+          <t>04/07/2026 14:13</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0001883-03.1996.8.16.0001</t>
+          <t>0049892-17.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Agência e Distribuição</t>
+          <t>Desapropriação Indireta</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>23/06/2026 20:43</t>
+          <t>22/06/2026 14:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>23/06/2026 20:43</t>
+          <t>22/06/2026 14:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05/07/2026 06:42</t>
+          <t>05/07/2026 01:02</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0030423-58.2020.8.16.0021</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3742,27 +3742,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05/07/2026 07:00</t>
+          <t>05/07/2026 02:25</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0076200-90.2024.8.16.0000</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>23/06/2026 16:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>23/06/2026 16:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>05/07/2026 07:12</t>
+          <t>04/07/2026 14:51</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0075641-07.2022.8.16.0000</t>
+          <t>0056285-13.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Contra a Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>29/08/2023</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>23/06/2026 14:23</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>23/06/2026 14:23</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>05/07/2026 07:15</t>
+          <t>04/07/2026 17:10</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0024826-81.2014.8.16.0001</t>
+          <t>0057622-45.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>05/07/2026 07:15</t>
+          <t>04/07/2026 15:09</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0020134-32.2021.8.16.0021</t>
+          <t>0059414-60.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>23/06/2026 14:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>23/06/2026 14:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>05/07/2026 07:15</t>
+          <t>05/07/2026 04:44</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0062792-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>04/07/2026 14:13</t>
+          <t>05/07/2026 02:52</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0020692-30.2022.8.16.0001</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>04/07/2026 14:18</t>
+          <t>05/07/2026 02:50</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,7 +4061,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0023601-84.2015.8.16.0035</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0001665-35.2024.8.16.0084</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22/06/2026 15:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>22/06/2026 15:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>05/07/2026 03:38</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0073849-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>05/07/2026 05:50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>05/07/2026 03:43</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0083802-27.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Cessão de Crédito | Consórcio</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>04/07/2026 14:30</t>
+          <t>05/07/2026 03:22</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0001243-07.2021.8.16.0071</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>04/07/2026 14:33</t>
+          <t>05/07/2026 01:48</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,37 +4343,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0086943-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>04/07/2026 14:40</t>
+          <t>04/07/2026 17:08</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0019503-80.2023.8.16.0001</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>05/07/2026 02:40</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0000916-70.2024.8.16.0196</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>05/07/2026 00:54</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0105436-87.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>04/07/2026 14:51</t>
+          <t>05/07/2026 03:06</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0057622-45.2025.8.16.0000</t>
+          <t>0109651-43.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>04/07/2026 15:09</t>
+          <t>05/07/2026 05:27</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>04/07/2026 15:13</t>
+          <t>05/07/2026 03:35</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0000016-67.1996.8.16.0132</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04/07/2026 15:14</t>
+          <t>05/07/2026 05:08</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0123109-93.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Crédito Rural</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>04/07/2026 15:17</t>
+          <t>04/07/2026 23:55</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4758,429 +4758,6 @@
         </is>
       </c>
       <c r="I92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>0003300-85.2019.8.16.0194</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>26/05/2021</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>02/07/2026 15:23</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>02/07/2026 15:23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>04/07/2026 16:08</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>0000615-03.2021.8.16.0076</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>12/07/2024</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>29/06/2026 14:23</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>29/06/2026 14:23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>04/07/2026 16:17</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>0006011-56.2022.8.16.0033</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>12/08/2025</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>23/06/2026 16:13</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>23/06/2026 16:13</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>04/07/2026 16:21</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>0014490-80.2018.8.16.0129</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Roubo</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>19/02/2024</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>24/06/2026 15:03</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>24/06/2026 15:03</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>04/07/2026 16:58</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0002286-77.2021.8.16.0103</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Seguro</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>22/01/2024</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>01/07/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>01/07/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:04</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>0002617-90.2023.8.16.0167</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Feminicídio | Crime Tentado</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>03/07/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>03/07/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:05</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>0000857-02.2023.8.16.0040</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>23/06/2026 19:03</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>23/06/2026 19:03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:08</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>0086943-28.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>26/06/2026 16:33</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>26/06/2026 16:33</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:08</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0056285-13.2024.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Contra a Mulher | Ameaça</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>01/07/2026 13:43</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>01/07/2026 13:43</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:10</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/07/2026 03:19</t>
+          <t>21/07/2026 11:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/07/2026 01:07</t>
+          <t>21/07/2026 10:58</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,37 +724,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000657-31.2008.8.16.0004</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10/02/2022</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/07/2026 04:17</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0000916-70.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000763-58.2023.8.16.0168</t>
+          <t>0001218-93.2020.8.16.0114</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/07/2026 02:57</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000813-54.2024.8.16.0102</t>
+          <t>0001243-07.2021.8.16.0071</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Superendividamento</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>23/06/2026 19:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/07/2026 04:36</t>
+          <t>04/07/2026 14:33</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000857-02.2023.8.16.0040</t>
+          <t>0001417-61.2021.8.16.0056</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>04/07/2026 17:08</t>
+          <t>21/07/2026 10:13</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000877-47.2012.8.16.0179</t>
+          <t>0001665-35.2024.8.16.0084</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>22/06/2026 15:33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>22/06/2026 15:33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/07/2026 02:08</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0000916-70.2024.8.16.0196</t>
+          <t>0001987-07.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>21/07/2026 16:53</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0001988-16.2008.8.16.0047</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/07/2026 05:39</t>
+          <t>21/07/2026 05:55</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>04/07/2026 14:40</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001243-07.2021.8.16.0071</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>04/07/2026 14:33</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001417-61.2021.8.16.0056</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/07/2026 04:45</t>
+          <t>04/07/2026 16:08</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/07/2026 02:33</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001590-04.2023.8.16.0028</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18/07/2024</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/07/2026 05:51</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001665-35.2024.8.16.0084</t>
+          <t>0006011-56.2022.8.16.0033</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22/06/2026 15:33</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22/06/2026 15:33</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>04/07/2026 16:21</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001987-07.2023.8.16.0079</t>
+          <t>0006751-45.2021.8.16.0034</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Esbulho / Turbação / Ameaça</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/07/2026 04:14</t>
+          <t>04/07/2026 14:30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001988-16.2008.8.16.0047</t>
+          <t>0006810-30.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/07/2026 05:54</t>
+          <t>21/07/2026 11:35</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>04/07/2026 14:40</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0007799-39.2024.8.16.0194</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>23/06/2026 17:43</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>23/06/2026 17:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/07/2026 00:47</t>
+          <t>21/07/2026 07:26</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002415-17.2024.8.16.0123</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Edital</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/07/2026 05:29</t>
+          <t>21/07/2026 02:10</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0002617-90.2023.8.16.0167</t>
+          <t>0008506-04.2023.8.16.0174</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Feminicídio | Crime Tentado</t>
+          <t>Correção Monetária</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>23/06/2026 17:14</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>23/06/2026 17:15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/07/2026 17:05</t>
+          <t>04/07/2026 13:41</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0002669-34.2025.8.16.0000</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Registrado na ANVISA</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/07/2026 05:33</t>
+          <t>21/07/2026 08:27</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>04/07/2026 16:08</t>
+          <t>21/07/2026 10:56</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0012630-20.2024.8.16.0069</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/07/2026 02:20</t>
+          <t>21/07/2026 05:34</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0004396-28.2025.8.16.0000</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>04/07/2026 17:49</t>
+          <t>21/07/2026 12:14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/07/2026 00:40</t>
+          <t>21/07/2026 04:31</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0014658-88.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>05/07/2026 03:14</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004582-39.2022.8.16.0038</t>
+          <t>0019503-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>04/07/2026 17:34</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0006011-56.2022.8.16.0033</t>
+          <t>0020134-32.2021.8.16.0021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>23/06/2026 14:13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>23/06/2026 14:13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>04/07/2026 16:21</t>
+          <t>21/07/2026 10:05</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0020692-30.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>05/07/2026 01:16</t>
+          <t>04/07/2026 14:18</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0021062-79.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Oferta e Publicidade</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>04/07/2026 14:30</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0006810-30.2021.8.16.0035</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>05/07/2026 03:47</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0023601-84.2015.8.16.0035</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>05/07/2026 04:13</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05/07/2026 02:27</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0008506-04.2023.8.16.0174</t>
+          <t>0030402-77.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Correção Monetária</t>
+          <t>Corretagem</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23/06/2026 17:14</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>23/06/2026 17:15</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>04/07/2026 13:41</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0030423-58.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/07/2026 03:43</t>
+          <t>21/07/2026 14:51</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0037607-38.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Previdência privada | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>27/01/2021</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05/07/2026 00:24</t>
+          <t>21/07/2026 02:23</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0039625-20.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05/07/2026 03:18</t>
+          <t>04/07/2026 15:13</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05/07/2026 02:00</t>
+          <t>04/07/2026 15:17</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0012630-20.2024.8.16.0069</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05/07/2026 01:28</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/07/2026 01:15</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/07/2026 07:40</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0019503-80.2023.8.16.0001</t>
+          <t>0045998-62.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>21/07/2026 17:04</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0020692-30.2022.8.16.0001</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>04/07/2026 14:18</t>
+          <t>04/07/2026 14:13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0020770-22.2025.8.16.0000</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>05/07/2026 05:40</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0021062-79.2023.8.16.0031</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>05/07/2026 05:17</t>
+          <t>04/07/2026 14:51</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0057622-45.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>23/06/2026 16:13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>05/07/2026 01:41</t>
+          <t>04/07/2026 15:09</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0023601-84.2015.8.16.0035</t>
+          <t>0062792-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>21/07/2026 08:41</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0024386-41.2021.8.16.0001</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>05/07/2026 05:25</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>05/07/2026 00:19</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0030402-77.2022.8.16.0000</t>
+          <t>0075641-07.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>29/08/2023</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 14:23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>23/06/2026 14:23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>05/07/2026 04:52</t>
+          <t>21/07/2026 14:51</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0036612-13.2023.8.16.0000</t>
+          <t>0076200-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>13/06/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>23/06/2026 16:33</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>23/06/2026 16:33</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>05/07/2026 04:02</t>
+          <t>21/07/2026 10:05</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>05/07/2026 00:56</t>
+          <t>21/07/2026 01:59</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0037607-38.2014.8.16.0001</t>
+          <t>0083802-27.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Previdência privada | Indenização por Dano Material</t>
+          <t>Cessão de Crédito | Consórcio</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27/01/2021</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>05/07/2026 07:22</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>04/07/2026 15:13</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>04/07/2026 15:17</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>05/07/2026 05:56</t>
+          <t>21/07/2026 13:16</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0105436-87.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>05/07/2026 04:54</t>
+          <t>21/07/2026 10:13</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0109651-43.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05/07/2026 04:02</t>
+          <t>21/07/2026 07:14</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05/07/2026 04:48</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05/07/2026 04:14</t>
+          <t>21/07/2026 04:49</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0123109-93.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>Crédito Rural</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05/07/2026 05:23</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0128373-91.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>23/06/2026 14:33</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>23/06/2026 14:33</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>04/07/2026 14:13</t>
+          <t>04/07/2026 15:51</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3677,1087 +3677,6 @@
         </is>
       </c>
       <c r="I69" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>0049892-17.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Desapropriação Indireta</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>22/06/2026 14:03</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>22/06/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>05/07/2026 01:02</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>0051552-46.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Duplicata</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>27/05/2025</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>02/07/2026 17:23</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>02/07/2026 17:23</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>05/07/2026 02:25</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>0051985-33.2013.8.16.0001</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>07/06/2022</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>02/07/2026 15:23</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>02/07/2026 15:23</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>04/07/2026 14:51</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>0056285-13.2024.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Contra a Mulher | Ameaça</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>01/07/2026 13:43</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>01/07/2026 13:43</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:10</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>0057622-45.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>23/06/2026 16:13</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>23/06/2026 16:13</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>04/07/2026 15:09</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>0059414-60.2023.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Contratos Bancários</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>19/03/2026</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>23/06/2026 17:03</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>23/06/2026 17:03</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>05/07/2026 04:44</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>0062792-32.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>18/07/2025</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>26/06/2026 15:13</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>26/06/2026 15:13</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>05/07/2026 02:52</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>0067511-93.2016.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Erro Médico</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>19/06/2024</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>01/07/2026 15:53</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>01/07/2026 15:53</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>05/07/2026 02:50</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>0071353-45.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>29/10/2025</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>02/07/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>02/07/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>04/07/2026 23:55</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>0072332-62.2024.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>24/03/2026</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>05/07/2026 03:38</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>0073849-47.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Prescrição e Decadência</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>27/06/2025</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>26/06/2026 17:03</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>26/06/2026 17:03</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>05/07/2026 05:50</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>0082204-46.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>31/10/2025</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:03</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:03</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>05/07/2026 03:43</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>0083802-27.2023.8.16.0014</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Cessão de Crédito | Consórcio</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>23/10/2025</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>23/06/2026 13:43</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>23/06/2026 13:43</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>05/07/2026 03:22</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>0086039-76.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Rescisão / Resolução</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>18/09/2024</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>29/06/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>29/06/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>05/07/2026 01:48</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>0086943-28.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>26/06/2026 16:33</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>26/06/2026 16:33</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>04/07/2026 17:08</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>0091320-13.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Defeito, nulidade ou anulação</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>23/10/2025</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>02/07/2026 11:50</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>02/07/2026 11:50</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>05/07/2026 02:40</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>0100507-45.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Hipoteca</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>21/01/2025</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>01/07/2026 13:33</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>01/07/2026 13:33</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>05/07/2026 00:54</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>0105436-87.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>06/10/2025</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>24/06/2026 14:13</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>24/06/2026 14:13</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>05/07/2026 03:06</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>0109651-43.2023.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>05/06/2025</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>24/06/2026 15:13</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>24/06/2026 15:13</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>05/07/2026 05:27</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>0120044-90.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Compensação</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>04/03/2026</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>29/06/2026 13:03</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>29/06/2026 13:03</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>05/07/2026 03:35</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0121535-35.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>28/11/2025</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>05/07/2026 05:08</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>0123109-93.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Crédito Rural</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>29/10/2025</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>26/06/2026 17:23</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>26/06/2026 17:23</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>04/07/2026 23:55</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>0128373-91.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>13/11/2025</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>23/06/2026 14:33</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>23/06/2026 14:33</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>04/07/2026 15:51</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0000016-67.1996.8.16.0132</t>
+          <t>0045998-62.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>04/07/2026 15:14</t>
+          <t>21/07/2026 17:04</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0000083-06.2025.8.16.0103</t>
+          <t>0001987-07.2023.8.16.0079</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reivindicação | Provas</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>23/06/2026 18:03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>21/07/2026 16:53</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000587-56.2022.8.16.0090</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21/07/2026 11:33</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000615-03.2021.8.16.0076</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>04/07/2026 16:17</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000616-29.2022.8.16.0148</t>
+          <t>0075641-07.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>29/08/2023</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>23/06/2026 14:23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>23/06/2026 14:23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21/07/2026 10:58</t>
+          <t>21/07/2026 14:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0030423-58.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>21/07/2026 14:51</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000916-70.2024.8.16.0196</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>21/07/2026 13:16</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>21/07/2026 12:14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0001243-07.2021.8.16.0071</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>04/07/2026 14:33</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,22 +912,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0001417-61.2021.8.16.0056</t>
+          <t>0030402-77.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Corretagem</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21/07/2026 10:13</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0001665-35.2024.8.16.0084</t>
+          <t>0000083-06.2025.8.16.0103</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Reivindicação | Provas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22/06/2026 15:33</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22/06/2026 15:33</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001987-07.2023.8.16.0079</t>
+          <t>0083802-27.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Cessão de Crédito | Consórcio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>23/06/2026 13:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21/07/2026 16:53</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001988-16.2008.8.16.0047</t>
+          <t>0123109-93.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Crédito Rural</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21/07/2026 05:55</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,37 +1100,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>04/07/2026 14:40</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21/07/2026 08:43</t>
+          <t>21/07/2026 10:56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>04/07/2026 16:08</t>
+          <t>21/07/2026 10:58</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0003664-09.2019.8.16.0113</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>21/07/2026 11:33</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0006810-30.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21/07/2026 06:48</t>
+          <t>21/07/2026 11:35</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0006011-56.2022.8.16.0033</t>
+          <t>0076200-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>13/06/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>23/06/2026 16:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>23/06/2026 16:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>04/07/2026 16:21</t>
+          <t>21/07/2026 10:05</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0020134-32.2021.8.16.0021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>23/06/2026 14:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>23/06/2026 14:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>04/07/2026 14:30</t>
+          <t>21/07/2026 10:05</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0006810-30.2021.8.16.0035</t>
+          <t>0105436-87.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21/07/2026 11:35</t>
+          <t>21/07/2026 10:13</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0001417-61.2021.8.16.0056</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>09/12/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>23/06/2026 14:53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>21/07/2026 10:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0007799-39.2024.8.16.0194</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23/06/2026 17:43</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23/06/2026 17:43</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21/07/2026 07:26</t>
+          <t>21/07/2026 08:27</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0062792-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21/07/2026 02:10</t>
+          <t>21/07/2026 08:41</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0008506-04.2023.8.16.0174</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Correção Monetária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23/06/2026 17:14</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23/06/2026 17:15</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/07/2026 13:41</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21/07/2026 08:27</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21/07/2026 10:56</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0012630-20.2024.8.16.0069</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/07/2026 05:34</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21/07/2026 12:14</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21/07/2026 04:31</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0019503-80.2023.8.16.0001</t>
+          <t>0109651-43.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>21/07/2026 07:14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0020134-32.2021.8.16.0021</t>
+          <t>0007799-39.2024.8.16.0194</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Rescisão do contrato e devolução do dinheiro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23/06/2026 14:13</t>
+          <t>23/06/2026 17:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23/06/2026 14:13</t>
+          <t>23/06/2026 17:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21/07/2026 10:05</t>
+          <t>21/07/2026 07:26</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0020692-30.2022.8.16.0001</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>04/07/2026 14:18</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0021062-79.2023.8.16.0031</t>
+          <t>0012630-20.2024.8.16.0069</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade</t>
+          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 13:13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>21/07/2026 05:34</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0001988-16.2008.8.16.0047</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>26/06/2026 13:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>21/07/2026 05:55</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0023601-84.2015.8.16.0035</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21/07/2026 07:06</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,37 +2275,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0030402-77.2022.8.16.0000</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>21/07/2026 04:31</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0030423-58.2020.8.16.0021</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21/07/2026 14:51</t>
+          <t>21/07/2026 04:49</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,37 +2369,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0037607-38.2014.8.16.0001</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Previdência privada | Indenização por Dano Material</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>27/01/2021</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21/07/2026 02:23</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0021062-79.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Oferta e Publicidade</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>04/07/2026 15:13</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>04/07/2026 15:17</t>
+          <t>21/07/2026 01:59</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>21/07/2026 02:10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0037607-38.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>Previdência privada | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>27/01/2021</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>21/07/2026 02:23</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0045998-62.2026.8.16.0000</t>
+          <t>0024826-81.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Previdência privada</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21/07/2026 17:04</t>
+          <t>21/07/2026 02:24</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0000209-04.2022.8.16.0122</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Confissão/Composição de Dívida</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>21/05/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>23/06/2026 15:23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>23/06/2026 15:23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>04/07/2026 14:13</t>
+          <t>21/07/2026 02:24</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0036612-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>23/06/2026 20:33</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21/07/2026 08:04</t>
+          <t>21/07/2026 02:29</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>04/07/2026 14:51</t>
+          <t>21/07/2026 01:24</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0057622-45.2025.8.16.0000</t>
+          <t>0002669-34.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Registrado na ANVISA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>04/07/2026 15:09</t>
+          <t>20/07/2026 23:58</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0062792-32.2024.8.16.0000</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21/07/2026 08:41</t>
+          <t>21/07/2026 00:10</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,37 +2980,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>21/07/2026 00:11</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0001590-04.2023.8.16.0028</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>18/07/2024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>21/07/2026 00:28</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0075641-07.2022.8.16.0000</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>29/08/2023</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>23/06/2026 14:23</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>23/06/2026 14:23</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21/07/2026 14:51</t>
+          <t>21/07/2026 00:35</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0076200-90.2024.8.16.0000</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>23/06/2026 16:33</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>23/06/2026 16:33</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21/07/2026 10:05</t>
+          <t>05/07/2026 00:19</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21/07/2026 01:59</t>
+          <t>05/07/2026 02:08</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0083802-27.2023.8.16.0014</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cessão de Crédito | Consórcio</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>05/07/2026 02:20</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>05/07/2026 02:33</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0000763-58.2023.8.16.0168</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>23/06/2026 13:13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>05/07/2026 02:57</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0100507-45.2023.8.16.0000</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21/07/2026 13:16</t>
+          <t>05/07/2026 03:14</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0105436-87.2024.8.16.0000</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21/07/2026 10:13</t>
+          <t>05/07/2026 03:18</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0109651-43.2023.8.16.0000</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21/07/2026 07:14</t>
+          <t>05/07/2026 03:38</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>0000813-54.2024.8.16.0102</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>05/07/2026 04:36</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0121535-35.2024.8.16.0000</t>
+          <t>0059414-60.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>23/06/2026 17:03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21/07/2026 04:49</t>
+          <t>05/07/2026 04:44</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0123109-93.2024.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Crédito Rural</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>05/07/2026 04:48</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,45 +3638,1549 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>0024386-41.2021.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>26/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>26/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>05/07/2026 05:25</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0002415-17.2024.8.16.0123</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Edital</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>23/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>23/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>05/07/2026 05:29</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0000994-81.2021.8.16.0095</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>24/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>24/06/2026 13:43</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>05/07/2026 05:39</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0020770-22.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Direitos e Títulos de Crédito</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>26/06/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>26/06/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>05/07/2026 05:40</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0073849-47.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Prescrição e Decadência</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>27/06/2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>26/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>26/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>05/07/2026 05:50</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0041235-44.2024.8.16.0014</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Práticas Abusivas</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>18/06/2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>01/07/2026 19:23</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>01/07/2026 19:23</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>05/07/2026 05:56</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0017946-36.2021.8.16.0031</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>26/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>26/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>05/07/2026 06:12</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0003837-28.2018.8.16.0126</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>27/02/2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>30/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>30/06/2026 14:33</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>05/07/2026 06:21</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0001883-03.1996.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Agência e Distribuição</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>23/06/2026 20:43</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>23/06/2026 20:43</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>05/07/2026 06:42</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0048561-97.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:13</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0020692-30.2022.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:18</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0023601-84.2015.8.16.0035</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>26/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>26/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:23</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0001218-93.2020.8.16.0114</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Contratos Bancários</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>02/02/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:33</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:29</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0014658-88.2018.8.16.0030</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>28/05/2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>29/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>29/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:29</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0006751-45.2021.8.16.0034</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Esbulho / Turbação / Ameaça</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:53</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:30</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0001243-07.2021.8.16.0071</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>23/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>23/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:33</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0002022-73.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Mandato</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>02/12/2024</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:40</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0019503-80.2023.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>26/06/2026 15:43</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>26/06/2026 15:43</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:46</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0000916-70.2024.8.16.0196</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Roubo Majorado</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>01/07/2026 20:23</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>01/07/2026 20:23</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:46</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0051985-33.2013.8.16.0001</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>07/06/2022</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>04/07/2026 14:51</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0057622-45.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>04/07/2026 15:09</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0039625-20.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>29/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>29/06/2026 15:33</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>04/07/2026 15:13</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0000016-67.1996.8.16.0132</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nota Promissória</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>11/07/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>04/07/2026 15:14</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0041154-84.2018.8.16.0021</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>01/07/2026 17:43</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>01/07/2026 17:43</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>04/07/2026 15:17</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>0128373-91.2024.8.16.0000</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>Prestação de Serviços</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>13/11/2025</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>23/06/2026 14:33</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>23/06/2026 14:33</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>04/07/2026 15:51</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0003300-85.2019.8.16.0194</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>26/05/2021</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>04/07/2026 16:08</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0000615-03.2021.8.16.0076</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tráfico de Drogas e Condutas Afins</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>12/07/2024</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>04/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0006011-56.2022.8.16.0033</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>23/06/2026 16:13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>04/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0014490-80.2018.8.16.0129</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Roubo</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>19/02/2024</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>24/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>24/06/2026 15:03</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>04/07/2026 16:58</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0002286-77.2021.8.16.0103</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Seguro</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>22/01/2024</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:03</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:03</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>04/07/2026 17:04</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0002617-90.2023.8.16.0167</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Feminicídio | Crime Tentado</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>03/07/2026 13:13</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>03/07/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>04/07/2026 17:05</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0000857-02.2023.8.16.0040</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Indenização por Dano Material</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>23/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>23/06/2026 19:03</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>04/07/2026 17:08</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0086943-28.2025.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>26/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>26/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>04/07/2026 17:08</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0001987-07.2023.8.16.0079</t>
+          <t>0113087-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23/06/2026 18:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21/07/2026 16:53</t>
+          <t>04/07/2026 23:36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -593,27 +593,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>05/07/2026 00:19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>05/07/2026 02:08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0075641-07.2022.8.16.0000</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29/08/2023</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23/06/2026 14:23</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23/06/2026 14:23</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21/07/2026 14:51</t>
+          <t>05/07/2026 02:20</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0030423-58.2020.8.16.0021</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>21/07/2026 14:51</t>
+          <t>05/07/2026 02:33</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0100507-45.2023.8.16.0000</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21/07/2026 13:16</t>
+          <t>05/07/2026 03:14</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,27 +828,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21/07/2026 12:14</t>
+          <t>05/07/2026 03:18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>05/07/2026 03:38</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,37 +912,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0030402-77.2022.8.16.0000</t>
+          <t>0000813-54.2024.8.16.0102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Corretagem</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>05/07/2026 04:36</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000083-06.2025.8.16.0103</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reivindicação | Provas</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>05/07/2026 04:48</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0083802-27.2023.8.16.0014</t>
+          <t>0024386-41.2021.8.16.0001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cessão de Crédito | Consórcio</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23/06/2026 13:43</t>
+          <t>26/06/2026 16:13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>05/07/2026 05:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0123109-93.2024.8.16.0000</t>
+          <t>0000994-81.2021.8.16.0095</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Crédito Rural</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>24/06/2026 13:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>05/07/2026 05:39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0020770-22.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>26/06/2026 19:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>05/07/2026 05:40</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0073849-47.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>27/06/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>26/06/2026 17:03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21/07/2026 10:56</t>
+          <t>05/07/2026 05:50</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0000616-29.2022.8.16.0148</t>
+          <t>0041235-44.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,27 +1204,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21/07/2026 10:58</t>
+          <t>05/07/2026 05:56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0000587-56.2022.8.16.0090</t>
+          <t>0017946-36.2021.8.16.0031</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21/07/2026 11:33</t>
+          <t>05/07/2026 06:12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0006810-30.2021.8.16.0035</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21/07/2026 11:35</t>
+          <t>05/07/2026 06:21</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,37 +1335,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0076200-90.2024.8.16.0000</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13/06/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23/06/2026 16:33</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23/06/2026 16:33</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21/07/2026 10:05</t>
+          <t>21/07/2026 00:10</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0020134-32.2021.8.16.0021</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23/06/2026 14:13</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23/06/2026 14:13</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21/07/2026 10:05</t>
+          <t>21/07/2026 00:11</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0105436-87.2024.8.16.0000</t>
+          <t>0001590-04.2023.8.16.0028</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>18/07/2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>26/06/2026 18:43</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21/07/2026 10:13</t>
+          <t>21/07/2026 00:28</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0001417-61.2021.8.16.0056</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>09/12/2024</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23/06/2026 14:53</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21/07/2026 10:13</t>
+          <t>21/07/2026 00:35</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21/07/2026 08:27</t>
+          <t>21/07/2026 01:24</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0062792-32.2024.8.16.0000</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21/07/2026 08:41</t>
+          <t>21/07/2026 01:59</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21/07/2026 08:43</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003664-09.2019.8.16.0113</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>21/07/2026 02:10</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0037607-38.2014.8.16.0001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Previdência privada | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>27/01/2021</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>26/06/2026 15:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>21/07/2026 02:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,27 +1862,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21/07/2026 06:48</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21/07/2026 07:06</t>
+          <t>21/07/2026 04:31</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0109651-43.2023.8.16.0000</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21/07/2026 07:14</t>
+          <t>21/07/2026 04:49</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0007799-39.2024.8.16.0194</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23/06/2026 17:43</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23/06/2026 17:43</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21/07/2026 07:26</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0021062-79.2023.8.16.0031</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Oferta e Publicidade</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21/07/2026 08:04</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0109651-43.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>05/06/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>24/06/2026 15:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21/07/2026 04:31</t>
+          <t>21/07/2026 07:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0121535-35.2024.8.16.0000</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21/07/2026 04:49</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>21/07/2026 08:27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0021062-79.2023.8.16.0031</t>
+          <t>0062792-32.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade</t>
+          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>18/07/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>26/06/2026 15:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>21/07/2026 08:41</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21/07/2026 01:59</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,37 +2557,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21/07/2026 02:10</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,37 +2651,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0037607-38.2014.8.16.0001</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Previdência privada | Indenização por Dano Material</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27/01/2021</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21/07/2026 02:23</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0024826-81.2014.8.16.0001</t>
+          <t>0105436-87.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Previdência privada</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>24/06/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21/07/2026 02:24</t>
+          <t>21/07/2026 10:13</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0000209-04.2022.8.16.0122</t>
+          <t>0123109-93.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Confissão/Composição de Dívida</t>
+          <t>Crédito Rural</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21/05/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>23/06/2026 15:23</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>23/06/2026 15:23</t>
+          <t>26/06/2026 17:23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21/07/2026 02:24</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0036612-13.2023.8.16.0000</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fornecimento de insumos | Práticas Abusivas | Multa Cominatória / Astreintes</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>23/06/2026 20:33</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21/07/2026 02:29</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21/07/2026 01:24</t>
+          <t>21/07/2026 10:56</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0002669-34.2025.8.16.0000</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Registrado na ANVISA</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20/07/2026 23:58</t>
+          <t>21/07/2026 10:58</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21/07/2026 00:10</t>
+          <t>21/07/2026 11:33</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0006810-30.2021.8.16.0035</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>24/06/2026 14:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21/07/2026 00:11</t>
+          <t>21/07/2026 11:35</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,37 +3027,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0001590-04.2023.8.16.0028</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>18/07/2024</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21/07/2026 00:28</t>
+          <t>21/07/2026 12:14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0000657-31.2008.8.16.0004</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10/02/2022</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21/07/2026 00:35</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0000083-06.2025.8.16.0103</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Reivindicação | Provas</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>26/06/2026 14:23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>05/07/2026 00:19</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0000877-47.2012.8.16.0179</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>05/07/2026 02:08</t>
+          <t>21/07/2026 13:16</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,37 +3215,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0030423-58.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>05/07/2026 02:20</t>
+          <t>21/07/2026 14:51</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>05/07/2026 02:33</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0000763-58.2023.8.16.0168</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>23/06/2026 13:13</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>05/07/2026 02:57</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,37 +3356,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>05/07/2026 03:14</t>
+          <t>04/07/2026 14:13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0023601-84.2015.8.16.0035</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>26/06/2026 19:03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>05/07/2026 03:18</t>
+          <t>04/07/2026 14:23</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0072332-62.2024.8.16.0014</t>
+          <t>0001218-93.2020.8.16.0114</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>05/07/2026 03:38</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0000813-54.2024.8.16.0102</t>
+          <t>0014658-88.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Superendividamento</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05/07/2026 04:36</t>
+          <t>04/07/2026 14:29</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0059414-60.2023.8.16.0014</t>
+          <t>0006751-45.2021.8.16.0034</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Esbulho / Turbação / Ameaça</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>23/06/2026 17:03</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05/07/2026 04:44</t>
+          <t>04/07/2026 14:30</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05/07/2026 04:48</t>
+          <t>04/07/2026 14:40</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0024386-41.2021.8.16.0001</t>
+          <t>0019503-80.2023.8.16.0001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>26/06/2026 15:43</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05/07/2026 05:25</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0002415-17.2024.8.16.0123</t>
+          <t>0000916-70.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edital</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>23/06/2026 15:33</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05/07/2026 05:29</t>
+          <t>04/07/2026 14:46</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05/07/2026 05:39</t>
+          <t>04/07/2026 14:51</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0020770-22.2025.8.16.0000</t>
+          <t>0039625-20.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3789,27 +3789,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>05/07/2026 05:40</t>
+          <t>04/07/2026 15:13</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0073849-47.2024.8.16.0000</t>
+          <t>0000016-67.1996.8.16.0132</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>05/07/2026 05:50</t>
+          <t>04/07/2026 15:14</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>05/07/2026 05:56</t>
+          <t>04/07/2026 15:17</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0017946-36.2021.8.16.0031</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>04/07/2026 16:08</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0000615-03.2021.8.16.0076</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>05/07/2026 06:21</t>
+          <t>04/07/2026 16:17</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,37 +4014,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0001883-03.1996.8.16.0001</t>
+          <t>0014490-80.2018.8.16.0129</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Agência e Distribuição</t>
+          <t>Roubo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01/07/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23/06/2026 20:43</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>23/06/2026 20:43</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>05/07/2026 06:42</t>
+          <t>04/07/2026 16:58</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0002286-77.2021.8.16.0103</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>04/07/2026 14:13</t>
+          <t>04/07/2026 17:04</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0020692-30.2022.8.16.0001</t>
+          <t>0002617-90.2023.8.16.0167</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rescisão do contrato e devolução do dinheiro | Indenização por Dano Moral</t>
+          <t>Feminicídio | Crime Tentado</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>04/07/2026 14:18</t>
+          <t>04/07/2026 17:05</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0023601-84.2015.8.16.0035</t>
+          <t>0086943-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>26/06/2026 16:33</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>04/07/2026 17:08</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0056285-13.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Contra a Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>04/07/2026 17:10</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0004582-39.2022.8.16.0038</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>04/07/2026 17:34</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0004396-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>04/07/2026 14:30</t>
+          <t>04/07/2026 17:49</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0001243-07.2021.8.16.0071</t>
+          <t>0051674-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>04/07/2026 14:33</t>
+          <t>04/07/2026 17:49</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,37 +4390,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0086374-27.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>04/07/2026 14:40</t>
+          <t>04/07/2026 17:52</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0019503-80.2023.8.16.0001</t>
+          <t>0001361-89.2024.8.16.0131</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>24/06/2026 13:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>24/06/2026 13:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>04/07/2026 17:54</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0000916-70.2024.8.16.0196</t>
+          <t>0043074-49.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>04/07/2026 17:54</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,37 +4531,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0001534-06.2021.8.16.0039</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>04/07/2026 14:51</t>
+          <t>04/07/2026 18:21</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0057622-45.2025.8.16.0000</t>
+          <t>0086199-35.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>04/07/2026 15:09</t>
+          <t>04/07/2026 18:23</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0090399-20.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04/07/2026 15:13</t>
+          <t>04/07/2026 18:58</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0000016-67.1996.8.16.0132</t>
+          <t>0003037-48.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>04/07/2026 15:14</t>
+          <t>04/07/2026 19:04</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0043261-54.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Perdas e Danos</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>04/07/2026 15:17</t>
+          <t>04/07/2026 19:18</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0128373-91.2024.8.16.0000</t>
+          <t>0020028-94.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>23/06/2026 14:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>23/06/2026 14:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>04/07/2026 15:51</t>
+          <t>04/07/2026 19:44</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>5001122-83.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Indenização por Dano Moral | Limitação de Juros</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>04/07/2026 16:08</t>
+          <t>04/07/2026 19:52</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0000615-03.2021.8.16.0076</t>
+          <t>0001619-98.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4870,27 +4870,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>04/07/2026 16:17</t>
+          <t>04/07/2026 20:04</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0006011-56.2022.8.16.0033</t>
+          <t>0050229-06.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4917,27 +4917,27 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atraso na Entrega do Imóvel | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>23/06/2026 16:13</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>04/07/2026 16:21</t>
+          <t>04/07/2026 20:24</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0014490-80.2018.8.16.0129</t>
+          <t>0000992-97.2019.8.16.0090</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Roubo</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>03/07/2026 13:03</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>03/07/2026 13:03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>04/07/2026 16:58</t>
+          <t>04/07/2026 20:29</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5001,37 +5001,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0002286-77.2021.8.16.0103</t>
+          <t>0036551-31.2018.8.16.0000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>04/07/2026 17:04</t>
+          <t>04/07/2026 20:45</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5048,37 +5048,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0002617-90.2023.8.16.0167</t>
+          <t>0048692-38.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Feminicídio | Crime Tentado</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>04/07/2026 17:05</t>
+          <t>04/07/2026 20:58</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0000857-02.2023.8.16.0040</t>
+          <t>0028301-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5105,27 +5105,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>23/06/2026 19:03</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>04/07/2026 17:08</t>
+          <t>04/07/2026 20:59</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0086943-28.2025.8.16.0000</t>
+          <t>0015085-47.2014.8.16.0185</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5152,27 +5152,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>26/06/2026 18:23</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>26/06/2026 18:23</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>04/07/2026 17:08</t>
+          <t>04/07/2026 21:05</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -489,37 +489,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0045998-62.2026.8.16.0000</t>
+          <t>0000016-67.1996.8.16.0132</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21/07/2026 17:04</t>
+          <t>24/07/2026 16:42</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0113087-73.2024.8.16.0000</t>
+          <t>0000168-18.2023.8.16.0117</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,27 +546,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>04/07/2026 23:36</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0000492-27.2021.8.16.0004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>ICMS / Incidência Sobre o Ativo Fixo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/07/2026 00:19</t>
+          <t>24/07/2026 11:02</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000877-47.2012.8.16.0179</t>
+          <t>0000530-18.2022.8.16.0129</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,27 +640,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>20/02/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/07/2026 02:08</t>
+          <t>24/07/2026 13:29</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/07/2026 02:20</t>
+          <t>21/07/2026 11:33</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,12 +724,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0000615-03.2021.8.16.0076</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -739,22 +739,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/07/2026 02:33</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/07/2026 03:14</t>
+          <t>21/07/2026 10:58</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/07/2026 03:18</t>
+          <t>21/07/2026 00:35</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0072332-62.2024.8.16.0014</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/07/2026 03:38</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/07/2026 04:36</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/07/2026 04:48</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0024386-41.2021.8.16.0001</t>
+          <t>0000916-70.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>26/06/2026 16:13</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/07/2026 05:25</t>
+          <t>24/07/2026 13:26</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0000994-81.2021.8.16.0095</t>
+          <t>0000992-97.2019.8.16.0090</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>03/07/2026 13:03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24/06/2026 13:43</t>
+          <t>03/07/2026 13:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/07/2026 05:39</t>
+          <t>24/07/2026 17:42</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0020770-22.2025.8.16.0000</t>
+          <t>0001164-06.2018.8.16.0080</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Direitos e Títulos de Crédito</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26/06/2026 19:23</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/07/2026 05:40</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,37 +1147,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0073849-47.2024.8.16.0000</t>
+          <t>0001218-93.2020.8.16.0114</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27/06/2025</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26/06/2026 17:03</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/07/2026 05:50</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0001252-45.2024.8.16.0141</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/07/2026 05:56</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0017946-36.2021.8.16.0031</t>
+          <t>0001490-67.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/07/2026 06:12</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0001534-06.2021.8.16.0039</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/07/2026 06:21</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0001619-98.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21/07/2026 00:10</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0001904-29.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21/07/2026 00:11</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0001590-04.2023.8.16.0028</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Prova Ilícita | Busca e Apreensão de Bens | Desclassificação | Aplicação da Pena | Regime inicial | Posse de Drogas para Consumo Pessoal</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18/07/2024</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26/06/2026 18:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21/07/2026 00:28</t>
+          <t>24/07/2026 13:40</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,37 +1476,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0000657-31.2008.8.16.0004</t>
+          <t>0002027-26.2023.8.16.0196</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10/02/2022</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>01/07/2026 14:21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21/07/2026 00:35</t>
+          <t>24/07/2026 12:32</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21/07/2026 01:24</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0002306-46.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21/07/2026 01:59</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0003037-48.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>04/07/2026 19:04</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0003125-86.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21/07/2026 02:10</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0037607-38.2014.8.16.0001</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Previdência privada | Indenização por Dano Material</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27/01/2021</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26/06/2026 15:53</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/07/2026 02:23</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>24/07/2026 12:41</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1909,27 +1909,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21/07/2026 04:31</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0121535-35.2024.8.16.0000</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21/07/2026 04:49</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0004883-55.2009.8.16.0130</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>24/07/2026 11:36</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0021062-79.2023.8.16.0031</t>
+          <t>0005460-15.2021.8.16.0194</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oferta e Publicidade</t>
+          <t>Propriedade Intelectual / Industrial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>01/07/2026 14:03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>01/07/2026 14:03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>24/07/2026 11:14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0012630-20.2024.8.16.0069</t>
+          <t>0005610-11.2023.8.16.0037</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Revisão de Juros Remuneratórios, Capitalização/Anatocismo</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26/06/2026 13:13</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21/07/2026 05:34</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0001988-16.2008.8.16.0047</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>26/06/2026 13:53</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21/07/2026 05:55</t>
+          <t>21/07/2026 01:24</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0006159-21.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21/07/2026 06:48</t>
+          <t>24/07/2026 13:03</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0006751-45.2021.8.16.0034</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Esbulho / Turbação / Ameaça</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21/07/2026 07:06</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0109651-43.2023.8.16.0000</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dano ao Erário | Tutela de Urgência | Obrigação de Fazer / Não Fazer | Ônus da Prova | Violação dos Princípios Administrativos</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05/06/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24/06/2026 15:13</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21/07/2026 07:14</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21/07/2026 08:04</t>
+          <t>21/07/2026 02:10</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0062792-32.2024.8.16.0000</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Desconsideração da Personalidade Jurídica | Pagamento</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18/07/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>26/06/2026 15:13</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21/07/2026 08:41</t>
+          <t>21/07/2026 00:11</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0009912-78.2015.8.16.0000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21/07/2026 08:43</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0010338-97.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2520,27 +2520,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0003664-09.2019.8.16.0113</t>
+          <t>0010792-81.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0011450-13.2020.8.16.0035</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Calúnia | Difamação</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>24/07/2026 11:14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0105436-87.2024.8.16.0000</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>24/06/2026 14:13</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21/07/2026 10:13</t>
+          <t>21/07/2026 10:56</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0123109-93.2024.8.16.0000</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Crédito Rural</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>26/06/2026 17:23</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>21/07/2026 12:14</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>21/07/2026 04:31</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0014658-88.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21/07/2026 10:56</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0000616-29.2022.8.16.0148</t>
+          <t>0020031-15.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>30/06/2026 09:43</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>30/06/2026 09:43</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21/07/2026 10:58</t>
+          <t>24/07/2026 11:16</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0000587-56.2022.8.16.0090</t>
+          <t>0021590-86.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Empreitada</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>30/04/2024</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21/07/2026 11:33</t>
+          <t>24/07/2026 11:07</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0006810-30.2021.8.16.0035</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Tutela de Urgência | Indenização por Dano Material</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24/06/2026 14:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21/07/2026 11:35</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0025126-43.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>02/07/2026 13:23</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>02/07/2026 13:23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21/07/2026 12:14</t>
+          <t>24/07/2026 16:46</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,7 +3074,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3084,27 +3084,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0000083-06.2025.8.16.0103</t>
+          <t>0029176-20.2017.8.16.0030</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reivindicação | Provas</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material | Oposição | Penhora / Depósito/ Avaliação | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>26/06/2026 14:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0100507-45.2023.8.16.0000</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21/07/2026 13:16</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0036551-31.2018.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>24/07/2026 12:37</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>21/07/2026 00:10</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,12 +3356,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0039625-20.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3371,22 +3371,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>04/07/2026 14:13</t>
+          <t>24/07/2026 13:40</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0023601-84.2015.8.16.0035</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>26/06/2026 19:03</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>04/07/2026 14:23</t>
+          <t>24/07/2026 13:59</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0041235-44.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3460,27 +3460,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>24/07/2026 11:15</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>04/07/2026 14:29</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3554,27 +3554,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>04/07/2026 14:30</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,37 +3591,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>04/07/2026 14:40</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0019503-80.2023.8.16.0001</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>26/06/2026 15:43</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0000916-70.2024.8.16.0196</t>
+          <t>0043074-49.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>04/07/2026 14:46</t>
+          <t>24/07/2026 16:15</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>04/07/2026 14:51</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0045998-62.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>04/07/2026 15:13</t>
+          <t>21/07/2026 17:04</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0000016-67.1996.8.16.0132</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>04/07/2026 15:14</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0049512-23.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>04/07/2026 15:17</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,7 +3920,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>04/07/2026 16:08</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0000615-03.2021.8.16.0076</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3977,27 +3977,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>04/07/2026 16:17</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0014490-80.2018.8.16.0129</t>
+          <t>0066543-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Roubo</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>30/06/2026 13:53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>30/06/2026 13:53</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>04/07/2026 16:58</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0002286-77.2021.8.16.0103</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>04/07/2026 17:04</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,37 +4108,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0002617-90.2023.8.16.0167</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Feminicídio | Crime Tentado</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>04/07/2026 17:05</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,7 +4155,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0086943-28.2025.8.16.0000</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4165,27 +4165,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>26/06/2026 16:33</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>04/07/2026 17:08</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0056285-13.2024.8.16.0014</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Contra a Mulher | Ameaça</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>04/07/2026 17:10</t>
+          <t>21/07/2026 01:59</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0004582-39.2022.8.16.0038</t>
+          <t>0082575-10.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>04/07/2026 17:34</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0004396-28.2025.8.16.0000</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>04/07/2026 17:49</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0051674-22.2021.8.16.0014</t>
+          <t>0086374-27.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>04/07/2026 17:49</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0086374-27.2025.8.16.0000</t>
+          <t>0090399-20.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>04/07/2026 17:52</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0001361-89.2024.8.16.0131</t>
+          <t>0090909-33.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Compromisso | Locação de Imóvel</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>24/06/2026 13:13</t>
+          <t>01/07/2026 14:43</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>24/06/2026 13:13</t>
+          <t>01/07/2026 14:43</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>04/07/2026 17:54</t>
+          <t>24/07/2026 10:33</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,37 +4484,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0043074-49.2024.8.16.0000</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>04/07/2026 17:54</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0001534-06.2021.8.16.0039</t>
+          <t>0093616-08.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>02/07/2026 15:13</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>02/07/2026 15:13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>04/07/2026 18:21</t>
+          <t>24/07/2026 11:39</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0086199-35.2018.8.16.0014</t>
+          <t>0097707-10.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>04/07/2026 18:23</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0090399-20.2024.8.16.0000</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>02/07/2026 13:43</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>02/07/2026 13:43</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04/07/2026 18:58</t>
+          <t>21/07/2026 13:16</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0003037-48.2023.8.16.0021</t>
+          <t>0113087-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>04/07/2026 19:04</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0043261-54.2020.8.16.0014</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Perdas e Danos</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>04/07/2026 19:18</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0020028-94.2025.8.16.0000</t>
+          <t>0121535-35.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4776,27 +4776,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>04/07/2026 19:44</t>
+          <t>21/07/2026 04:49</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>04/07/2026 19:52</t>
+          <t>24/07/2026 16:42</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4852,335 +4852,6 @@
         </is>
       </c>
       <c r="I94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>0001619-98.2024.8.16.0196</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>25/09/2025</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>01/07/2026 20:23</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>01/07/2026 20:23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>04/07/2026 20:04</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>0050229-06.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>04/07/2026 20:24</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>0000992-97.2019.8.16.0090</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>03/07/2026 13:03</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>03/07/2026 13:03</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>04/07/2026 20:29</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>0036551-31.2018.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Condomínio</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>30/12/1899</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>29/06/2026 13:13</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>29/06/2026 13:13</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>04/07/2026 20:45</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>0048692-38.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>29/06/2026 13:03</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>29/06/2026 13:03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>04/07/2026 20:58</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>0028301-62.2025.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Compra e Venda</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>05/03/2026</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>01/07/2026 14:53</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>01/07/2026 14:53</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>04/07/2026 20:59</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>0015085-47.2014.8.16.0185</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>26/06/2026 18:23</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>26/06/2026 18:23</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>04/07/2026 21:05</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000587-56.2022.8.16.0090</t>
+          <t>0000615-03.2021.8.16.0076</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22/02/2024</t>
+          <t>12/07/2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/07/2026 15:03</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21/07/2026 11:33</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000615-03.2021.8.16.0076</t>
+          <t>0000657-31.2008.8.16.0004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,27 +734,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Descontos Indevidos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>10/02/2022</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>21/07/2026 00:35</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000616-29.2022.8.16.0148</t>
+          <t>0000739-43.2021.8.16.0154</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/07/2026 15:43</t>
+          <t>02/07/2026 16:36</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21/07/2026 10:58</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -818,37 +818,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0000657-31.2008.8.16.0004</t>
+          <t>0000813-54.2024.8.16.0102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Descontos Indevidos</t>
+          <t>Superendividamento</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10/02/2022</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>01/07/2026 19:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21/07/2026 00:35</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000739-43.2021.8.16.0154</t>
+          <t>0000877-47.2012.8.16.0179</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,27 +875,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>ISS/ Imposto sobre Serviços</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>02/07/2026 16:13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000813-54.2024.8.16.0102</t>
+          <t>0000916-70.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,27 +922,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Superendividamento</t>
+          <t>Roubo Majorado</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/07/2026 19:13</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 13:26</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0000877-47.2012.8.16.0179</t>
+          <t>0000992-97.2019.8.16.0090</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -969,27 +969,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ISS/ Imposto sobre Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>03/07/2026 13:03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>02/07/2026 16:13</t>
+          <t>03/07/2026 13:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>24/07/2026 12:42</t>
+          <t>24/07/2026 17:42</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0000916-70.2024.8.16.0196</t>
+          <t>0001252-45.2024.8.16.0141</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Roubo Majorado</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>24/07/2026 13:26</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0000992-97.2019.8.16.0090</t>
+          <t>0001490-67.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>03/07/2026 13:03</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>03/07/2026 13:03</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24/07/2026 17:42</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001164-06.2018.8.16.0080</t>
+          <t>0001534-06.2021.8.16.0039</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01/07/2026 17:33</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>01/07/2026 17:33</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,27 +1157,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001252-45.2024.8.16.0141</t>
+          <t>0001619-98.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,37 +1241,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001490-67.2023.8.16.0119</t>
+          <t>0001775-57.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 12:49</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001534-06.2021.8.16.0039</t>
+          <t>0001904-29.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>24/07/2026 12:42</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001619-98.2024.8.16.0196</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 13:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001904-29.2022.8.16.0013</t>
+          <t>0002027-26.2023.8.16.0196</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>01/07/2026 14:21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:32</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>24/07/2026 13:40</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002027-26.2023.8.16.0196</t>
+          <t>0002286-77.2021.8.16.0103</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/07/2026 14:21</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>24/07/2026 12:32</t>
+          <t>24/07/2026 12:52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0002617-90.2023.8.16.0167</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Feminicídio | Crime Tentado</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21/07/2026 08:43</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002306-46.2022.8.16.0196</t>
+          <t>0003037-48.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Furto</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0003037-48.2023.8.16.0021</t>
+          <t>0003125-86.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>04/07/2026 19:04</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003125-86.2022.8.16.0000</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24/07/2026 10:37</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,37 +1758,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003664-09.2019.8.16.0113</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0003839-05.2017.8.16.0038</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Uso de documento falso | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>24/07/2026 10:37</t>
+          <t>24/07/2026 20:04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0004396-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1914,22 +1914,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>21/07/2026 06:48</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1961,22 +1961,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>24/07/2026 10:58</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004883-55.2009.8.16.0130</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>01/07/2026 15:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01/07/2026 15:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24/07/2026 11:36</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0005460-15.2021.8.16.0194</t>
+          <t>0004582-39.2022.8.16.0038</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Propriedade Intelectual / Industrial</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>01/07/2026 14:03</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>01/07/2026 14:03</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>24/07/2026 11:14</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0005610-11.2023.8.16.0037</t>
+          <t>0004883-55.2009.8.16.0130</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>03/07/2026 13:23</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>03/07/2026 13:23</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 11:36</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0005460-15.2021.8.16.0194</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Propriedade Intelectual / Industrial</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21/07/2026 01:24</t>
+          <t>24/07/2026 11:14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0006159-21.2024.8.16.0058</t>
+          <t>0005610-11.2023.8.16.0037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,27 +2191,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>24/07/2026 13:03</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>21/07/2026 01:24</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0006159-21.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 13:03</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21/07/2026 02:10</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21/07/2026 08:27</t>
+          <t>21/07/2026 02:10</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21/07/2026 00:11</t>
+          <t>21/07/2026 08:27</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,37 +2463,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0009912-78.2015.8.16.0000</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>02/07/2026 15:53</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>02/07/2026 15:53</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>21/07/2026 00:11</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0010338-97.2019.8.16.0017</t>
+          <t>0009912-78.2015.8.16.0000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seguro | Direitos e Títulos de Crédito</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20/09/2024</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>01/07/2026 18:03</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01/07/2026 18:03</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0010792-81.2024.8.16.0056</t>
+          <t>0010338-97.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 10:02</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 10:02</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0011450-13.2020.8.16.0035</t>
+          <t>0010792-81.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Calúnia | Difamação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0011450-13.2020.8.16.0035</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Calúnia | Difamação</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>24/07/2026 11:14</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,7 +2698,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21/07/2026 10:56</t>
+          <t>24/07/2026 11:14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0014242-18.2015.8.16.0001</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nota Promissória</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01/07/2026 20:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21/07/2026 12:14</t>
+          <t>21/07/2026 10:56</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0020028-94.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0029176-20.2017.8.16.0030</t>
+          <t>0028301-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3131,27 +3131,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material | Oposição | Penhora / Depósito/ Avaliação | Cumprimento Provisório de Sentença</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>24/07/2026 19:05</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0029176-20.2017.8.16.0030</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material | Oposição | Penhora / Depósito/ Avaliação | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21/07/2026 07:06</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0030423-58.2020.8.16.0021</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21/07/2026 14:51</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3507,27 +3507,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0041716-83.2023.8.16.0000</t>
+          <t>0043074-49.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21/07/2026 12:44</t>
+          <t>24/07/2026 16:15</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0043261-54.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Perdas e Danos</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 19:44</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0042798-52.2023.8.16.0000</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,37 +3685,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0043074-49.2024.8.16.0000</t>
+          <t>0048692-38.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>24/07/2026 16:15</t>
+          <t>24/07/2026 19:05</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0043986-12.2025.8.16.0000</t>
+          <t>0049512-23.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
+          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21/07/2026 15:12</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0045998-62.2026.8.16.0000</t>
+          <t>0050229-06.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21/07/2026 17:04</t>
+          <t>24/07/2026 20:44</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,37 +3826,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0049512-23.2026.8.16.0000</t>
+          <t>0051674-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
+          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>01/07/2026 17:53</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>01/07/2026 17:53</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>21/07/2026 08:04</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0056285-13.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Contra a Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0090909-33.2024.8.16.0000</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Compromisso | Locação de Imóvel</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>01/07/2026 14:43</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>01/07/2026 14:43</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>24/07/2026 10:33</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0093616-08.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>02/07/2026 15:13</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>02/07/2026 15:13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>24/07/2026 11:39</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0093616-08.2023.8.16.0000</t>
+          <t>0095221-86.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Recuperação judicial e Falência | Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>02/07/2026 15:13</t>
+          <t>07/07/2026 14:10</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>02/07/2026 15:13</t>
+          <t>07/07/2026 15:23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>24/07/2026 11:39</t>
+          <t>24/07/2026 12:52</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0097707-10.2024.8.16.0000</t>
+          <t>0099012-29.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Interpretação / Revisão de Contrato</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01/07/2026 16:23</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 19:03</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0100507-45.2023.8.16.0000</t>
+          <t>0113087-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hipoteca</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>01/07/2026 13:33</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>21/07/2026 13:16</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0113087-73.2024.8.16.0000</t>
+          <t>0120044-90.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural</t>
+          <t>Compensação</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>21/07/2026 03:37</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>5001122-83.2016.8.16.0000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4729,27 +4729,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Indenização por Dano Moral | Limitação de Juros</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>24/07/2026 16:42</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4758,100 +4758,6 @@
         </is>
       </c>
       <c r="I92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>0121535-35.2024.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>28/11/2025</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:43</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>02/07/2026 16:43</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>21/07/2026 04:49</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>5001122-83.2016.8.16.0000</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Indenização por Dano Moral | Limitação de Juros</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>10/11/2025</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>01/07/2026 18:03</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>01/07/2026 18:03</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>24/07/2026 16:42</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0001252-45.2024.8.16.0141</t>
+          <t>0001164-06.2018.8.16.0080</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001490-67.2023.8.16.0119</t>
+          <t>0001218-93.2020.8.16.0114</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>02/02/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001534-06.2021.8.16.0039</t>
+          <t>0001252-45.2024.8.16.0141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24/07/2026 12:42</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0001490-67.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,22 +1157,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001619-98.2024.8.16.0196</t>
+          <t>0001534-06.2021.8.16.0039</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>29/06/2026 14:03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001775-57.2022.8.16.0196</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1256,22 +1256,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01/07/2026 17:33</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 17:33</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24/07/2026 12:49</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001904-29.2022.8.16.0013</t>
+          <t>0001619-98.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0001775-57.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24/07/2026 13:40</t>
+          <t>24/07/2026 12:49</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0002027-26.2023.8.16.0196</t>
+          <t>0001904-29.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>01/07/2026 14:21</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24/07/2026 12:32</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21/07/2026 08:43</t>
+          <t>24/07/2026 13:40</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002286-77.2021.8.16.0103</t>
+          <t>0002027-26.2023.8.16.0196</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>01/07/2026 14:21</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>24/07/2026 12:52</t>
+          <t>24/07/2026 12:32</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,37 +1523,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002617-90.2023.8.16.0167</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Feminicídio | Crime Tentado</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0003037-48.2023.8.16.0021</t>
+          <t>0002286-77.2021.8.16.0103</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24/07/2026 18:52</t>
+          <t>24/07/2026 12:52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,7 +1617,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0003125-86.2022.8.16.0000</t>
+          <t>0002306-46.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1627,27 +1627,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>24/07/2026 10:37</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>0002617-90.2023.8.16.0167</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Feminicídio | Crime Tentado</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003664-09.2019.8.16.0113</t>
+          <t>0003037-48.2023.8.16.0021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>29/06/2026 15:03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,32 +1758,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0003125-86.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003839-05.2017.8.16.0038</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Uso de documento falso | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>24/07/2026 20:04</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,37 +1852,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>24/07/2026 12:41</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0004396-28.2025.8.16.0000</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0003839-05.2017.8.16.0038</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Uso de documento falso | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21/07/2026 06:48</t>
+          <t>24/07/2026 20:04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0004375-53.2016.8.16.0037</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>26/08/2021</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>29/06/2026 14:43</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24/07/2026 10:58</t>
+          <t>24/07/2026 12:41</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0004582-39.2022.8.16.0038</t>
+          <t>0004396-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0004883-55.2009.8.16.0130</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>01/07/2026 15:33</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>01/07/2026 15:33</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>24/07/2026 11:36</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0005460-15.2021.8.16.0194</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Propriedade Intelectual / Industrial</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01/07/2026 14:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01/07/2026 14:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24/07/2026 11:14</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0005610-11.2023.8.16.0037</t>
+          <t>0004582-39.2022.8.16.0038</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>03/07/2026 13:23</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>03/07/2026 13:23</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0004883-55.2009.8.16.0130</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21/07/2026 01:24</t>
+          <t>24/07/2026 11:36</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0006159-21.2024.8.16.0058</t>
+          <t>0005460-15.2021.8.16.0194</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Propriedade Intelectual / Industrial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 14:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 14:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>24/07/2026 13:03</t>
+          <t>24/07/2026 11:14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0005610-11.2023.8.16.0037</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2337,22 +2337,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0006153-05.2017.8.16.0011</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Preconceituosa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21/07/2026 02:10</t>
+          <t>21/07/2026 01:24</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0006159-21.2024.8.16.0058</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2426,27 +2426,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21/07/2026 08:27</t>
+          <t>24/07/2026 13:03</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0006751-45.2021.8.16.0034</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Esbulho / Turbação / Ameaça</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>29/06/2026 13:53</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21/07/2026 00:11</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,37 +2510,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0009912-78.2015.8.16.0000</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>02/07/2026 15:53</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/07/2026 15:53</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0010338-97.2019.8.16.0017</t>
+          <t>0008050-15.2022.8.16.0069</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seguro | Direitos e Títulos de Crédito</t>
+          <t>Contratos Bancários | Repetição do Indébito</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20/09/2024</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>01/07/2026 18:03</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>01/07/2026 18:03</t>
+          <t>29/06/2026 14:23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>21/07/2026 02:10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0010792-81.2024.8.16.0056</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>01/07/2026 10:02</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>01/07/2026 10:02</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>21/07/2026 08:27</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0011450-13.2020.8.16.0035</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Calúnia | Difamação</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>21/07/2026 00:11</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0009912-78.2015.8.16.0000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24/07/2026 11:14</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0012598-91.2025.8.16.0000</t>
+          <t>0010338-97.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2755,27 +2755,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Seguro | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21/07/2026 10:56</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0010792-81.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21/07/2026 04:31</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0020028-94.2025.8.16.0000</t>
+          <t>0011450-13.2020.8.16.0035</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2849,27 +2849,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Calúnia | Difamação</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24/07/2026 18:52</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,37 +2886,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0020031-15.2026.8.16.0000</t>
+          <t>0012547-80.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>30/06/2026 09:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>30/06/2026 09:43</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24/07/2026 11:16</t>
+          <t>24/07/2026 11:14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,37 +2933,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0021590-86.2022.8.16.0019</t>
+          <t>0014373-48.2021.8.16.0044</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Empreitada</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>30/04/2024</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>24/07/2026 11:07</t>
+          <t>21/07/2026 04:31</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0014658-88.2018.8.16.0030</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0025126-43.2024.8.16.0017</t>
+          <t>0020028-94.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>02/07/2026 13:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>02/07/2026 13:23</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>24/07/2026 16:46</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0020031-15.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>30/06/2026 09:43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>30/06/2026 09:43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>24/07/2026 11:16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0028301-62.2025.8.16.0000</t>
+          <t>0021590-86.2022.8.16.0019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Empreitada</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>30/04/2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>24/07/2026 19:05</t>
+          <t>24/07/2026 11:07</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0029176-20.2017.8.16.0030</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3178,27 +3178,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material | Oposição | Penhora / Depósito/ Avaliação | Cumprimento Provisório de Sentença</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0025126-43.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>02/07/2026 13:23</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>02/07/2026 13:23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21/07/2026 07:06</t>
+          <t>24/07/2026 16:46</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,37 +3262,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0036551-31.2018.8.16.0000</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>24/07/2026 12:37</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,37 +3309,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0028301-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21/07/2026 00:10</t>
+          <t>24/07/2026 19:05</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0029176-20.2017.8.16.0030</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material | Oposição | Penhora / Depósito/ Avaliação | Cumprimento Provisório de Sentença</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>29/06/2026 13:33</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>24/07/2026 13:40</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>24/07/2026 13:59</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0036551-31.2018.8.16.0000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Condomínio</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>30/12/1899</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>29/06/2026 13:13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>24/07/2026 11:15</t>
+          <t>24/07/2026 12:37</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0036884-38.2018.8.16.0014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Furto Qualificado</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>21/07/2026 00:10</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0043074-49.2024.8.16.0000</t>
+          <t>0039625-20.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>29/06/2026 15:33</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>24/07/2026 16:15</t>
+          <t>24/07/2026 13:40</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0043261-54.2020.8.16.0014</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Perdas e Danos</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>24/07/2026 19:44</t>
+          <t>24/07/2026 13:59</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,37 +3638,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0041235-44.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Práticas Abusivas</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>18/06/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 11:15</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0048692-38.2025.8.16.0000</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>24/07/2026 19:05</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0049512-23.2026.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01/07/2026 17:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/07/2026 17:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0050229-06.2024.8.16.0000</t>
+          <t>0043074-49.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>24/07/2026 20:44</t>
+          <t>24/07/2026 16:15</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0043261-54.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Perdas e Danos</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21/07/2026 08:04</t>
+          <t>24/07/2026 19:44</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0051674-22.2021.8.16.0014</t>
+          <t>0048561-97.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>29/06/2026 14:13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0048692-38.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>29/06/2026 13:03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 19:05</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0056285-13.2024.8.16.0014</t>
+          <t>0049512-23.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Contra a Mulher | Ameaça</t>
+          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0066543-90.2025.8.16.0000</t>
+          <t>0050229-06.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>30/06/2026 13:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>30/06/2026 13:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>24/07/2026 12:42</t>
+          <t>24/07/2026 20:44</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0051674-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0072332-62.2024.8.16.0014</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0056285-13.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Contra a Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>21/07/2026 01:59</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0082575-10.2024.8.16.0000</t>
+          <t>0066543-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>30/06/2026 13:53</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>30/06/2026 13:53</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>24/07/2026 10:58</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0086374-27.2025.8.16.0000</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0090399-20.2024.8.16.0000</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>02/07/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>02/07/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0091320-13.2023.8.16.0000</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>02/07/2026 11:50</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>21/07/2026 01:59</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0093616-08.2023.8.16.0000</t>
+          <t>0082575-10.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prescrição e Decadência</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>31/07/2024</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02/07/2026 15:13</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>02/07/2026 15:13</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>24/07/2026 11:39</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0095221-86.2023.8.16.0000</t>
+          <t>0086039-76.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Recuperação judicial e Falência | Desconsideração da Personalidade Jurídica</t>
+          <t>Rescisão / Resolução</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20/05/2025</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>07/07/2026 14:10</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>07/07/2026 15:23</t>
+          <t>29/06/2026 14:33</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>24/07/2026 12:52</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0099012-29.2024.8.16.0000</t>
+          <t>0086374-27.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Interpretação / Revisão de Contrato</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>24/07/2026 19:03</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0113087-73.2024.8.16.0000</t>
+          <t>0090399-20.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Rural</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4672,7 +4672,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0120044-90.2024.8.16.0000</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4682,27 +4682,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Compensação</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>21/07/2026 03:37</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4719,45 +4719,374 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>0093616-08.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Prescrição e Decadência</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>31/07/2024</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:13</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>24/07/2026 11:39</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0095221-86.2023.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Recuperação judicial e Falência | Desconsideração da Personalidade Jurídica</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>20/05/2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>07/07/2026 14:10</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>07/07/2026 15:23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>24/07/2026 12:52</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0097707-10.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Bancário</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:23</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>24/07/2026 11:01</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0099012-29.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Interpretação / Revisão de Contrato</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>29/06/2026 14:23</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>24/07/2026 19:03</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0113087-73.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cédula de Crédito Rural</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>01/07/2026 14:13</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>01/07/2026 14:13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>24/07/2026 12:48</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0120044-90.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Compensação</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>29/06/2026 13:03</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>21/07/2026 03:37</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0121535-35.2024.8.16.0000</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Seguro | Sucumbenciais | Ordem de Preferência</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>28/11/2025</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:43</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:43</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>21/07/2026 04:49</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>5001122-83.2016.8.16.0000</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Agravo em Recurso Especial</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Agravo em Recurso Especial</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
         <is>
           <t>Indenização por Dano Moral | Limitação de Juros</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>10/11/2025</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>01/07/2026 18:03</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>01/07/2026 18:03</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>24/07/2026 16:42</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>

--- a/docs/resultados.xlsx
+++ b/docs/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -583,37 +583,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0000492-27.2021.8.16.0004</t>
+          <t>0000530-18.2022.8.16.0129</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ICMS / Incidência Sobre o Ativo Fixo</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20/05/2025</t>
+          <t>20/02/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02/07/2026 16:36</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24/07/2026 11:02</t>
+          <t>24/07/2026 13:29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,37 +630,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0000530-18.2022.8.16.0129</t>
+          <t>0000587-56.2022.8.16.0090</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20/02/2025</t>
+          <t>22/02/2024</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>02/07/2026 15:03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24/07/2026 13:29</t>
+          <t>21/07/2026 11:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -677,37 +677,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000615-03.2021.8.16.0076</t>
+          <t>0000616-29.2022.8.16.0148</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral | Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12/07/2024</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>02/07/2026 15:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>21/07/2026 10:58</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0001218-93.2020.8.16.0114</t>
+          <t>0001252-45.2024.8.16.0141</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>02/02/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0001252-45.2024.8.16.0141</t>
+          <t>0001490-67.2023.8.16.0119</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0001490-67.2023.8.16.0119</t>
+          <t>0001549-16.2021.8.16.0090</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1157,22 +1157,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>18/09/2023</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>01/07/2026 14:01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1194,37 +1194,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0001534-06.2021.8.16.0039</t>
+          <t>0001619-98.2024.8.16.0196</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prestação de Serviços</t>
+          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29/06/2026 14:03</t>
+          <t>01/07/2026 20:23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24/07/2026 12:42</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0001549-16.2021.8.16.0090</t>
+          <t>0001775-57.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1256,22 +1256,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18/09/2023</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>01/07/2026 14:01</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>01/07/2026 17:33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 12:49</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1288,37 +1288,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0001619-98.2024.8.16.0196</t>
+          <t>0001904-29.2022.8.16.0013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Crimes do Sistema Nacional de Armas | Aplicação da Pena</t>
+          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>01/07/2026 20:23</t>
+          <t>02/07/2026 14:23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0001775-57.2022.8.16.0196</t>
+          <t>0002022-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>02/12/2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01/07/2026 17:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01/07/2026 17:33</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24/07/2026 12:49</t>
+          <t>24/07/2026 13:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0001904-29.2022.8.16.0013</t>
+          <t>0002027-26.2023.8.16.0196</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Multas e demais Sanções | Efeito Suspensivo / Impugnação / Embargos à Execução</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>01/07/2026 14:21</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02/07/2026 14:23</t>
+          <t>03/07/2026 07:18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:32</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0002022-73.2024.8.16.0000</t>
+          <t>0002180-67.2023.8.16.0064</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02/12/2024</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>24/07/2026 13:40</t>
+          <t>21/07/2026 08:43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0002027-26.2023.8.16.0196</t>
+          <t>0002286-77.2021.8.16.0103</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>22/01/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01/07/2026 14:21</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>03/07/2026 07:18</t>
+          <t>01/07/2026 16:03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>24/07/2026 12:32</t>
+          <t>24/07/2026 12:52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0002180-67.2023.8.16.0064</t>
+          <t>0002306-46.2022.8.16.0196</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Furto</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21/07/2026 08:43</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0002286-77.2021.8.16.0103</t>
+          <t>0002367-58.2023.8.16.0102</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seguro</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22/01/2024</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>01/07/2026 09:30</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>01/07/2026 16:03</t>
+          <t>01/07/2026 09:30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24/07/2026 12:52</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1617,37 +1617,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0002306-46.2022.8.16.0196</t>
+          <t>0002617-90.2023.8.16.0167</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Furto</t>
+          <t>Feminicídio | Crime Tentado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>03/07/2026 13:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1664,37 +1664,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0002617-90.2023.8.16.0167</t>
+          <t>0003125-86.2022.8.16.0000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Feminicídio | Crime Tentado</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>03/07/2026 13:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0003037-48.2023.8.16.0021</t>
+          <t>0003300-85.2019.8.16.0194</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1721,27 +1721,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>26/05/2021</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>29/06/2026 15:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24/07/2026 18:52</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1758,7 +1758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0003125-86.2022.8.16.0000</t>
+          <t>0003664-09.2019.8.16.0113</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Mandato</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>01/07/2026 16:53</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>24/07/2026 10:37</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1805,37 +1805,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0003300-85.2019.8.16.0194</t>
+          <t>0003837-28.2018.8.16.0126</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cheque | Promessa de Compra e Venda | Execução de Título Extrajudicial | Penhora / Depósito/ Avaliação | Embargos de Terceiro</t>
+          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26/05/2021</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>30/06/2026 14:33</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>24/07/2026 10:37</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0003664-09.2019.8.16.0113</t>
+          <t>0003839-05.2017.8.16.0038</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mandato</t>
+          <t>Tráfico de Drogas e Condutas Afins | Uso de documento falso | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 20:04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1899,37 +1899,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0003837-28.2018.8.16.0126</t>
+          <t>0004349-19.2023.8.16.0196</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Embargos de Divergência em Agravo em Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Defeito, nulidade ou anulação</t>
+          <t>Roubo Majorado | Crimes de Trânsito</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>27/02/2025</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30/06/2026 14:33</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>24/07/2026 10:37</t>
+          <t>24/07/2026 18:40</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0003839-05.2017.8.16.0038</t>
+          <t>0004396-28.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1956,27 +1956,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Uso de documento falso | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/07/2026 16:53</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>24/07/2026 20:04</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1993,37 +1993,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0004375-53.2016.8.16.0037</t>
+          <t>0004398-95.2025.8.16.0097</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26/08/2021</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>29/06/2026 14:43</t>
+          <t>01/07/2026 11:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24/07/2026 12:41</t>
+          <t>21/07/2026 06:48</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2040,7 +2040,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0004396-28.2025.8.16.0000</t>
+          <t>0004550-45.2024.8.16.0044</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2055,22 +2055,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>01/07/2026 16:13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0004398-95.2025.8.16.0097</t>
+          <t>0004582-39.2022.8.16.0038</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2097,27 +2097,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>12/08/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>01/07/2026 11:03</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21/07/2026 06:48</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0004550-45.2024.8.16.0044</t>
+          <t>0004883-55.2009.8.16.0130</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>01/07/2026 16:13</t>
+          <t>01/07/2026 15:33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24/07/2026 10:58</t>
+          <t>24/07/2026 11:36</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0004582-39.2022.8.16.0038</t>
+          <t>0005610-11.2023.8.16.0037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Defeito, nulidade ou anulação</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>01/07/2026 19:53</t>
+          <t>03/07/2026 13:23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0004883-55.2009.8.16.0130</t>
+          <t>0006514-37.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Contratos Bancários</t>
+          <t>Vícios de Construção | Ônus da Prova | Indenização por Dano Moral | Obrigação de Fazer / Não Fazer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>01/07/2026 15:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>01/07/2026 15:33</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>24/07/2026 11:36</t>
+          <t>24/07/2026 17:40</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0005460-15.2021.8.16.0194</t>
+          <t>0007244-77.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2285,27 +2285,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Propriedade Intelectual / Industrial</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>01/07/2026 14:03</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>01/07/2026 14:03</t>
+          <t>01/07/2026 13:03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>24/07/2026 11:14</t>
+          <t>21/07/2026 09:15</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0005610-11.2023.8.16.0037</t>
+          <t>0009249-12.2019.8.16.0026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2332,27 +2332,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Servidão Administrativa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>03/07/2026 13:23</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>03/07/2026 13:23</t>
+          <t>02/07/2026 14:53</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>21/07/2026 08:27</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0006153-05.2017.8.16.0011</t>
+          <t>0009625-61.2024.8.16.0013</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Preconceituosa</t>
+          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21/07/2026 01:24</t>
+          <t>21/07/2026 00:11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2416,37 +2416,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0006159-21.2024.8.16.0058</t>
+          <t>0009912-78.2015.8.16.0000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Empréstimo consignado | Indenização por Dano Moral | Indenização por Dano Material</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 15:53</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24/07/2026 13:03</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0006751-45.2021.8.16.0034</t>
+          <t>0010338-97.2019.8.16.0017</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Esbulho / Turbação / Ameaça</t>
+          <t>Seguro | Direitos e Títulos de Crédito</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29/06/2026 13:53</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0007244-77.2024.8.16.0014</t>
+          <t>0010792-81.2024.8.16.0056</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2525,22 +2525,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>01/07/2026 13:03</t>
+          <t>01/07/2026 10:02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21/07/2026 09:15</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0008050-15.2022.8.16.0069</t>
+          <t>0011450-13.2020.8.16.0035</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2567,27 +2567,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Repetição do Indébito</t>
+          <t>Calúnia | Difamação</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29/06/2026 14:23</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21/07/2026 02:10</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2604,7 +2604,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0009249-12.2019.8.16.0026</t>
+          <t>0012598-91.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Servidão Administrativa</t>
+          <t>Contratos Bancários</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2624,17 +2624,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>02/07/2026 14:53</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21/07/2026 08:27</t>
+          <t>21/07/2026 10:56</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0009625-61.2024.8.16.0013</t>
+          <t>0014242-18.2015.8.16.0001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Restituição de Coisas Apreendidas | Tráfico de Drogas e Condutas Afins</t>
+          <t>Nota Promissória</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>01/07/2026 20:33</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21/07/2026 00:11</t>
+          <t>21/07/2026 12:14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2698,37 +2698,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0009912-78.2015.8.16.0000</t>
+          <t>0015944-52.2022.8.16.0001</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Rescisão do contrato e devolução do dinheiro | Perdas e Danos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02/07/2026 15:53</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>02/07/2026 15:53</t>
+          <t>01/07/2026 19:53</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 19:07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2745,37 +2745,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0010338-97.2019.8.16.0017</t>
+          <t>0016945-36.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seguro | Direitos e Títulos de Crédito</t>
+          <t>Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20/09/2024</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>01/07/2026 18:03</t>
+          <t>30/06/2026 08:10</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>01/07/2026 18:03</t>
+          <t>30/06/2026 08:10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 18:40</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0010792-81.2024.8.16.0056</t>
+          <t>0020028-94.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Locação de Imóvel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>01/07/2026 10:02</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>01/07/2026 10:02</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24/07/2026 12:48</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2839,37 +2839,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0011450-13.2020.8.16.0035</t>
+          <t>0020031-15.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Calúnia | Difamação</t>
+          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>30/06/2026 09:43</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>30/06/2026 09:43</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 11:16</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0012547-80.2025.8.16.0000</t>
+          <t>0022499-27.2014.8.16.0014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Receptação</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>01/07/2026 18:23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24/07/2026 11:14</t>
+          <t>21/07/2026 09:34</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0014373-48.2021.8.16.0044</t>
+          <t>0025126-43.2024.8.16.0017</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 13:23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>02/07/2026 13:23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21/07/2026 04:31</t>
+          <t>24/07/2026 16:46</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0014658-88.2018.8.16.0030</t>
+          <t>0026834-21.2020.8.16.0001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>05/03/2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 15:03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 12:58</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0020028-94.2025.8.16.0000</t>
+          <t>0028301-62.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3037,27 +3037,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Locação de Imóvel</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>05/03/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>24/07/2026 18:52</t>
+          <t>24/07/2026 19:05</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3074,37 +3074,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0020031-15.2026.8.16.0000</t>
+          <t>0029996-22.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Associação para a Produção e Tráfico e Condutas Afins</t>
+          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30/06/2026 09:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>30/06/2026 09:43</t>
+          <t>01/07/2026 18:43</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>24/07/2026 11:16</t>
+          <t>21/07/2026 07:06</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3121,37 +3121,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0021590-86.2022.8.16.0019</t>
+          <t>0030423-58.2020.8.16.0021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Empreitada</t>
+          <t>Seguro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>30/04/2024</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>24/07/2026 11:07</t>
+          <t>21/07/2026 14:51</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0022499-27.2014.8.16.0014</t>
+          <t>0033064-69.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Receptação</t>
+          <t>Compra e Venda</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>08/07/2024</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>01/07/2026 18:23</t>
+          <t>01/07/2026 18:03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>24/07/2026 17:58</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3215,7 +3215,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0025126-43.2024.8.16.0017</t>
+          <t>0034802-03.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,27 +3225,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Franquia | Requerimento de Reintegração de Posse</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>05/09/2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>02/07/2026 13:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>02/07/2026 13:23</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>24/07/2026 16:46</t>
+          <t>24/07/2026 20:16</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3262,7 +3262,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0026834-21.2020.8.16.0001</t>
+          <t>0036073-47.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3272,27 +3272,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Recuperação judicial e Falência</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>05/03/2024</t>
+          <t>28/11/2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 11:58</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>01/07/2026 15:03</t>
+          <t>02/07/2026 11:58</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>24/07/2026 20:16</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3309,7 +3309,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0028301-62.2025.8.16.0000</t>
+          <t>0041154-84.2018.8.16.0021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3319,27 +3319,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Compra e Venda</t>
+          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>05/03/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>01/07/2026 17:43</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>24/07/2026 19:05</t>
+          <t>24/07/2026 13:59</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0029176-20.2017.8.16.0030</t>
+          <t>0041690-77.2022.8.16.0014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3366,27 +3366,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral | Indenização por Dano Material | Oposição | Penhora / Depósito/ Avaliação | Cumprimento Provisório de Sentença</t>
+          <t>Crimes contra a Ordem Tributária</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>29/06/2026 13:33</t>
+          <t>01/07/2026 19:03</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>24/07/2026 12:58</t>
+          <t>21/07/2026 04:52</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0029996-22.2023.8.16.0000</t>
+          <t>0041716-83.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3413,27 +3413,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Contratos Bancários | Cédula de Crédito Bancário</t>
+          <t>Locação de Imóvel | Cobrança de Aluguéis - Sem despejo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>25/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>01/07/2026 18:43</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21/07/2026 07:06</t>
+          <t>21/07/2026 12:44</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3450,37 +3450,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0036551-31.2018.8.16.0000</t>
+          <t>0041815-11.2023.8.16.0014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Condomínio</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>30/12/1899</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>29/06/2026 13:13</t>
+          <t>01/07/2026 14:13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>24/07/2026 12:37</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3497,37 +3497,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0036884-38.2018.8.16.0014</t>
+          <t>0042798-52.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Furto Qualificado</t>
+          <t>Rescisão / Resolução | Perdas e Danos | Cláusula Penal | Arras ou Sinal</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21/07/2026 00:10</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3544,37 +3544,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0039625-20.2023.8.16.0000</t>
+          <t>0043074-49.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Compromisso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>29/07/2025</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>29/06/2026 15:33</t>
+          <t>01/07/2026 14:53</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>24/07/2026 13:40</t>
+          <t>24/07/2026 16:15</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0041154-84.2018.8.16.0021</t>
+          <t>0043261-54.2020.8.16.0014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Sustação de Protesto | Indenização por Dano Moral</t>
+          <t>Perdas e Danos</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>01/07/2026 17:43</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>24/07/2026 13:59</t>
+          <t>24/07/2026 19:44</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3638,7 +3638,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0041235-44.2024.8.16.0014</t>
+          <t>0043986-12.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3648,27 +3648,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Práticas Abusivas</t>
+          <t>Tratamento médico-hospitalar | Práticas Abusivas</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>18/06/2025</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>01/07/2026 19:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>24/07/2026 11:15</t>
+          <t>21/07/2026 15:12</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0041690-77.2022.8.16.0014</t>
+          <t>0044606-24.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3695,27 +3695,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Crimes contra a Ordem Tributária</t>
+          <t>IPTU/ Imposto Predial e Territorial Urbano</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 14:03</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>01/07/2026 19:03</t>
+          <t>02/07/2026 14:03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21/07/2026 04:52</t>
+          <t>24/07/2026 18:52</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3732,37 +3732,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0041815-11.2023.8.16.0014</t>
+          <t>0049512-23.2026.8.16.0000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Ordinário em Habeas Corpus</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>01/07/2026 14:13</t>
+          <t>01/07/2026 17:53</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>24/07/2026 11:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3779,37 +3779,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0043074-49.2024.8.16.0000</t>
+          <t>0050229-06.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Compromisso</t>
+          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>01/07/2026 14:53</t>
+          <t>02/07/2026 16:43</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>24/07/2026 16:15</t>
+          <t>24/07/2026 20:44</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0043261-54.2020.8.16.0014</t>
+          <t>0051552-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3836,27 +3836,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Perdas e Danos</t>
+          <t>Duplicata</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19/09/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>02/07/2026 17:23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>24/07/2026 19:44</t>
+          <t>21/07/2026 08:04</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3873,37 +3873,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0048561-97.2024.8.16.0000</t>
+          <t>0051674-22.2021.8.16.0014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cédula de Crédito Bancário</t>
+          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19/11/2025</t>
+          <t>17/10/2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>29/06/2026 14:13</t>
+          <t>02/07/2026 14:43</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3920,37 +3920,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0048692-38.2025.8.16.0000</t>
+          <t>0051985-33.2013.8.16.0001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Compra e Venda | Indenização do Prejuízo</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>07/06/2022</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>29/06/2026 13:03</t>
+          <t>02/07/2026 15:23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>24/07/2026 19:05</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3967,37 +3967,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0049512-23.2026.8.16.0000</t>
+          <t>0056285-13.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recurso Ordinário em Habeas Corpus</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins | Falsificação / Corrupção / Adulteração / Alteração de produto destinado a fins terapêuticos ou medicinais | Prisão Preventiva</t>
+          <t>Contra a Mulher | Ameaça</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>01/07/2026 17:53</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>01/07/2026 17:53</t>
+          <t>01/07/2026 13:43</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>24/07/2026 11:00</t>
+          <t>24/07/2026 12:51</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0050229-06.2024.8.16.0000</t>
+          <t>0066543-90.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4024,27 +4024,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução | Assistência Judiciária Gratuita</t>
+          <t>Tráfico de Drogas e Condutas Afins</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>30/06/2026 13:53</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>02/07/2026 16:43</t>
+          <t>30/06/2026 13:53</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>24/07/2026 20:44</t>
+          <t>24/07/2026 12:42</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4061,37 +4061,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0051552-46.2024.8.16.0000</t>
+          <t>0067511-93.2016.8.16.0014</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agravo em Recurso Especial</t>
+          <t>Recurso Especial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Erro Médico</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>02/07/2026 17:23</t>
+          <t>01/07/2026 15:53</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21/07/2026 08:04</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4108,7 +4108,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0051674-22.2021.8.16.0014</t>
+          <t>0071353-45.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Vícios de Construção | Obrigação de Fazer / Não Fazer | Ônus da Prova</t>
+          <t>Dívida Ativa (Execução Fiscal)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>29/10/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>02/07/2026 14:43</t>
+          <t>02/07/2026 13:13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>21/07/2026 10:54</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4155,37 +4155,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0051985-33.2013.8.16.0001</t>
+          <t>0072332-62.2024.8.16.0014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Compra e Venda | Indenização do Prejuízo</t>
+          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>07/06/2022</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>02/07/2026 15:23</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4202,7 +4202,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0056285-13.2024.8.16.0014</t>
+          <t>0082204-46.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Contra a Mulher | Ameaça</t>
+          <t>Indenização por Dano Material</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>01/07/2026 13:43</t>
+          <t>02/07/2026 16:03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>24/07/2026 12:51</t>
+          <t>21/07/2026 01:59</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0066543-90.2025.8.16.0000</t>
+          <t>0082575-10.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4259,27 +4259,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tráfico de Drogas e Condutas Afins</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>30/06/2026 13:53</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>30/06/2026 13:53</t>
+          <t>02/07/2026 16:23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>24/07/2026 12:42</t>
+          <t>24/07/2026 10:58</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4296,37 +4296,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0067511-93.2016.8.16.0014</t>
+          <t>0086374-27.2025.8.16.0000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Recurso Especial</t>
+          <t>Agravo em Recurso Especial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Erro Médico</t>
+          <t>Homicídio Qualificado</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19/06/2024</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>01/07/2026 15:53</t>
+          <t>01/07/2026 13:23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21/07/2026 02:09</t>
+          <t>24/07/2026 13:22</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0071353-45.2024.8.16.0000</t>
+          <t>0090399-20.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4353,27 +4353,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dívida Ativa (Execução Fiscal)</t>
+          <t>Indenização por Dano Moral</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>29/10/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>02/07/2026 13:13</t>
+          <t>02/07/2026 13:43</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21/07/2026 10:54</t>
+          <t>24/07/2026 12:48</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0072332-62.2024.8.16.0014</t>
+          <t>0091320-13.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material | Indenização por Dano Moral</t>
+          <t>Defeito, nulidade ou anulação</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 11:50</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>24/07/2026 11:01</t>
+          <t>21/07/2026 02:09</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0082204-46.2024.8.16.0000</t>
+          <t>0093616-08.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4447,27 +4447,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indenização por Dano Material</t>
+          <t>Prescrição e Decadência</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
+          <t>31/07/2024</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 15:13</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>02/07/2026 16:03</t>
+          <t>02/07/2026 15:13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21/07/2026 01:59</t>
+          <t>24/07/2026 11:39</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0082575-10.2024.8.16.0000</t>
+          <t>0095221-86.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Recuperação judicial e Falência | Desconsideração da Personalidade Jurídica</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>07/07/2026 14:10</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>02/07/2026 16:23</t>
+          <t>07/07/2026 15:23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>24/07/2026 10:58</t>
+          <t>24/07/2026 12:52</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0086039-76.2023.8.16.0000</t>
+          <t>0097707-10.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4541,27 +4541,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rescisão / Resolução</t>
+          <t>Cédula de Crédito Bancário</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>18/09/2024</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>29/06/2026 14:33</t>
+          <t>01/07/2026 16:23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>21/07/2026 09:34</t>
+          <t>24/07/2026 11:01</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4578,7 +4578,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0086374-27.2025.8.16.0000</t>
+          <t>0100507-45.2023.8.16.0000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4588,27 +4588,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Homicídio Qualificado</t>
+          <t>Hipoteca</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>01/07/2026 13:23</t>
+          <t>01/07/2026 13:33</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>24/07/2026 13:22</t>
+          <t>21/07/2026 13:16</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4625,7 +4625,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0090399-20.2024.8.16.0000</t>
+          <t>0113087-73.2024.8.16.0000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indenização por Dano Moral</t>
+          <t>Cédula de Crédito Rural</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>17/09/2025</t>
         </is>
 